--- a/Versão5/DOCU/Ontologia_DOCUM.xlsx
+++ b/Versão5/DOCU/Ontologia_DOCUM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\DOCU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FB61DC-5B15-4B6C-BBB3-8D013246916D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5C5722-4788-415C-9B3C-300EE7310708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -937,9 +937,6 @@
     <t>é.revogante.de</t>
   </si>
   <si>
-    <t>é.revogado.por</t>
-  </si>
-  <si>
     <t>Manual</t>
   </si>
   <si>
@@ -2071,6 +2068,9 @@
   </si>
   <si>
     <t>é.usado.por</t>
+  </si>
+  <si>
+    <t>é.quem.revogou</t>
   </si>
 </sst>
 </file>
@@ -3037,7 +3037,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3048,7 +3048,7 @@
         <v>81</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3059,7 +3059,7 @@
         <v>201</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3070,7 +3070,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3082,7 +3082,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3094,7 +3094,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3105,7 +3105,7 @@
         <v>34</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -3113,10 +3113,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3127,7 +3127,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3138,7 +3138,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3149,7 +3149,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3160,7 +3160,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3171,7 +3171,7 @@
         <v>202</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3182,7 +3182,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3193,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3204,7 +3204,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3215,7 +3215,7 @@
         <v>201</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3224,10 +3224,10 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46160.371336342592</v>
+        <v>46213.80458877315</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3238,7 +3238,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3249,7 +3249,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3260,7 +3260,7 @@
         <v>33</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3271,7 +3271,7 @@
         <v>203</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3282,19 +3282,19 @@
         <v>204</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="50" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B24" s="6" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize documentation data</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3350,7 +3350,7 @@
         <v>65</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G1" s="45" t="s">
         <v>66</v>
@@ -3404,16 +3404,16 @@
         <v>61</v>
       </c>
       <c r="X1" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="Y1" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="Y1" s="26" t="s">
+      <c r="Z1" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="Z1" s="47" t="s">
+      <c r="AA1" s="48" t="s">
         <v>314</v>
-      </c>
-      <c r="AA1" s="48" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3421,19 +3421,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="55" t="s">
+        <v>435</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>322</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>323</v>
+      </c>
+      <c r="F2" s="56" t="s">
         <v>436</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>322</v>
-      </c>
-      <c r="D2" s="55" t="s">
-        <v>323</v>
-      </c>
-      <c r="E2" s="55" t="s">
-        <v>324</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>437</v>
       </c>
       <c r="G2" s="46" t="s">
         <v>9</v>
@@ -3467,10 +3467,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="49" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q2" s="49" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="R2" s="58" t="s">
         <v>9</v>
@@ -3501,7 +3501,7 @@
         <v>9</v>
       </c>
       <c r="Z2" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA2" s="49" t="str">
         <f t="shared" ref="AA2:AA12" si="0">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -3513,19 +3513,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C3" s="56" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="55" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="55" t="s">
-        <v>323</v>
-      </c>
       <c r="E3" s="55" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G3" s="46" t="s">
         <v>9</v>
@@ -3559,10 +3559,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="49" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q3" s="49" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="R3" s="58" t="s">
         <v>9</v>
@@ -3593,7 +3593,7 @@
         <v>9</v>
       </c>
       <c r="Z3" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA3" s="49" t="str">
         <f t="shared" si="0"/>
@@ -3605,19 +3605,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C4" s="56" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="55" t="s">
         <v>322</v>
       </c>
-      <c r="D4" s="55" t="s">
-        <v>323</v>
-      </c>
       <c r="E4" s="55" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G4" s="46" t="s">
         <v>9</v>
@@ -3651,10 +3651,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="49" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q4" s="49" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R4" s="58" t="s">
         <v>9</v>
@@ -3685,7 +3685,7 @@
         <v>9</v>
       </c>
       <c r="Z4" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA4" s="49" t="str">
         <f t="shared" si="0"/>
@@ -3697,19 +3697,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C5" s="56" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="55" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="55" t="s">
-        <v>323</v>
-      </c>
       <c r="E5" s="55" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G5" s="46" t="s">
         <v>9</v>
@@ -3743,10 +3743,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="49" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q5" s="49" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R5" s="58" t="s">
         <v>9</v>
@@ -3777,7 +3777,7 @@
         <v>9</v>
       </c>
       <c r="Z5" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA5" s="49" t="str">
         <f t="shared" si="0"/>
@@ -3789,19 +3789,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C6" s="56" t="s">
+        <v>321</v>
+      </c>
+      <c r="D6" s="55" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="55" t="s">
-        <v>323</v>
-      </c>
       <c r="E6" s="55" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G6" s="46" t="s">
         <v>9</v>
@@ -3835,10 +3835,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="49" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q6" s="49" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="R6" s="58" t="s">
         <v>9</v>
@@ -3869,7 +3869,7 @@
         <v>9</v>
       </c>
       <c r="Z6" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA6" s="49" t="str">
         <f t="shared" si="0"/>
@@ -3887,13 +3887,13 @@
         <v>82</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G7" s="46" t="s">
         <v>9</v>
@@ -3927,7 +3927,7 @@
         <v>Arquivo</v>
       </c>
       <c r="P7" s="49" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="Q7" s="49" t="str">
         <f>_xlfn.TRANSLATE(P7,"pt","es")</f>
@@ -3962,7 +3962,7 @@
         <v>9</v>
       </c>
       <c r="Z7" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA7" s="49" t="str">
         <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
@@ -3980,13 +3980,13 @@
         <v>82</v>
       </c>
       <c r="D8" s="42" t="s">
+        <v>634</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>633</v>
+      </c>
+      <c r="F8" s="44" t="s">
         <v>635</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>634</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>636</v>
       </c>
       <c r="G8" s="46" t="s">
         <v>9</v>
@@ -4020,10 +4020,10 @@
         <v>Template</v>
       </c>
       <c r="P8" s="49" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="Q8" s="49" t="str">
-        <f t="shared" ref="Q8:Q12" si="8">_xlfn.TRANSLATE(P8,"pt","es")</f>
+        <f t="shared" ref="Q8:Q10" si="8">_xlfn.TRANSLATE(P8,"pt","es")</f>
         <v>Define un archivo usado como plantilla, prototipo, plantilla, puede ser rte, dwt, etc.</v>
       </c>
       <c r="R8" s="58" t="s">
@@ -4055,7 +4055,7 @@
         <v>9</v>
       </c>
       <c r="Z8" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA8" s="49" t="str">
         <f t="shared" ref="AA8:AA11" si="12">_xlfn.TRANSLATE(P8,"pt","en")</f>
@@ -4073,13 +4073,13 @@
         <v>82</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G9" s="46" t="s">
         <v>9</v>
@@ -4113,7 +4113,7 @@
         <v>Aplicação</v>
       </c>
       <c r="P9" s="49" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="Q9" s="49" t="str">
         <f t="shared" si="8"/>
@@ -4148,7 +4148,7 @@
         <v>9</v>
       </c>
       <c r="Z9" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA9" s="49" t="str">
         <f t="shared" si="12"/>
@@ -4166,13 +4166,13 @@
         <v>82</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G10" s="46" t="s">
         <v>9</v>
@@ -4206,7 +4206,7 @@
         <v>Dados Estruturados</v>
       </c>
       <c r="P10" s="49" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="Q10" s="49" t="str">
         <f t="shared" si="8"/>
@@ -4241,7 +4241,7 @@
         <v>9</v>
       </c>
       <c r="Z10" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA10" s="49" t="str">
         <f t="shared" si="12"/>
@@ -4259,13 +4259,13 @@
         <v>82</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G11" s="46" t="s">
         <v>9</v>
@@ -4299,7 +4299,7 @@
         <v>Dados Não Estruturados</v>
       </c>
       <c r="P11" s="49" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="Q11" s="49" t="str">
         <f t="shared" ref="Q11" si="13">_xlfn.TRANSLATE(P11,"pt","es")</f>
@@ -4334,7 +4334,7 @@
         <v>9</v>
       </c>
       <c r="Z11" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA11" s="49" t="str">
         <f t="shared" si="12"/>
@@ -4352,13 +4352,13 @@
         <v>82</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G12" s="46" t="s">
         <v>9</v>
@@ -4392,10 +4392,10 @@
         <v>Biblioteca</v>
       </c>
       <c r="P12" s="49" t="s">
+        <v>657</v>
+      </c>
+      <c r="Q12" s="49" t="s">
         <v>658</v>
-      </c>
-      <c r="Q12" s="49" t="s">
-        <v>659</v>
       </c>
       <c r="R12" s="58" t="s">
         <v>9</v>
@@ -4426,7 +4426,7 @@
         <v>9</v>
       </c>
       <c r="Z12" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA12" s="49" t="str">
         <f t="shared" si="0"/>
@@ -4444,13 +4444,13 @@
         <v>82</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G13" s="46" t="s">
         <v>9</v>
@@ -4513,13 +4513,13 @@
         <v>Key-DOC-13</v>
       </c>
       <c r="X13" s="60" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Y13" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z13" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA13" s="49" t="str">
         <f t="shared" ref="AA13:AA75" si="19">_xlfn.TRANSLATE(P13,"pt","en")</f>
@@ -4537,13 +4537,13 @@
         <v>82</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E14" s="41" t="s">
+        <v>557</v>
+      </c>
+      <c r="F14" s="44" t="s">
         <v>558</v>
-      </c>
-      <c r="F14" s="44" t="s">
-        <v>559</v>
       </c>
       <c r="G14" s="46" t="s">
         <v>9</v>
@@ -4606,13 +4606,13 @@
         <v>Key-DOC-14</v>
       </c>
       <c r="X14" s="60" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Y14" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z14" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA14" s="49" t="str">
         <f t="shared" si="19"/>
@@ -4630,13 +4630,13 @@
         <v>82</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G15" s="46" t="s">
         <v>9</v>
@@ -4699,13 +4699,13 @@
         <v>Key-DOC-15</v>
       </c>
       <c r="X15" s="60" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Y15" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z15" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA15" s="49" t="str">
         <f t="shared" si="19"/>
@@ -4723,13 +4723,13 @@
         <v>82</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E16" s="41" t="s">
         <v>185</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G16" s="46" t="s">
         <v>9</v>
@@ -4792,13 +4792,13 @@
         <v>Key-DOC-16</v>
       </c>
       <c r="X16" s="60" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Y16" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z16" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA16" s="49" t="str">
         <f t="shared" si="19"/>
@@ -4816,13 +4816,13 @@
         <v>82</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E17" s="41" t="s">
         <v>185</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G17" s="46" t="s">
         <v>9</v>
@@ -4885,13 +4885,13 @@
         <v>Key-DOC-17</v>
       </c>
       <c r="X17" s="60" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Y17" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z17" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA17" s="49" t="str">
         <f t="shared" si="19"/>
@@ -4909,13 +4909,13 @@
         <v>82</v>
       </c>
       <c r="D18" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E18" s="41" t="s">
         <v>185</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G18" s="46" t="s">
         <v>9</v>
@@ -4978,13 +4978,13 @@
         <v>Key-DOC-18</v>
       </c>
       <c r="X18" s="60" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Y18" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z18" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA18" s="49" t="str">
         <f t="shared" si="19"/>
@@ -5002,13 +5002,13 @@
         <v>82</v>
       </c>
       <c r="D19" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E19" s="41" t="s">
         <v>185</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G19" s="46" t="s">
         <v>9</v>
@@ -5071,13 +5071,13 @@
         <v>Key-DOC-19</v>
       </c>
       <c r="X19" s="60" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Y19" s="61" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Z19" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA19" s="49" t="str">
         <f t="shared" si="19"/>
@@ -5095,13 +5095,13 @@
         <v>82</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E20" s="41" t="s">
         <v>185</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G20" s="46" t="s">
         <v>9</v>
@@ -5164,13 +5164,13 @@
         <v>Key-DOC-20</v>
       </c>
       <c r="X20" s="60" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Y20" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z20" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA20" s="49" t="str">
         <f t="shared" si="19"/>
@@ -5188,13 +5188,13 @@
         <v>82</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E21" s="41" t="s">
         <v>185</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G21" s="46" t="s">
         <v>9</v>
@@ -5257,13 +5257,13 @@
         <v>Key-DOC-21</v>
       </c>
       <c r="X21" s="60" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Y21" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z21" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA21" s="49" t="str">
         <f t="shared" si="19"/>
@@ -5281,13 +5281,13 @@
         <v>82</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E22" s="41" t="s">
         <v>186</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G22" s="46" t="s">
         <v>9</v>
@@ -5350,13 +5350,13 @@
         <v>Key-DOC-22</v>
       </c>
       <c r="X22" s="60" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y22" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z22" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA22" s="49" t="str">
         <f t="shared" ref="AA22" si="24">_xlfn.TRANSLATE(P22,"pt","en")</f>
@@ -5374,13 +5374,13 @@
         <v>82</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E23" s="41" t="s">
         <v>186</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G23" s="46" t="s">
         <v>9</v>
@@ -5443,13 +5443,13 @@
         <v>Key-DOC-23</v>
       </c>
       <c r="X23" s="60" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y23" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z23" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA23" s="49" t="str">
         <f t="shared" ref="AA23:AA24" si="25">_xlfn.TRANSLATE(P23,"pt","en")</f>
@@ -5467,13 +5467,13 @@
         <v>82</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E24" s="41" t="s">
         <v>186</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G24" s="46" t="s">
         <v>9</v>
@@ -5536,13 +5536,13 @@
         <v>Key-DOC-24</v>
       </c>
       <c r="X24" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Y24" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z24" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA24" s="49" t="str">
         <f t="shared" si="25"/>
@@ -5560,13 +5560,13 @@
         <v>82</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E25" s="41" t="s">
         <v>186</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G25" s="46" t="s">
         <v>9</v>
@@ -5629,13 +5629,13 @@
         <v>Key-DOC-25</v>
       </c>
       <c r="X25" s="60" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Y25" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z25" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA25" s="49" t="str">
         <f t="shared" si="19"/>
@@ -5653,13 +5653,13 @@
         <v>82</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E26" s="41" t="s">
         <v>186</v>
       </c>
       <c r="F26" s="44" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G26" s="46" t="s">
         <v>9</v>
@@ -5722,13 +5722,13 @@
         <v>Key-DOC-26</v>
       </c>
       <c r="X26" s="60" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Y26" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z26" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA26" s="49" t="str">
         <f t="shared" si="19"/>
@@ -5746,13 +5746,13 @@
         <v>82</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E27" s="41" t="s">
         <v>186</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G27" s="46" t="s">
         <v>9</v>
@@ -5815,13 +5815,13 @@
         <v>Key-DOC-27</v>
       </c>
       <c r="X27" s="60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y27" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z27" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA27" s="49" t="str">
         <f t="shared" si="19"/>
@@ -5839,13 +5839,13 @@
         <v>82</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E28" s="41" t="s">
         <v>186</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G28" s="46" t="s">
         <v>9</v>
@@ -5879,7 +5879,7 @@
         <v>Simbolo Corte Linha Quebrada</v>
       </c>
       <c r="P28" s="57" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Q28" s="49" t="str">
         <f t="shared" si="20"/>
@@ -5908,13 +5908,13 @@
         <v>Key-DOC-28</v>
       </c>
       <c r="X28" s="60" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Y28" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z28" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA28" s="49" t="str">
         <f t="shared" si="19"/>
@@ -5932,13 +5932,13 @@
         <v>82</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E29" s="41" t="s">
         <v>187</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G29" s="46" t="s">
         <v>9</v>
@@ -5972,7 +5972,7 @@
         <v>Detalhe Decalque</v>
       </c>
       <c r="P29" s="57" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q29" s="49" t="str">
         <f t="shared" si="20"/>
@@ -6001,13 +6001,13 @@
         <v>Key-DOC-29</v>
       </c>
       <c r="X29" s="60" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Y29" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z29" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA29" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6025,13 +6025,13 @@
         <v>82</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E30" s="41" t="s">
         <v>187</v>
       </c>
       <c r="F30" s="44" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G30" s="46" t="s">
         <v>9</v>
@@ -6094,13 +6094,13 @@
         <v>Key-DOC-30</v>
       </c>
       <c r="X30" s="60" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Y30" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z30" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA30" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6118,13 +6118,13 @@
         <v>82</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E31" s="41" t="s">
         <v>187</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G31" s="46" t="s">
         <v>9</v>
@@ -6187,13 +6187,13 @@
         <v>Key-DOC-31</v>
       </c>
       <c r="X31" s="60" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Y31" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z31" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA31" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6211,13 +6211,13 @@
         <v>82</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E32" s="41" t="s">
         <v>187</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G32" s="46" t="s">
         <v>9</v>
@@ -6251,7 +6251,7 @@
         <v>Detalhe Linha Repetida</v>
       </c>
       <c r="P32" s="57" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="Q32" s="49" t="str">
         <f t="shared" si="20"/>
@@ -6280,13 +6280,13 @@
         <v>Key-DOC-32</v>
       </c>
       <c r="X32" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Y32" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z32" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA32" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6304,7 +6304,7 @@
         <v>82</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E33" s="41" t="s">
         <v>188</v>
@@ -6373,13 +6373,13 @@
         <v>Key-DOC-33</v>
       </c>
       <c r="X33" s="60" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y33" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z33" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA33" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6397,13 +6397,13 @@
         <v>82</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E34" s="41" t="s">
         <v>188</v>
       </c>
       <c r="F34" s="44" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G34" s="46" t="s">
         <v>9</v>
@@ -6466,13 +6466,13 @@
         <v>Key-DOC-34</v>
       </c>
       <c r="X34" s="60" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Y34" s="61" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z34" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA34" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6490,13 +6490,13 @@
         <v>82</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E35" s="41" t="s">
         <v>189</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G35" s="46" t="s">
         <v>9</v>
@@ -6559,13 +6559,13 @@
         <v>Key-DOC-35</v>
       </c>
       <c r="X35" s="60" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Y35" s="61" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Z35" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA35" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6583,13 +6583,13 @@
         <v>82</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E36" s="41" t="s">
         <v>189</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G36" s="46" t="s">
         <v>9</v>
@@ -6652,13 +6652,13 @@
         <v>Key-DOC-36</v>
       </c>
       <c r="X36" s="60" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Y36" s="61" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Z36" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA36" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6676,13 +6676,13 @@
         <v>82</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E37" s="41" t="s">
         <v>189</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G37" s="46" t="s">
         <v>9</v>
@@ -6716,7 +6716,7 @@
         <v>Marcador Cota</v>
       </c>
       <c r="P37" s="57" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="Q37" s="49" t="str">
         <f t="shared" si="20"/>
@@ -6745,13 +6745,13 @@
         <v>Key-DOC-37</v>
       </c>
       <c r="X37" s="60" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Y37" s="61" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Z37" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA37" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6769,13 +6769,13 @@
         <v>82</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E38" s="41" t="s">
         <v>189</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G38" s="46" t="s">
         <v>9</v>
@@ -6809,7 +6809,7 @@
         <v>Marcador Cota Símbolo</v>
       </c>
       <c r="P38" s="57" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q38" s="49" t="str">
         <f t="shared" si="20"/>
@@ -6838,13 +6838,13 @@
         <v>Key-DOC-38</v>
       </c>
       <c r="X38" s="60" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y38" s="61" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Z38" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA38" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6862,13 +6862,13 @@
         <v>82</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E39" s="41" t="s">
         <v>189</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G39" s="46" t="s">
         <v>9</v>
@@ -6902,7 +6902,7 @@
         <v>Marcador Caimento</v>
       </c>
       <c r="P39" s="57" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q39" s="49" t="str">
         <f t="shared" si="20"/>
@@ -6931,13 +6931,13 @@
         <v>Key-DOC-39</v>
       </c>
       <c r="X39" s="60" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y39" s="61" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Z39" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA39" s="49" t="str">
         <f t="shared" si="19"/>
@@ -6955,13 +6955,13 @@
         <v>82</v>
       </c>
       <c r="D40" s="42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E40" s="41" t="s">
         <v>189</v>
       </c>
       <c r="F40" s="44" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G40" s="46" t="s">
         <v>9</v>
@@ -7024,13 +7024,13 @@
         <v>Key-DOC-40</v>
       </c>
       <c r="X40" s="60" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y40" s="61" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Z40" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA40" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7048,13 +7048,13 @@
         <v>82</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E41" s="41" t="s">
         <v>190</v>
       </c>
       <c r="F41" s="44" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G41" s="46" t="s">
         <v>9</v>
@@ -7088,7 +7088,7 @@
         <v>Dimensão</v>
       </c>
       <c r="P41" s="57" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q41" s="49" t="str">
         <f t="shared" si="20"/>
@@ -7117,13 +7117,13 @@
         <v>Key-DOC-41</v>
       </c>
       <c r="X41" s="60" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Y41" s="61" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z41" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA41" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7141,13 +7141,13 @@
         <v>82</v>
       </c>
       <c r="D42" s="42" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E42" s="41" t="s">
         <v>190</v>
       </c>
       <c r="F42" s="44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G42" s="46" t="s">
         <v>9</v>
@@ -7210,13 +7210,13 @@
         <v>Key-DOC-42</v>
       </c>
       <c r="X42" s="60" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Y42" s="61" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z42" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA42" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7234,13 +7234,13 @@
         <v>82</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E43" s="41" t="s">
         <v>190</v>
       </c>
       <c r="F43" s="44" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G43" s="46" t="s">
         <v>9</v>
@@ -7303,13 +7303,13 @@
         <v>Key-DOC-43</v>
       </c>
       <c r="X43" s="60" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Y43" s="61" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z43" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA43" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7327,13 +7327,13 @@
         <v>82</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E44" s="41" t="s">
         <v>191</v>
       </c>
       <c r="F44" s="44" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G44" s="46" t="s">
         <v>9</v>
@@ -7396,13 +7396,13 @@
         <v>Key-DOC-44</v>
       </c>
       <c r="X44" s="60" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y44" s="61" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z44" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA44" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7420,13 +7420,13 @@
         <v>82</v>
       </c>
       <c r="D45" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E45" s="41" t="s">
         <v>191</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G45" s="46" t="s">
         <v>9</v>
@@ -7489,13 +7489,13 @@
         <v>Key-DOC-45</v>
       </c>
       <c r="X45" s="60" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y45" s="61" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z45" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA45" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7513,13 +7513,13 @@
         <v>82</v>
       </c>
       <c r="D46" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F46" s="44" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G46" s="46" t="s">
         <v>9</v>
@@ -7582,13 +7582,13 @@
         <v>Key-DOC-46</v>
       </c>
       <c r="X46" s="60" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Y46" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z46" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA46" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7606,13 +7606,13 @@
         <v>82</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G47" s="46" t="s">
         <v>9</v>
@@ -7646,7 +7646,7 @@
         <v>Linhas Invisíveis</v>
       </c>
       <c r="P47" s="57" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="Q47" s="49" t="str">
         <f t="shared" si="20"/>
@@ -7675,13 +7675,13 @@
         <v>Key-DOC-47</v>
       </c>
       <c r="X47" s="60" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y47" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z47" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA47" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7699,13 +7699,13 @@
         <v>82</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E48" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F48" s="44" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G48" s="46" t="s">
         <v>9</v>
@@ -7739,7 +7739,7 @@
         <v>Linhas Projetadas</v>
       </c>
       <c r="P48" s="57" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q48" s="49" t="str">
         <f t="shared" si="20"/>
@@ -7768,13 +7768,13 @@
         <v>Key-DOC-48</v>
       </c>
       <c r="X48" s="60" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Y48" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z48" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA48" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7792,13 +7792,13 @@
         <v>82</v>
       </c>
       <c r="D49" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E49" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F49" s="44" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G49" s="46" t="s">
         <v>9</v>
@@ -7861,13 +7861,13 @@
         <v>Key-DOC-49</v>
       </c>
       <c r="X49" s="60" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y49" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z49" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA49" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7885,13 +7885,13 @@
         <v>82</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F50" s="44" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G50" s="46" t="s">
         <v>9</v>
@@ -7925,7 +7925,7 @@
         <v>Linhas Centrais</v>
       </c>
       <c r="P50" s="57" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q50" s="49" t="str">
         <f t="shared" si="20"/>
@@ -7954,13 +7954,13 @@
         <v>Key-DOC-50</v>
       </c>
       <c r="X50" s="60" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Y50" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z50" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA50" s="49" t="str">
         <f t="shared" si="19"/>
@@ -7978,13 +7978,13 @@
         <v>82</v>
       </c>
       <c r="D51" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E51" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F51" s="44" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G51" s="46" t="s">
         <v>9</v>
@@ -8047,13 +8047,13 @@
         <v>Key-DOC-51</v>
       </c>
       <c r="X51" s="60" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Y51" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z51" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA51" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8071,13 +8071,13 @@
         <v>82</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E52" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F52" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G52" s="46" t="s">
         <v>9</v>
@@ -8140,13 +8140,13 @@
         <v>Key-DOC-52</v>
       </c>
       <c r="X52" s="60" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Y52" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z52" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA52" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8164,13 +8164,13 @@
         <v>82</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E53" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F53" s="44" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G53" s="46" t="s">
         <v>9</v>
@@ -8204,7 +8204,7 @@
         <v>Linhas Acima</v>
       </c>
       <c r="P53" s="57" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q53" s="49" t="str">
         <f t="shared" si="20"/>
@@ -8233,13 +8233,13 @@
         <v>Key-DOC-53</v>
       </c>
       <c r="X53" s="60" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Y53" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z53" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA53" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8257,13 +8257,13 @@
         <v>82</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F54" s="44" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G54" s="46" t="s">
         <v>9</v>
@@ -8326,13 +8326,13 @@
         <v>Key-DOC-54</v>
       </c>
       <c r="X54" s="60" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Y54" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z54" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA54" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8350,13 +8350,13 @@
         <v>82</v>
       </c>
       <c r="D55" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E55" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F55" s="44" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G55" s="46" t="s">
         <v>9</v>
@@ -8390,7 +8390,7 @@
         <v>Linhas Ocultas Piso</v>
       </c>
       <c r="P55" s="57" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Q55" s="49" t="str">
         <f t="shared" si="20"/>
@@ -8419,13 +8419,13 @@
         <v>Key-DOC-55</v>
       </c>
       <c r="X55" s="60" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y55" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z55" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA55" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8443,13 +8443,13 @@
         <v>82</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E56" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F56" s="44" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G56" s="46" t="s">
         <v>9</v>
@@ -8512,13 +8512,13 @@
         <v>Key-DOC-56</v>
       </c>
       <c r="X56" s="60" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Y56" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z56" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA56" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8536,13 +8536,13 @@
         <v>82</v>
       </c>
       <c r="D57" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E57" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F57" s="44" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G57" s="46" t="s">
         <v>9</v>
@@ -8576,7 +8576,7 @@
         <v>Colunas Linhas Ocultas</v>
       </c>
       <c r="P57" s="57" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="Q57" s="49" t="str">
         <f t="shared" si="20"/>
@@ -8605,13 +8605,13 @@
         <v>Key-DOC-57</v>
       </c>
       <c r="X57" s="60" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y57" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z57" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA57" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8629,13 +8629,13 @@
         <v>82</v>
       </c>
       <c r="D58" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E58" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F58" s="44" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G58" s="46" t="s">
         <v>9</v>
@@ -8669,7 +8669,7 @@
         <v>Fundação Linhas Ocultas</v>
       </c>
       <c r="P58" s="57" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q58" s="49" t="str">
         <f t="shared" si="20"/>
@@ -8698,13 +8698,13 @@
         <v>Key-DOC-58</v>
       </c>
       <c r="X58" s="60" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y58" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z58" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA58" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8722,13 +8722,13 @@
         <v>82</v>
       </c>
       <c r="D59" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E59" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F59" s="44" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G59" s="46" t="s">
         <v>9</v>
@@ -8762,7 +8762,7 @@
         <v>Vigas Linhas Ocultas</v>
       </c>
       <c r="P59" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="Q59" s="49" t="str">
         <f t="shared" si="20"/>
@@ -8791,13 +8791,13 @@
         <v>Key-DOC-59</v>
       </c>
       <c r="X59" s="60" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y59" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z59" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA59" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8815,13 +8815,13 @@
         <v>82</v>
       </c>
       <c r="D60" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E60" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F60" s="44" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G60" s="46" t="s">
         <v>9</v>
@@ -8855,7 +8855,7 @@
         <v>Paredes Linhas Ocultas</v>
       </c>
       <c r="P60" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="Q60" s="49" t="str">
         <f t="shared" si="20"/>
@@ -8884,13 +8884,13 @@
         <v>Key-DOC-60</v>
       </c>
       <c r="X60" s="60" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y60" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z60" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA60" s="49" t="str">
         <f t="shared" si="19"/>
@@ -8908,13 +8908,13 @@
         <v>82</v>
       </c>
       <c r="D61" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E61" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F61" s="44" t="s">
         <v>556</v>
-      </c>
-      <c r="F61" s="44" t="s">
-        <v>557</v>
       </c>
       <c r="G61" s="46" t="s">
         <v>9</v>
@@ -8977,13 +8977,13 @@
         <v>Key-DOC-61</v>
       </c>
       <c r="X61" s="60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Y61" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z61" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA61" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9001,13 +9001,13 @@
         <v>82</v>
       </c>
       <c r="D62" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E62" s="41" t="s">
         <v>192</v>
       </c>
       <c r="F62" s="44" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G62" s="46" t="s">
         <v>9</v>
@@ -9070,13 +9070,13 @@
         <v>Key-DOC-62</v>
       </c>
       <c r="X62" s="60" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Y62" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z62" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA62" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9094,13 +9094,13 @@
         <v>82</v>
       </c>
       <c r="D63" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E63" s="41" t="s">
         <v>192</v>
       </c>
       <c r="F63" s="44" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G63" s="46" t="s">
         <v>9</v>
@@ -9163,13 +9163,13 @@
         <v>Key-DOC-63</v>
       </c>
       <c r="X63" s="60" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y63" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z63" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA63" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9187,13 +9187,13 @@
         <v>82</v>
       </c>
       <c r="D64" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E64" s="41" t="s">
         <v>192</v>
       </c>
       <c r="F64" s="44" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G64" s="46" t="s">
         <v>9</v>
@@ -9256,13 +9256,13 @@
         <v>Key-DOC-64</v>
       </c>
       <c r="X64" s="60" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Y64" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z64" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA64" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9280,13 +9280,13 @@
         <v>82</v>
       </c>
       <c r="D65" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E65" s="41" t="s">
         <v>192</v>
       </c>
       <c r="F65" s="44" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G65" s="46" t="s">
         <v>9</v>
@@ -9349,13 +9349,13 @@
         <v>Key-DOC-65</v>
       </c>
       <c r="X65" s="60" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y65" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z65" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA65" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9373,13 +9373,13 @@
         <v>82</v>
       </c>
       <c r="D66" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E66" s="41" t="s">
         <v>193</v>
       </c>
       <c r="F66" s="44" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G66" s="46" t="s">
         <v>9</v>
@@ -9442,13 +9442,13 @@
         <v>Key-DOC-66</v>
       </c>
       <c r="X66" s="60" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Y66" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z66" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA66" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9466,13 +9466,13 @@
         <v>82</v>
       </c>
       <c r="D67" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E67" s="42" t="s">
         <v>194</v>
       </c>
       <c r="F67" s="44" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G67" s="46" t="s">
         <v>9</v>
@@ -9535,13 +9535,13 @@
         <v>Key-DOC-67</v>
       </c>
       <c r="X67" s="60" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y67" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z67" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA67" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9559,13 +9559,13 @@
         <v>82</v>
       </c>
       <c r="D68" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E68" s="41" t="s">
         <v>194</v>
       </c>
       <c r="F68" s="44" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G68" s="46" t="s">
         <v>9</v>
@@ -9628,13 +9628,13 @@
         <v>Key-DOC-68</v>
       </c>
       <c r="X68" s="60" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y68" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z68" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA68" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9652,13 +9652,13 @@
         <v>82</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E69" s="41" t="s">
         <v>123</v>
       </c>
       <c r="F69" s="44" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G69" s="46" t="s">
         <v>9</v>
@@ -9721,13 +9721,13 @@
         <v>Key-DOC-69</v>
       </c>
       <c r="X69" s="60" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Y69" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z69" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA69" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9745,13 +9745,13 @@
         <v>82</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E70" s="42" t="s">
         <v>195</v>
       </c>
       <c r="F70" s="44" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G70" s="46" t="s">
         <v>9</v>
@@ -9814,13 +9814,13 @@
         <v>Key-DOC-70</v>
       </c>
       <c r="X70" s="60" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y70" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z70" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA70" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9838,13 +9838,13 @@
         <v>82</v>
       </c>
       <c r="D71" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E71" s="42" t="s">
         <v>195</v>
       </c>
       <c r="F71" s="44" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G71" s="46" t="s">
         <v>9</v>
@@ -9907,13 +9907,13 @@
         <v>Key-DOC-71</v>
       </c>
       <c r="X71" s="60" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y71" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z71" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA71" s="49" t="str">
         <f t="shared" si="19"/>
@@ -9931,13 +9931,13 @@
         <v>82</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E72" s="42" t="s">
         <v>196</v>
       </c>
       <c r="F72" s="44" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G72" s="46" t="s">
         <v>9</v>
@@ -10000,13 +10000,13 @@
         <v>Key-DOC-72</v>
       </c>
       <c r="X72" s="60" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y72" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z72" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA72" s="49" t="str">
         <f t="shared" si="19"/>
@@ -10024,13 +10024,13 @@
         <v>82</v>
       </c>
       <c r="D73" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E73" s="42" t="s">
         <v>196</v>
       </c>
       <c r="F73" s="44" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G73" s="46" t="s">
         <v>9</v>
@@ -10093,13 +10093,13 @@
         <v>Key-DOC-73</v>
       </c>
       <c r="X73" s="60" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Y73" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z73" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA73" s="49" t="str">
         <f t="shared" si="19"/>
@@ -10117,13 +10117,13 @@
         <v>82</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E74" s="42" t="s">
         <v>197</v>
       </c>
       <c r="F74" s="44" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G74" s="46" t="s">
         <v>9</v>
@@ -10186,13 +10186,13 @@
         <v>Key-DOC-74</v>
       </c>
       <c r="X74" s="60" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y74" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z74" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA74" s="49" t="str">
         <f t="shared" si="19"/>
@@ -10210,13 +10210,13 @@
         <v>82</v>
       </c>
       <c r="D75" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E75" s="42" t="s">
         <v>197</v>
       </c>
       <c r="F75" s="44" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G75" s="46" t="s">
         <v>9</v>
@@ -10279,13 +10279,13 @@
         <v>Key-DOC-75</v>
       </c>
       <c r="X75" s="60" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Y75" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z75" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA75" s="49" t="str">
         <f t="shared" si="19"/>
@@ -10303,13 +10303,13 @@
         <v>82</v>
       </c>
       <c r="D76" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E76" s="41" t="s">
         <v>198</v>
       </c>
       <c r="F76" s="44" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G76" s="46" t="s">
         <v>9</v>
@@ -10372,13 +10372,13 @@
         <v>Key-DOC-76</v>
       </c>
       <c r="X76" s="60" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Y76" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z76" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA76" s="49" t="str">
         <f t="shared" ref="AA76:AA137" si="33">_xlfn.TRANSLATE(P76,"pt","en")</f>
@@ -10396,13 +10396,13 @@
         <v>82</v>
       </c>
       <c r="D77" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E77" s="41" t="s">
         <v>198</v>
       </c>
       <c r="F77" s="44" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G77" s="46" t="s">
         <v>9</v>
@@ -10465,13 +10465,13 @@
         <v>Key-DOC-77</v>
       </c>
       <c r="X77" s="60" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y77" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z77" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA77" s="49" t="str">
         <f t="shared" si="33"/>
@@ -10489,13 +10489,13 @@
         <v>82</v>
       </c>
       <c r="D78" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E78" s="41" t="s">
         <v>199</v>
       </c>
       <c r="F78" s="44" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G78" s="46" t="s">
         <v>9</v>
@@ -10558,13 +10558,13 @@
         <v>Key-DOC-78</v>
       </c>
       <c r="X78" s="60" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Y78" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z78" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA78" s="49" t="str">
         <f t="shared" si="33"/>
@@ -10582,13 +10582,13 @@
         <v>82</v>
       </c>
       <c r="D79" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E79" s="41" t="s">
         <v>199</v>
       </c>
       <c r="F79" s="44" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G79" s="46" t="s">
         <v>9</v>
@@ -10651,13 +10651,13 @@
         <v>Key-DOC-79</v>
       </c>
       <c r="X79" s="60" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y79" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z79" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA79" s="49" t="str">
         <f t="shared" si="33"/>
@@ -10675,10 +10675,10 @@
         <v>82</v>
       </c>
       <c r="D80" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E80" s="42" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F80" s="44" t="s">
         <v>138</v>
@@ -10744,13 +10744,13 @@
         <v>Key-DOC-80</v>
       </c>
       <c r="X80" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Y80" s="61" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z80" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA80" s="49" t="str">
         <f t="shared" ref="AA80" si="38">_xlfn.TRANSLATE(P80,"pt","en")</f>
@@ -10768,13 +10768,13 @@
         <v>82</v>
       </c>
       <c r="D81" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E81" s="42" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F81" s="44" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G81" s="46" t="s">
         <v>9</v>
@@ -10837,13 +10837,13 @@
         <v>Key-DOC-81</v>
       </c>
       <c r="X81" s="60" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y81" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z81" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA81" s="49" t="str">
         <f t="shared" si="33"/>
@@ -10861,13 +10861,13 @@
         <v>82</v>
       </c>
       <c r="D82" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E82" s="42" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F82" s="44" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G82" s="46" t="s">
         <v>9</v>
@@ -10930,13 +10930,13 @@
         <v>Key-DOC-82</v>
       </c>
       <c r="X82" s="60" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y82" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z82" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA82" s="49" t="str">
         <f t="shared" si="33"/>
@@ -10954,13 +10954,13 @@
         <v>82</v>
       </c>
       <c r="D83" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E83" s="42" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F83" s="44" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G83" s="46" t="s">
         <v>9</v>
@@ -11023,13 +11023,13 @@
         <v>Key-DOC-83</v>
       </c>
       <c r="X83" s="60" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y83" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z83" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA83" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11047,13 +11047,13 @@
         <v>82</v>
       </c>
       <c r="D84" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E84" s="41" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F84" s="44" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G84" s="46" t="s">
         <v>9</v>
@@ -11116,13 +11116,13 @@
         <v>Key-DOC-84</v>
       </c>
       <c r="X84" s="60" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Y84" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z84" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA84" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11140,13 +11140,13 @@
         <v>82</v>
       </c>
       <c r="D85" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E85" s="41" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F85" s="44" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G85" s="46" t="s">
         <v>9</v>
@@ -11209,13 +11209,13 @@
         <v>Key-DOC-85</v>
       </c>
       <c r="X85" s="60" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Y85" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z85" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA85" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11233,13 +11233,13 @@
         <v>82</v>
       </c>
       <c r="D86" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E86" s="41" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F86" s="44" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G86" s="46" t="s">
         <v>9</v>
@@ -11302,13 +11302,13 @@
         <v>Key-DOC-86</v>
       </c>
       <c r="X86" s="60" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Y86" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z86" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA86" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11326,13 +11326,13 @@
         <v>82</v>
       </c>
       <c r="D87" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E87" s="41" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F87" s="44" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G87" s="46" t="s">
         <v>9</v>
@@ -11395,13 +11395,13 @@
         <v>Key-DOC-87</v>
       </c>
       <c r="X87" s="60" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Y87" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z87" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA87" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11419,13 +11419,13 @@
         <v>82</v>
       </c>
       <c r="D88" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E88" s="41" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F88" s="44" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G88" s="46" t="s">
         <v>9</v>
@@ -11488,13 +11488,13 @@
         <v>Key-DOC-88</v>
       </c>
       <c r="X88" s="60" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Y88" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z88" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA88" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11512,13 +11512,13 @@
         <v>82</v>
       </c>
       <c r="D89" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E89" s="41" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F89" s="44" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G89" s="46" t="s">
         <v>9</v>
@@ -11581,13 +11581,13 @@
         <v>Key-DOC-89</v>
       </c>
       <c r="X89" s="60" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Y89" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z89" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA89" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11605,10 +11605,10 @@
         <v>82</v>
       </c>
       <c r="D90" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E90" s="41" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F90" s="44" t="s">
         <v>154</v>
@@ -11674,13 +11674,13 @@
         <v>Key-DOC-90</v>
       </c>
       <c r="X90" s="60" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y90" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z90" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA90" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11698,10 +11698,10 @@
         <v>82</v>
       </c>
       <c r="D91" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E91" s="41" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F91" s="44" t="s">
         <v>146</v>
@@ -11767,13 +11767,13 @@
         <v>Key-DOC-91</v>
       </c>
       <c r="X91" s="60" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y91" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z91" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA91" s="49" t="str">
         <f t="shared" si="33"/>
@@ -11791,13 +11791,13 @@
         <v>82</v>
       </c>
       <c r="D92" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E92" s="41" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F92" s="44" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G92" s="46" t="s">
         <v>9</v>
@@ -11860,13 +11860,13 @@
         <v>Key-DOC-92</v>
       </c>
       <c r="X92" s="60" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y92" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z92" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA92" s="49" t="str">
         <f t="shared" ref="AA92" si="44">_xlfn.TRANSLATE(P92,"pt","en")</f>
@@ -11884,10 +11884,10 @@
         <v>82</v>
       </c>
       <c r="D93" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E93" s="41" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F93" s="44" t="s">
         <v>147</v>
@@ -11953,13 +11953,13 @@
         <v>Key-DOC-93</v>
       </c>
       <c r="X93" s="60" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Y93" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z93" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA93" s="49" t="str">
         <f t="shared" ref="AA93:AA94" si="45">_xlfn.TRANSLATE(P93,"pt","en")</f>
@@ -11977,13 +11977,13 @@
         <v>82</v>
       </c>
       <c r="D94" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E94" s="41" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F94" s="44" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G94" s="46" t="s">
         <v>9</v>
@@ -12046,13 +12046,13 @@
         <v>Key-DOC-94</v>
       </c>
       <c r="X94" s="60" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Y94" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z94" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA94" s="49" t="str">
         <f t="shared" si="45"/>
@@ -12070,13 +12070,13 @@
         <v>82</v>
       </c>
       <c r="D95" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E95" s="41" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F95" s="44" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G95" s="46" t="s">
         <v>9</v>
@@ -12139,13 +12139,13 @@
         <v>Key-DOC-95</v>
       </c>
       <c r="X95" s="60" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Y95" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z95" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA95" s="49" t="str">
         <f t="shared" si="33"/>
@@ -12163,13 +12163,13 @@
         <v>82</v>
       </c>
       <c r="D96" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E96" s="41" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F96" s="44" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G96" s="46" t="s">
         <v>9</v>
@@ -12232,13 +12232,13 @@
         <v>Key-DOC-96</v>
       </c>
       <c r="X96" s="60" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Y96" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z96" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA96" s="49" t="str">
         <f t="shared" si="33"/>
@@ -12256,13 +12256,13 @@
         <v>82</v>
       </c>
       <c r="D97" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E97" s="41" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F97" s="44" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G97" s="46" t="s">
         <v>9</v>
@@ -12325,13 +12325,13 @@
         <v>Key-DOC-97</v>
       </c>
       <c r="X97" s="60" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y97" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z97" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA97" s="49" t="str">
         <f t="shared" ref="AA97" si="46">_xlfn.TRANSLATE(P97,"pt","en")</f>
@@ -12349,13 +12349,13 @@
         <v>82</v>
       </c>
       <c r="D98" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E98" s="41" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F98" s="44" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G98" s="46" t="s">
         <v>9</v>
@@ -12418,13 +12418,13 @@
         <v>Key-DOC-98</v>
       </c>
       <c r="X98" s="60" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y98" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z98" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA98" s="49" t="str">
         <f t="shared" ref="AA98" si="47">_xlfn.TRANSLATE(P98,"pt","en")</f>
@@ -12442,13 +12442,13 @@
         <v>82</v>
       </c>
       <c r="D99" s="42" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E99" s="41" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F99" s="44" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G99" s="46" t="s">
         <v>9</v>
@@ -12511,13 +12511,13 @@
         <v>Key-DOC-99</v>
       </c>
       <c r="X99" s="60" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y99" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z99" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA99" s="49" t="str">
         <f t="shared" si="33"/>
@@ -12535,13 +12535,13 @@
         <v>82</v>
       </c>
       <c r="D100" s="42" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E100" s="41" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F100" s="44" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G100" s="46" t="s">
         <v>9</v>
@@ -12604,13 +12604,13 @@
         <v>Key-DOC-100</v>
       </c>
       <c r="X100" s="60" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y100" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z100" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA100" s="49" t="str">
         <f t="shared" si="33"/>
@@ -12628,13 +12628,13 @@
         <v>82</v>
       </c>
       <c r="D101" s="42" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E101" s="41" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F101" s="44" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G101" s="46" t="s">
         <v>9</v>
@@ -12697,13 +12697,13 @@
         <v>Key-DOC-101</v>
       </c>
       <c r="X101" s="60" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Y101" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z101" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA101" s="49" t="str">
         <f t="shared" si="33"/>
@@ -12721,13 +12721,13 @@
         <v>82</v>
       </c>
       <c r="D102" s="42" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E102" s="41" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F102" s="44" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G102" s="46" t="s">
         <v>9</v>
@@ -12790,13 +12790,13 @@
         <v>Key-DOC-102</v>
       </c>
       <c r="X102" s="60" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Y102" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z102" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA102" s="49" t="str">
         <f t="shared" si="33"/>
@@ -12814,13 +12814,13 @@
         <v>82</v>
       </c>
       <c r="D103" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E103" s="41" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F103" s="44" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G103" s="46" t="s">
         <v>9</v>
@@ -12883,13 +12883,13 @@
         <v>Key-DOC-103</v>
       </c>
       <c r="X103" s="60" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y103" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z103" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA103" s="49" t="str">
         <f t="shared" si="33"/>
@@ -12907,13 +12907,13 @@
         <v>82</v>
       </c>
       <c r="D104" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E104" s="41" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F104" s="44" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G104" s="46" t="s">
         <v>9</v>
@@ -12976,13 +12976,13 @@
         <v>Key-DOC-104</v>
       </c>
       <c r="X104" s="60" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y104" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z104" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA104" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13000,13 +13000,13 @@
         <v>82</v>
       </c>
       <c r="D105" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E105" s="41" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F105" s="44" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G105" s="46" t="s">
         <v>9</v>
@@ -13069,13 +13069,13 @@
         <v>Key-DOC-105</v>
       </c>
       <c r="X105" s="60" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Y105" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z105" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA105" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13093,13 +13093,13 @@
         <v>82</v>
       </c>
       <c r="D106" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E106" s="41" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F106" s="44" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G106" s="46" t="s">
         <v>9</v>
@@ -13162,13 +13162,13 @@
         <v>Key-DOC-106</v>
       </c>
       <c r="X106" s="60" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Y106" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z106" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA106" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13186,13 +13186,13 @@
         <v>82</v>
       </c>
       <c r="D107" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E107" s="41" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F107" s="44" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G107" s="46" t="s">
         <v>9</v>
@@ -13255,13 +13255,13 @@
         <v>Key-DOC-107</v>
       </c>
       <c r="X107" s="60" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y107" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z107" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA107" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13279,13 +13279,13 @@
         <v>82</v>
       </c>
       <c r="D108" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E108" s="41" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F108" s="44" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G108" s="46" t="s">
         <v>9</v>
@@ -13348,13 +13348,13 @@
         <v>Key-DOC-108</v>
       </c>
       <c r="X108" s="60" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Y108" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z108" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA108" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13372,13 +13372,13 @@
         <v>82</v>
       </c>
       <c r="D109" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E109" s="41" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F109" s="44" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G109" s="46" t="s">
         <v>9</v>
@@ -13441,13 +13441,13 @@
         <v>Key-DOC-109</v>
       </c>
       <c r="X109" s="60" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y109" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z109" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA109" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13465,10 +13465,10 @@
         <v>82</v>
       </c>
       <c r="D110" s="42" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E110" s="41" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F110" s="44" t="s">
         <v>167</v>
@@ -13534,13 +13534,13 @@
         <v>Key-DOC-110</v>
       </c>
       <c r="X110" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Y110" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z110" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA110" s="49" t="str">
         <f t="shared" ref="AA110" si="55">_xlfn.TRANSLATE(P110,"pt","en")</f>
@@ -13558,13 +13558,13 @@
         <v>82</v>
       </c>
       <c r="D111" s="42" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E111" s="41" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F111" s="44" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G111" s="46" t="s">
         <v>9</v>
@@ -13627,13 +13627,13 @@
         <v>Key-DOC-111</v>
       </c>
       <c r="X111" s="60" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y111" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z111" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA111" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13651,10 +13651,10 @@
         <v>82</v>
       </c>
       <c r="D112" s="42" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E112" s="41" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F112" s="44" t="s">
         <v>200</v>
@@ -13720,13 +13720,13 @@
         <v>Key-DOC-112</v>
       </c>
       <c r="X112" s="60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Y112" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z112" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA112" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13744,13 +13744,13 @@
         <v>82</v>
       </c>
       <c r="D113" s="42" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E113" s="41" t="s">
+        <v>534</v>
+      </c>
+      <c r="F113" s="44" t="s">
         <v>535</v>
-      </c>
-      <c r="F113" s="44" t="s">
-        <v>536</v>
       </c>
       <c r="G113" s="46" t="s">
         <v>9</v>
@@ -13813,13 +13813,13 @@
         <v>Key-DOC-113</v>
       </c>
       <c r="X113" s="60" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Y113" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z113" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA113" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13837,13 +13837,13 @@
         <v>82</v>
       </c>
       <c r="D114" s="42" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E114" s="41" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F114" s="44" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G114" s="46" t="s">
         <v>9</v>
@@ -13906,13 +13906,13 @@
         <v>Key-DOC-114</v>
       </c>
       <c r="X114" s="60" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Y114" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z114" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA114" s="49" t="str">
         <f t="shared" si="33"/>
@@ -13930,13 +13930,13 @@
         <v>82</v>
       </c>
       <c r="D115" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E115" s="43" t="s">
         <v>184</v>
       </c>
       <c r="F115" s="44" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G115" s="46" t="s">
         <v>9</v>
@@ -13999,13 +13999,13 @@
         <v>Key-DOC-115</v>
       </c>
       <c r="X115" s="60" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y115" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z115" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA115" s="49" t="str">
         <f>_xlfn.TRANSLATE(P115,"pt","en")</f>
@@ -14023,13 +14023,13 @@
         <v>82</v>
       </c>
       <c r="D116" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E116" s="43" t="s">
         <v>184</v>
       </c>
       <c r="F116" s="44" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G116" s="46" t="s">
         <v>9</v>
@@ -14092,13 +14092,13 @@
         <v>Key-DOC-116</v>
       </c>
       <c r="X116" s="60" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Y116" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z116" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA116" s="49" t="str">
         <f t="shared" ref="AA116" si="56">_xlfn.TRANSLATE(P116,"pt","en")</f>
@@ -14116,13 +14116,13 @@
         <v>82</v>
       </c>
       <c r="D117" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E117" s="41" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F117" s="44" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G117" s="46" t="s">
         <v>9</v>
@@ -14185,13 +14185,13 @@
         <v>Key-DOC-117</v>
       </c>
       <c r="X117" s="60" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Y117" s="61" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Z117" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA117" s="49" t="str">
         <f t="shared" ref="AA117:AA118" si="57">_xlfn.TRANSLATE(P117,"pt","en")</f>
@@ -14209,13 +14209,13 @@
         <v>82</v>
       </c>
       <c r="D118" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E118" s="41" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F118" s="44" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G118" s="46" t="s">
         <v>9</v>
@@ -14278,13 +14278,13 @@
         <v>Key-DOC-118</v>
       </c>
       <c r="X118" s="60" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Y118" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z118" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA118" s="49" t="str">
         <f t="shared" si="57"/>
@@ -14302,13 +14302,13 @@
         <v>82</v>
       </c>
       <c r="D119" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E119" s="41" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F119" s="44" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G119" s="46" t="s">
         <v>9</v>
@@ -14371,13 +14371,13 @@
         <v>Key-DOC-119</v>
       </c>
       <c r="X119" s="60" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Y119" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z119" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA119" s="49" t="str">
         <f t="shared" si="33"/>
@@ -14395,13 +14395,13 @@
         <v>82</v>
       </c>
       <c r="D120" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E120" s="41" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F120" s="44" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G120" s="46" t="s">
         <v>9</v>
@@ -14464,13 +14464,13 @@
         <v>Key-DOC-120</v>
       </c>
       <c r="X120" s="60" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Y120" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z120" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA120" s="49" t="str">
         <f t="shared" si="33"/>
@@ -14488,13 +14488,13 @@
         <v>82</v>
       </c>
       <c r="D121" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E121" s="41" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F121" s="44" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G121" s="46" t="s">
         <v>9</v>
@@ -14557,13 +14557,13 @@
         <v>Key-DOC-121</v>
       </c>
       <c r="X121" s="60" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Y121" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z121" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA121" s="49" t="str">
         <f t="shared" si="33"/>
@@ -14581,13 +14581,13 @@
         <v>82</v>
       </c>
       <c r="D122" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E122" s="41" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F122" s="44" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G122" s="46" t="s">
         <v>9</v>
@@ -14650,13 +14650,13 @@
         <v>Key-DOC-122</v>
       </c>
       <c r="X122" s="60" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Y122" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z122" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA122" s="49" t="str">
         <f t="shared" si="33"/>
@@ -14674,13 +14674,13 @@
         <v>82</v>
       </c>
       <c r="D123" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E123" s="41" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F123" s="44" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G123" s="46" t="s">
         <v>9</v>
@@ -14743,13 +14743,13 @@
         <v>Key-DOC-123</v>
       </c>
       <c r="X123" s="60" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y123" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z123" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA123" s="49" t="str">
         <f t="shared" si="33"/>
@@ -14767,13 +14767,13 @@
         <v>82</v>
       </c>
       <c r="D124" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E124" s="41" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F124" s="44" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G124" s="46" t="s">
         <v>9</v>
@@ -14836,13 +14836,13 @@
         <v>Key-DOC-124</v>
       </c>
       <c r="X124" s="60" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y124" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z124" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA124" s="49" t="str">
         <f t="shared" si="33"/>
@@ -14860,13 +14860,13 @@
         <v>82</v>
       </c>
       <c r="D125" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E125" s="41" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F125" s="44" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G125" s="46" t="s">
         <v>9</v>
@@ -14929,13 +14929,13 @@
         <v>Key-DOC-125</v>
       </c>
       <c r="X125" s="60" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y125" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z125" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA125" s="49" t="str">
         <f t="shared" si="33"/>
@@ -14953,13 +14953,13 @@
         <v>82</v>
       </c>
       <c r="D126" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E126" s="41" t="s">
+        <v>541</v>
+      </c>
+      <c r="F126" s="44" t="s">
         <v>542</v>
-      </c>
-      <c r="F126" s="44" t="s">
-        <v>543</v>
       </c>
       <c r="G126" s="46" t="s">
         <v>9</v>
@@ -15022,13 +15022,13 @@
         <v>Key-DOC-126</v>
       </c>
       <c r="X126" s="60" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Y126" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z126" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA126" s="49" t="str">
         <f t="shared" si="33"/>
@@ -15046,10 +15046,10 @@
         <v>82</v>
       </c>
       <c r="D127" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E127" s="41" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F127" s="44" t="s">
         <v>177</v>
@@ -15115,13 +15115,13 @@
         <v>Key-DOC-127</v>
       </c>
       <c r="X127" s="60" t="s">
+        <v>433</v>
+      </c>
+      <c r="Y127" s="61" t="s">
+        <v>326</v>
+      </c>
+      <c r="Z127" s="58" t="s">
         <v>434</v>
-      </c>
-      <c r="Y127" s="61" t="s">
-        <v>327</v>
-      </c>
-      <c r="Z127" s="58" t="s">
-        <v>435</v>
       </c>
       <c r="AA127" s="49" t="str">
         <f t="shared" ref="AA127:AA129" si="71">_xlfn.TRANSLATE(P127,"pt","en")</f>
@@ -15139,13 +15139,13 @@
         <v>82</v>
       </c>
       <c r="D128" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E128" s="41" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F128" s="44" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G128" s="46" t="s">
         <v>9</v>
@@ -15179,7 +15179,7 @@
         <v>Etiqueta Parede</v>
       </c>
       <c r="P128" s="57" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="Q128" s="49" t="str">
         <f t="shared" si="34"/>
@@ -15208,13 +15208,13 @@
         <v>Key-DOC-128</v>
       </c>
       <c r="X128" s="60" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Y128" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z128" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA128" s="49" t="str">
         <f t="shared" si="71"/>
@@ -15232,13 +15232,13 @@
         <v>82</v>
       </c>
       <c r="D129" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E129" s="41" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F129" s="44" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G129" s="46" t="s">
         <v>9</v>
@@ -15272,7 +15272,7 @@
         <v>Etiqueta Porta</v>
       </c>
       <c r="P129" s="57" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Q129" s="49" t="str">
         <f t="shared" si="34"/>
@@ -15301,13 +15301,13 @@
         <v>Key-DOC-129</v>
       </c>
       <c r="X129" s="60" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="Y129" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z129" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA129" s="49" t="str">
         <f t="shared" si="71"/>
@@ -15325,13 +15325,13 @@
         <v>82</v>
       </c>
       <c r="D130" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E130" s="41" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F130" s="44" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G130" s="46" t="s">
         <v>9</v>
@@ -15365,7 +15365,7 @@
         <v>Etiqueta Janela</v>
       </c>
       <c r="P130" s="57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="Q130" s="49" t="str">
         <f t="shared" si="34"/>
@@ -15394,13 +15394,13 @@
         <v>Key-DOC-130</v>
       </c>
       <c r="X130" s="60" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="Y130" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z130" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA130" s="49" t="str">
         <f t="shared" si="33"/>
@@ -15418,10 +15418,10 @@
         <v>82</v>
       </c>
       <c r="D131" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="E131" s="41" t="s">
         <v>588</v>
-      </c>
-      <c r="E131" s="41" t="s">
-        <v>589</v>
       </c>
       <c r="F131" s="44" t="s">
         <v>261</v>
@@ -15458,7 +15458,7 @@
         <v>Domínio Público</v>
       </c>
       <c r="P131" s="57" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Q131" s="49" t="str">
         <f t="shared" si="34"/>
@@ -15493,7 +15493,7 @@
         <v>9</v>
       </c>
       <c r="Z131" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA131" s="49" t="str">
         <f t="shared" ref="AA131" si="77">_xlfn.TRANSLATE(P131,"pt","en")</f>
@@ -15511,13 +15511,13 @@
         <v>82</v>
       </c>
       <c r="D132" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="E132" s="41" t="s">
         <v>588</v>
       </c>
-      <c r="E132" s="41" t="s">
+      <c r="F132" s="44" t="s">
         <v>589</v>
-      </c>
-      <c r="F132" s="44" t="s">
-        <v>590</v>
       </c>
       <c r="G132" s="46" t="s">
         <v>9</v>
@@ -15586,7 +15586,7 @@
         <v>9</v>
       </c>
       <c r="Z132" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA132" s="49" t="str">
         <f t="shared" si="33"/>
@@ -15604,10 +15604,10 @@
         <v>82</v>
       </c>
       <c r="D133" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="E133" s="41" t="s">
         <v>588</v>
-      </c>
-      <c r="E133" s="41" t="s">
-        <v>589</v>
       </c>
       <c r="F133" s="44" t="s">
         <v>260</v>
@@ -15679,7 +15679,7 @@
         <v>9</v>
       </c>
       <c r="Z133" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA133" s="49" t="str">
         <f t="shared" si="33"/>
@@ -15697,10 +15697,10 @@
         <v>82</v>
       </c>
       <c r="D134" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="E134" s="41" t="s">
         <v>588</v>
-      </c>
-      <c r="E134" s="41" t="s">
-        <v>589</v>
       </c>
       <c r="F134" s="44" t="s">
         <v>246</v>
@@ -15772,7 +15772,7 @@
         <v>9</v>
       </c>
       <c r="Z134" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA134" s="49" t="str">
         <f t="shared" si="33"/>
@@ -15790,7 +15790,7 @@
         <v>82</v>
       </c>
       <c r="D135" s="42" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E135" s="41" t="s">
         <v>279</v>
@@ -15865,7 +15865,7 @@
         <v>9</v>
       </c>
       <c r="Z135" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA135" s="49" t="str">
         <f t="shared" si="33"/>
@@ -15883,7 +15883,7 @@
         <v>82</v>
       </c>
       <c r="D136" s="42" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E136" s="41" t="s">
         <v>279</v>
@@ -15958,7 +15958,7 @@
         <v>9</v>
       </c>
       <c r="Z136" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA136" s="49" t="str">
         <f t="shared" si="33"/>
@@ -15976,7 +15976,7 @@
         <v>82</v>
       </c>
       <c r="D137" s="42" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E137" s="41" t="s">
         <v>279</v>
@@ -16051,7 +16051,7 @@
         <v>9</v>
       </c>
       <c r="Z137" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA137" s="49" t="str">
         <f t="shared" si="33"/>
@@ -16069,13 +16069,13 @@
         <v>82</v>
       </c>
       <c r="D138" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E138" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F138" s="44" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G138" s="46" t="s">
         <v>9</v>
@@ -16109,7 +16109,7 @@
         <v>Guia</v>
       </c>
       <c r="P138" s="57" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q138" s="49" t="str">
         <f t="shared" si="34"/>
@@ -16144,7 +16144,7 @@
         <v>9</v>
       </c>
       <c r="Z138" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA138" s="49" t="str">
         <f t="shared" ref="AA138:AA145" si="78">_xlfn.TRANSLATE(P138,"pt","en")</f>
@@ -16162,13 +16162,13 @@
         <v>82</v>
       </c>
       <c r="D139" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E139" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F139" s="44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G139" s="46" t="s">
         <v>9</v>
@@ -16202,7 +16202,7 @@
         <v>Manual</v>
       </c>
       <c r="P139" s="57" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q139" s="49" t="str">
         <f t="shared" si="34"/>
@@ -16237,7 +16237,7 @@
         <v>9</v>
       </c>
       <c r="Z139" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA139" s="49" t="str">
         <f t="shared" si="78"/>
@@ -16255,13 +16255,13 @@
         <v>82</v>
       </c>
       <c r="D140" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E140" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F140" s="44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G140" s="46" t="s">
         <v>9</v>
@@ -16295,7 +16295,7 @@
         <v>Livro</v>
       </c>
       <c r="P140" s="57" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q140" s="49" t="str">
         <f t="shared" si="34"/>
@@ -16330,7 +16330,7 @@
         <v>9</v>
       </c>
       <c r="Z140" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA140" s="49" t="str">
         <f t="shared" si="78"/>
@@ -16348,13 +16348,13 @@
         <v>82</v>
       </c>
       <c r="D141" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E141" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F141" s="44" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G141" s="46" t="s">
         <v>9</v>
@@ -16388,7 +16388,7 @@
         <v>Treinamento</v>
       </c>
       <c r="P141" s="57" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q141" s="49" t="str">
         <f t="shared" si="34"/>
@@ -16423,7 +16423,7 @@
         <v>9</v>
       </c>
       <c r="Z141" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA141" s="49" t="str">
         <f t="shared" si="78"/>
@@ -16441,13 +16441,13 @@
         <v>82</v>
       </c>
       <c r="D142" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E142" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F142" s="44" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G142" s="46" t="s">
         <v>9</v>
@@ -16481,7 +16481,7 @@
         <v>Normativa</v>
       </c>
       <c r="P142" s="57" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q142" s="49" t="str">
         <f t="shared" si="34"/>
@@ -16516,7 +16516,7 @@
         <v>9</v>
       </c>
       <c r="Z142" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA142" s="49" t="str">
         <f t="shared" si="78"/>
@@ -16534,13 +16534,13 @@
         <v>82</v>
       </c>
       <c r="D143" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E143" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F143" s="44" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G143" s="46" t="s">
         <v>9</v>
@@ -16574,7 +16574,7 @@
         <v>Apresentação</v>
       </c>
       <c r="P143" s="57" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q143" s="49" t="str">
         <f t="shared" si="34"/>
@@ -16609,7 +16609,7 @@
         <v>9</v>
       </c>
       <c r="Z143" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA143" s="49" t="str">
         <f t="shared" si="78"/>
@@ -16627,13 +16627,13 @@
         <v>82</v>
       </c>
       <c r="D144" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E144" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="F144" s="44" t="s">
         <v>299</v>
-      </c>
-      <c r="F144" s="44" t="s">
-        <v>300</v>
       </c>
       <c r="G144" s="46" t="s">
         <v>9</v>
@@ -16667,7 +16667,7 @@
         <v>Fichário</v>
       </c>
       <c r="P144" s="57" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q144" s="49" t="str">
         <f t="shared" si="34"/>
@@ -16702,7 +16702,7 @@
         <v>9</v>
       </c>
       <c r="Z144" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA144" s="49" t="str">
         <f t="shared" si="78"/>
@@ -16720,13 +16720,13 @@
         <v>82</v>
       </c>
       <c r="D145" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E145" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F145" s="44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G145" s="46" t="s">
         <v>9</v>
@@ -16760,7 +16760,7 @@
         <v>Formulário</v>
       </c>
       <c r="P145" s="57" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q145" s="49" t="str">
         <f t="shared" ref="Q145" si="84">_xlfn.TRANSLATE(P145,"pt","es")</f>
@@ -16795,7 +16795,7 @@
         <v>9</v>
       </c>
       <c r="Z145" s="58" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA145" s="49" t="str">
         <f t="shared" si="78"/>
@@ -17017,7 +17017,7 @@
         <v>146</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -17131,10 +17131,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>9</v>
@@ -17170,7 +17170,7 @@
         <v>16</v>
       </c>
       <c r="O2" s="30" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="P2" s="31" t="s">
         <v>9</v>
@@ -17202,16 +17202,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>9</v>
@@ -17241,13 +17241,13 @@
         <v>16</v>
       </c>
       <c r="O3" s="30" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="P3" s="31" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q3" s="21" t="s">
         <v>654</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>655</v>
       </c>
       <c r="R3" s="31" t="s">
         <v>9</v>
@@ -17273,16 +17273,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>9</v>
@@ -17312,13 +17312,13 @@
         <v>16</v>
       </c>
       <c r="O4" s="30" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="P4" s="31" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q4" s="21" t="s">
         <v>654</v>
-      </c>
-      <c r="Q4" s="21" t="s">
-        <v>655</v>
       </c>
       <c r="R4" s="31" t="s">
         <v>9</v>
@@ -17344,16 +17344,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>9</v>
@@ -17383,13 +17383,13 @@
         <v>16</v>
       </c>
       <c r="O5" s="30" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="P5" s="31" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q5" s="21" t="s">
         <v>654</v>
-      </c>
-      <c r="Q5" s="21" t="s">
-        <v>655</v>
       </c>
       <c r="R5" s="31" t="s">
         <v>9</v>
@@ -17415,16 +17415,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>9</v>
@@ -17454,13 +17454,13 @@
         <v>16</v>
       </c>
       <c r="O6" s="30" t="s">
+        <v>652</v>
+      </c>
+      <c r="P6" s="31" t="s">
         <v>653</v>
       </c>
-      <c r="P6" s="31" t="s">
+      <c r="Q6" s="21" t="s">
         <v>654</v>
-      </c>
-      <c r="Q6" s="21" t="s">
-        <v>655</v>
       </c>
       <c r="R6" s="31" t="s">
         <v>9</v>
@@ -17486,16 +17486,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>656</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>657</v>
-      </c>
       <c r="D7" s="19" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F7" s="19" t="s">
         <v>9</v>
@@ -17525,25 +17525,25 @@
         <v>16</v>
       </c>
       <c r="O7" s="30" t="s">
+        <v>659</v>
+      </c>
+      <c r="P7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="R7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="31" t="s">
         <v>660</v>
       </c>
-      <c r="P7" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="R7" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="T7" s="31" t="s">
+      <c r="U7" s="21" t="s">
         <v>661</v>
-      </c>
-      <c r="U7" s="21" t="s">
-        <v>662</v>
       </c>
       <c r="V7" s="31" t="s">
         <v>9</v>
@@ -17563,16 +17563,16 @@
         <v>154</v>
       </c>
       <c r="D8" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F8" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H8" s="19" t="s">
         <v>9</v>
@@ -17596,7 +17596,7 @@
         <v>16</v>
       </c>
       <c r="O8" s="30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P8" s="31" t="s">
         <v>207</v>
@@ -17605,7 +17605,7 @@
         <v>208</v>
       </c>
       <c r="R8" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S8" s="21" t="s">
         <v>226</v>
@@ -17634,16 +17634,16 @@
         <v>154</v>
       </c>
       <c r="D9" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E9" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F9" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>9</v>
@@ -17667,7 +17667,7 @@
         <v>16</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P9" s="31" t="s">
         <v>207</v>
@@ -17676,7 +17676,7 @@
         <v>208</v>
       </c>
       <c r="R9" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S9" s="21" t="s">
         <v>227</v>
@@ -17705,16 +17705,16 @@
         <v>154</v>
       </c>
       <c r="D10" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F10" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H10" s="19" t="s">
         <v>9</v>
@@ -17738,7 +17738,7 @@
         <v>16</v>
       </c>
       <c r="O10" s="30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P10" s="31" t="s">
         <v>207</v>
@@ -17747,7 +17747,7 @@
         <v>208</v>
       </c>
       <c r="R10" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S10" s="21" t="s">
         <v>228</v>
@@ -17776,16 +17776,16 @@
         <v>154</v>
       </c>
       <c r="D11" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E11" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F11" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H11" s="19" t="s">
         <v>9</v>
@@ -17809,7 +17809,7 @@
         <v>16</v>
       </c>
       <c r="O11" s="30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P11" s="31" t="s">
         <v>207</v>
@@ -17818,7 +17818,7 @@
         <v>208</v>
       </c>
       <c r="R11" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S11" s="21" t="s">
         <v>229</v>
@@ -17847,16 +17847,16 @@
         <v>154</v>
       </c>
       <c r="D12" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F12" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H12" s="19" t="s">
         <v>9</v>
@@ -17880,7 +17880,7 @@
         <v>16</v>
       </c>
       <c r="O12" s="30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P12" s="31" t="s">
         <v>207</v>
@@ -17889,7 +17889,7 @@
         <v>208</v>
       </c>
       <c r="R12" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S12" s="21" t="s">
         <v>230</v>
@@ -17918,16 +17918,16 @@
         <v>154</v>
       </c>
       <c r="D13" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F13" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H13" s="19" t="s">
         <v>9</v>
@@ -17951,7 +17951,7 @@
         <v>16</v>
       </c>
       <c r="O13" s="30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P13" s="31" t="s">
         <v>207</v>
@@ -17960,7 +17960,7 @@
         <v>208</v>
       </c>
       <c r="R13" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S13" s="21" t="s">
         <v>231</v>
@@ -17989,16 +17989,16 @@
         <v>147</v>
       </c>
       <c r="D14" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E14" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F14" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H14" s="19" t="s">
         <v>9</v>
@@ -18031,7 +18031,7 @@
         <v>215</v>
       </c>
       <c r="R14" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S14" s="21" t="s">
         <v>218</v>
@@ -18060,16 +18060,16 @@
         <v>147</v>
       </c>
       <c r="D15" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E15" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F15" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H15" s="19" t="s">
         <v>9</v>
@@ -18102,7 +18102,7 @@
         <v>215</v>
       </c>
       <c r="R15" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S15" s="21" t="s">
         <v>219</v>
@@ -18131,16 +18131,16 @@
         <v>147</v>
       </c>
       <c r="D16" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E16" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F16" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H16" s="19" t="s">
         <v>9</v>
@@ -18173,7 +18173,7 @@
         <v>215</v>
       </c>
       <c r="R16" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S16" s="21" t="s">
         <v>220</v>
@@ -18202,16 +18202,16 @@
         <v>147</v>
       </c>
       <c r="D17" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E17" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F17" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H17" s="19" t="s">
         <v>9</v>
@@ -18244,7 +18244,7 @@
         <v>215</v>
       </c>
       <c r="R17" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S17" s="21" t="s">
         <v>221</v>
@@ -18273,16 +18273,16 @@
         <v>177</v>
       </c>
       <c r="D18" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F18" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>9</v>
@@ -18312,10 +18312,10 @@
         <v>207</v>
       </c>
       <c r="Q18" s="21" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="R18" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S18" s="21" t="s">
         <v>224</v>
@@ -18344,16 +18344,16 @@
         <v>177</v>
       </c>
       <c r="D19" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E19" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F19" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H19" s="19" t="s">
         <v>9</v>
@@ -18383,10 +18383,10 @@
         <v>207</v>
       </c>
       <c r="Q19" s="21" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="R19" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S19" s="21" t="s">
         <v>225</v>
@@ -18415,16 +18415,16 @@
         <v>177</v>
       </c>
       <c r="D20" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F20" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H20" s="19" t="s">
         <v>9</v>
@@ -18454,10 +18454,10 @@
         <v>207</v>
       </c>
       <c r="Q20" s="21" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R20" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S20" s="21" t="s">
         <v>240</v>
@@ -18486,16 +18486,16 @@
         <v>177</v>
       </c>
       <c r="D21" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E21" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F21" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H21" s="19" t="s">
         <v>9</v>
@@ -18525,10 +18525,10 @@
         <v>207</v>
       </c>
       <c r="Q21" s="21" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="R21" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S21" s="21" t="s">
         <v>241</v>
@@ -18557,16 +18557,16 @@
         <v>177</v>
       </c>
       <c r="D22" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F22" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H22" s="19" t="s">
         <v>9</v>
@@ -18596,10 +18596,10 @@
         <v>207</v>
       </c>
       <c r="Q22" s="21" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R22" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S22" s="21" t="s">
         <v>242</v>
@@ -18628,16 +18628,16 @@
         <v>177</v>
       </c>
       <c r="D23" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="E23" s="20" t="s">
-        <v>648</v>
-      </c>
       <c r="F23" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H23" s="19" t="s">
         <v>9</v>
@@ -18667,10 +18667,10 @@
         <v>207</v>
       </c>
       <c r="Q23" s="21" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="R23" s="31" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S23" s="21" t="s">
         <v>243</v>
@@ -18696,7 +18696,7 @@
         <v>255</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>9</v>
@@ -18767,7 +18767,7 @@
         <v>256</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>9</v>
@@ -18838,7 +18838,7 @@
         <v>244</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>9</v>
@@ -18906,7 +18906,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>261</v>
@@ -18945,7 +18945,7 @@
         <v>16</v>
       </c>
       <c r="O27" s="37" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="P27" s="31" t="s">
         <v>9</v>
@@ -19261,7 +19261,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>269</v>
@@ -19300,7 +19300,7 @@
         <v>16</v>
       </c>
       <c r="O32" s="37" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P32" s="31" t="s">
         <v>9</v>
@@ -19480,7 +19480,7 @@
         <v>270</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>288</v>
+        <v>665</v>
       </c>
       <c r="E35" s="20" t="s">
         <v>285</v>

--- a/Versão5/DOCU/Ontologia_DOCUM.xlsx
+++ b/Versão5/DOCU/Ontologia_DOCUM.xlsx
@@ -3224,7 +3224,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46213.80458877315</v>
+        <v>46214.346514699071</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>318</v>

--- a/Versão5/DOCU/Ontologia_DOCUM.xlsx
+++ b/Versão5/DOCU/Ontologia_DOCUM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\DOCU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A6DBB4-E722-4562-990E-640DE48AA26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9309847A-9477-4FE1-90EA-1FD252D1323B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3266" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3266" uniqueCount="662">
   <si>
     <t>Edição</t>
   </si>
@@ -2046,9 +2046,6 @@
     <t>é.quem.revogou</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -2056,6 +2053,12 @@
   </si>
   <si>
     <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Documentais</t>
   </si>
 </sst>
 </file>
@@ -2362,7 +2365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2525,7 +2528,6 @@
     <xf numFmtId="0" fontId="3" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2551,71 +2553,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2741,6 +2679,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3059,15 +3005,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3078,7 +3024,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -3089,7 +3035,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3100,7 +3046,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3111,7 +3057,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -3123,7 +3069,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -3135,7 +3081,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -3146,7 +3092,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -3157,7 +3103,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -3168,7 +3114,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -3179,7 +3125,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -3190,7 +3136,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -3201,7 +3147,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -3212,7 +3158,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -3223,7 +3169,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -3234,7 +3180,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -3245,7 +3191,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -3256,19 +3202,19 @@
         <v>317</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46216.375280671295</v>
+        <v>46243.519222106479</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -3279,7 +3225,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -3290,7 +3236,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -3301,7 +3247,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>35</v>
       </c>
@@ -3312,7 +3258,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>36</v>
       </c>
@@ -3323,7 +3269,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>315</v>
       </c>
@@ -3343,36 +3289,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BE914A-3965-4A61-9195-D2681A91581F}">
   <dimension ref="A1:AA145"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="63" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3828125" style="62" customWidth="1"/>
+    <col min="2" max="2" width="5.3046875" style="44" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="44" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="7.28515625" style="44" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" style="44" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" style="44" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="50.42578125" style="44" customWidth="1"/>
-    <col min="17" max="17" width="72.140625" style="44" customWidth="1"/>
-    <col min="18" max="18" width="5.28515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" style="44" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="44" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" style="44" customWidth="1"/>
+    <col min="4" max="4" width="12.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.84375" style="44" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.69140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="7.3046875" style="44" customWidth="1"/>
+    <col min="12" max="12" width="7.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.69140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.53515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="50.3828125" style="44" customWidth="1"/>
+    <col min="17" max="17" width="72.15234375" style="44" customWidth="1"/>
+    <col min="18" max="18" width="5.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.3046875" style="44" customWidth="1"/>
+    <col min="20" max="20" width="14.53515625" style="44" customWidth="1"/>
+    <col min="21" max="21" width="14.15234375" style="44" customWidth="1"/>
     <col min="22" max="22" width="7" style="44" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.42578125" style="44" customWidth="1"/>
+    <col min="23" max="23" width="8.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.3828125" style="44" customWidth="1"/>
     <col min="25" max="25" width="15" style="44" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="44" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="44"/>
+    <col min="26" max="26" width="5.15234375" style="44" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.69140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:27" ht="51.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="61" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="47" t="s">
@@ -3454,12 +3400,12 @@
         <v>313</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="56" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="45">
         <v>2</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C2" s="52" t="s">
         <v>432</v>
@@ -3468,7 +3414,7 @@
         <v>321</v>
       </c>
       <c r="E2" s="53" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F2" s="53" t="s">
         <v>320</v>
@@ -3508,7 +3454,7 @@
         <v>322</v>
       </c>
       <c r="Q2" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R2" s="43" t="s">
         <v>9</v>
@@ -3539,19 +3485,19 @@
         <v>9</v>
       </c>
       <c r="Z2" s="43" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AA2" s="43" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="56" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="45">
         <v>3</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C3" s="52" t="s">
         <v>432</v>
@@ -3560,7 +3506,7 @@
         <v>321</v>
       </c>
       <c r="E3" s="53" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F3" s="53" t="s">
         <v>433</v>
@@ -3600,7 +3546,7 @@
         <v>434</v>
       </c>
       <c r="Q3" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R3" s="43" t="s">
         <v>9</v>
@@ -3638,12 +3584,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="56" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="45">
         <v>4</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C4" s="52" t="s">
         <v>432</v>
@@ -3652,7 +3598,7 @@
         <v>321</v>
       </c>
       <c r="E4" s="53" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>435</v>
@@ -3692,7 +3638,7 @@
         <v>436</v>
       </c>
       <c r="Q4" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R4" s="43" t="s">
         <v>9</v>
@@ -3730,12 +3676,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="56" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="45">
         <v>5</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C5" s="52" t="s">
         <v>432</v>
@@ -3744,7 +3690,7 @@
         <v>321</v>
       </c>
       <c r="E5" s="53" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F5" s="53" t="s">
         <v>437</v>
@@ -3784,7 +3730,7 @@
         <v>438</v>
       </c>
       <c r="Q5" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R5" s="43" t="s">
         <v>9</v>
@@ -3822,12 +3768,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="56" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="45">
         <v>6</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C6" s="52" t="s">
         <v>432</v>
@@ -3836,7 +3782,7 @@
         <v>321</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F6" s="53" t="s">
         <v>439</v>
@@ -3876,7 +3822,7 @@
         <v>440</v>
       </c>
       <c r="Q6" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R6" s="43" t="s">
         <v>9</v>
@@ -3914,23 +3860,23 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="45">
         <v>7</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D7" s="56" t="s">
         <v>625</v>
       </c>
-      <c r="E7" s="57" t="s">
+      <c r="E7" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="57" t="s">
         <v>623</v>
       </c>
       <c r="G7" s="46" t="s">
@@ -3949,19 +3895,19 @@
         <v>9</v>
       </c>
       <c r="L7" s="54" t="str">
-        <f t="shared" ref="L3:L72" si="5">CONCATENATE("", C7)</f>
-        <v>Documental</v>
+        <f t="shared" ref="L7:L72" si="5">CONCATENATE("", C7)</f>
+        <v>Documentais</v>
       </c>
       <c r="M7" s="54" t="str">
-        <f t="shared" ref="M3:M72" si="6">CONCATENATE("", D7)</f>
+        <f t="shared" ref="M7:M72" si="6">CONCATENATE("", D7)</f>
         <v>Digitalizados</v>
       </c>
       <c r="N7" s="54" t="str">
-        <f t="shared" ref="N3:N72" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N7:N72" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
         <v>Elemento Digital</v>
       </c>
       <c r="O7" s="54" t="str">
-        <f t="shared" ref="O3:O72" si="8">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O7:O72" si="8">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
         <v>Arquivo</v>
       </c>
       <c r="P7" s="43" t="s">
@@ -3976,7 +3922,7 @@
       </c>
       <c r="S7" s="43" t="str">
         <f t="shared" ref="S7:U13" si="9">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T7" s="43" t="str">
         <f t="shared" si="9"/>
@@ -4007,23 +3953,23 @@
         <v>Defines a project file or default file of an application, it can be rvt, dwg, dgn, ifc, etc...</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="45">
         <v>8</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D8" s="56" t="s">
         <v>625</v>
       </c>
-      <c r="E8" s="57" t="s">
+      <c r="E8" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="57" t="s">
         <v>626</v>
       </c>
       <c r="G8" s="46" t="s">
@@ -4043,7 +3989,7 @@
       </c>
       <c r="L8" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M8" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4069,7 +4015,7 @@
       </c>
       <c r="S8" s="43" t="str">
         <f t="shared" ref="S8:S11" si="11">SUBSTITUTE(C8, "_", " ")</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T8" s="43" t="str">
         <f t="shared" ref="T8:T11" si="12">SUBSTITUTE(D8, "_", " ")</f>
@@ -4100,23 +4046,23 @@
         <v>Defines a file used as a template, prototype, template, can be rte, dwt, etc...</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="45">
         <v>9</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D9" s="56" t="s">
         <v>625</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="57" t="s">
         <v>627</v>
       </c>
       <c r="G9" s="46" t="s">
@@ -4136,7 +4082,7 @@
       </c>
       <c r="L9" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M9" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4162,7 +4108,7 @@
       </c>
       <c r="S9" s="43" t="str">
         <f t="shared" si="11"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T9" s="43" t="str">
         <f t="shared" si="12"/>
@@ -4193,23 +4139,23 @@
         <v>Defines a file of an application. It can be Autolisp, Python, C#, etc..</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="45">
         <v>10</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D10" s="56" t="s">
         <v>625</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="57" t="s">
         <v>629</v>
       </c>
       <c r="G10" s="46" t="s">
@@ -4229,7 +4175,7 @@
       </c>
       <c r="L10" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M10" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4255,7 +4201,7 @@
       </c>
       <c r="S10" s="43" t="str">
         <f t="shared" si="11"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T10" s="43" t="str">
         <f t="shared" si="12"/>
@@ -4286,23 +4232,23 @@
         <v>Defines a file used as a structured data receiver, it can be txt, xml, etc...</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="45">
         <v>11</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D11" s="56" t="s">
         <v>625</v>
       </c>
-      <c r="E11" s="57" t="s">
+      <c r="E11" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="57" t="s">
         <v>630</v>
       </c>
       <c r="G11" s="46" t="s">
@@ -4322,7 +4268,7 @@
       </c>
       <c r="L11" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M11" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4348,7 +4294,7 @@
       </c>
       <c r="S11" s="43" t="str">
         <f t="shared" si="11"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T11" s="43" t="str">
         <f t="shared" si="12"/>
@@ -4379,23 +4325,23 @@
         <v>Defines a file used as a receiver of unstructured data, can be pdf, doc, videos, etc...</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="45">
         <v>12</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D12" s="56" t="s">
         <v>625</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="57" t="s">
         <v>647</v>
       </c>
       <c r="G12" s="46" t="s">
@@ -4415,7 +4361,7 @@
       </c>
       <c r="L12" s="54" t="str">
         <f t="shared" ref="L12" si="16">CONCATENATE("", C12)</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M12" s="54" t="str">
         <f t="shared" ref="M12" si="17">CONCATENATE("", D12)</f>
@@ -4440,7 +4386,7 @@
       </c>
       <c r="S12" s="43" t="str">
         <f t="shared" si="9"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T12" s="43" t="str">
         <f t="shared" si="9"/>
@@ -4467,27 +4413,27 @@
         <v>431</v>
       </c>
       <c r="AA12" s="43" t="str">
-        <f t="shared" ref="AA2:AA12" si="20">_xlfn.TRANSLATE(P12,"pt","en")</f>
+        <f t="shared" ref="AA12" si="20">_xlfn.TRANSLATE(P12,"pt","en")</f>
         <v>Defines a digital library of elements for the project.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="45">
         <v>13</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D13" s="56" t="s">
         <v>557</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="58" t="s">
         <v>553</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="57" t="s">
         <v>555</v>
       </c>
       <c r="G13" s="46" t="s">
@@ -4507,7 +4453,7 @@
       </c>
       <c r="L13" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M13" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4533,7 +4479,7 @@
       </c>
       <c r="S13" s="43" t="str">
         <f t="shared" si="9"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T13" s="43" t="str">
         <f t="shared" si="9"/>
@@ -4550,10 +4496,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-13</v>
       </c>
-      <c r="X13" s="60" t="s">
+      <c r="X13" s="59" t="s">
         <v>326</v>
       </c>
-      <c r="Y13" s="61" t="s">
+      <c r="Y13" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z13" s="43" t="s">
@@ -4564,23 +4510,23 @@
         <v>Layout - Nodes</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="45">
         <v>14</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D14" s="56" t="s">
         <v>557</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="E14" s="58" t="s">
         <v>553</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="57" t="s">
         <v>554</v>
       </c>
       <c r="G14" s="46" t="s">
@@ -4600,7 +4546,7 @@
       </c>
       <c r="L14" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M14" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4626,7 +4572,7 @@
       </c>
       <c r="S14" s="43" t="str">
         <f t="shared" ref="S14:S45" si="23">SUBSTITUTE(C14, "_", " ")</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T14" s="43" t="str">
         <f t="shared" ref="T14:T77" si="24">SUBSTITUTE(D14, "_", " ")</f>
@@ -4643,10 +4589,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-14</v>
       </c>
-      <c r="X14" s="60" t="s">
+      <c r="X14" s="59" t="s">
         <v>327</v>
       </c>
-      <c r="Y14" s="61" t="s">
+      <c r="Y14" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z14" s="43" t="s">
@@ -4657,23 +4603,23 @@
         <v>Layout - Bases of the path</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="45">
         <v>15</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D15" s="56" t="s">
         <v>557</v>
       </c>
-      <c r="E15" s="59" t="s">
+      <c r="E15" s="58" t="s">
         <v>553</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="57" t="s">
         <v>454</v>
       </c>
       <c r="G15" s="46" t="s">
@@ -4693,7 +4639,7 @@
       </c>
       <c r="L15" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M15" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4719,7 +4665,7 @@
       </c>
       <c r="S15" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T15" s="43" t="str">
         <f t="shared" si="24"/>
@@ -4736,10 +4682,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-15</v>
       </c>
-      <c r="X15" s="60" t="s">
+      <c r="X15" s="59" t="s">
         <v>328</v>
       </c>
-      <c r="Y15" s="61" t="s">
+      <c r="Y15" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z15" s="43" t="s">
@@ -4750,23 +4696,23 @@
         <v>Layout - Bases of the pipe brought</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="45">
         <v>16</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D16" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="57" t="s">
         <v>455</v>
       </c>
       <c r="G16" s="46" t="s">
@@ -4786,7 +4732,7 @@
       </c>
       <c r="L16" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M16" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4812,7 +4758,7 @@
       </c>
       <c r="S16" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T16" s="43" t="str">
         <f t="shared" si="24"/>
@@ -4829,10 +4775,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-16</v>
       </c>
-      <c r="X16" s="60" t="s">
+      <c r="X16" s="59" t="s">
         <v>329</v>
       </c>
-      <c r="Y16" s="61" t="s">
+      <c r="Y16" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z16" s="43" t="s">
@@ -4843,23 +4789,23 @@
         <v>Callout Symbol</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="45">
         <v>17</v>
       </c>
       <c r="B17" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D17" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E17" s="59" t="s">
+      <c r="E17" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="F17" s="58" t="s">
+      <c r="F17" s="57" t="s">
         <v>456</v>
       </c>
       <c r="G17" s="46" t="s">
@@ -4879,7 +4825,7 @@
       </c>
       <c r="L17" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M17" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4905,7 +4851,7 @@
       </c>
       <c r="S17" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T17" s="43" t="str">
         <f t="shared" si="24"/>
@@ -4922,10 +4868,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-17</v>
       </c>
-      <c r="X17" s="60" t="s">
+      <c r="X17" s="59" t="s">
         <v>330</v>
       </c>
-      <c r="Y17" s="61" t="s">
+      <c r="Y17" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z17" s="43" t="s">
@@ -4936,23 +4882,23 @@
         <v>Call Detail Delimitation</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="45">
         <v>18</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D18" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="57" t="s">
         <v>457</v>
       </c>
       <c r="G18" s="46" t="s">
@@ -4972,7 +4918,7 @@
       </c>
       <c r="L18" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M18" s="54" t="str">
         <f t="shared" si="6"/>
@@ -4998,7 +4944,7 @@
       </c>
       <c r="S18" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T18" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5015,10 +4961,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-18</v>
       </c>
-      <c r="X18" s="60" t="s">
+      <c r="X18" s="59" t="s">
         <v>331</v>
       </c>
-      <c r="Y18" s="61" t="s">
+      <c r="Y18" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z18" s="43" t="s">
@@ -5029,23 +4975,23 @@
         <v>Callout Symbol - Head</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="45">
         <v>19</v>
       </c>
       <c r="B19" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D19" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E19" s="59" t="s">
+      <c r="E19" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="57" t="s">
         <v>458</v>
       </c>
       <c r="G19" s="46" t="s">
@@ -5065,7 +5011,7 @@
       </c>
       <c r="L19" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M19" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5091,7 +5037,7 @@
       </c>
       <c r="S19" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T19" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5108,10 +5054,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-19</v>
       </c>
-      <c r="X19" s="60" t="s">
+      <c r="X19" s="59" t="s">
         <v>332</v>
       </c>
-      <c r="Y19" s="61" t="s">
+      <c r="Y19" s="60" t="s">
         <v>445</v>
       </c>
       <c r="Z19" s="43" t="s">
@@ -5122,23 +5068,23 @@
         <v>Leader Symbol - Leader Line</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="45">
         <v>20</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C20" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D20" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="57" t="s">
         <v>459</v>
       </c>
       <c r="G20" s="46" t="s">
@@ -5158,7 +5104,7 @@
       </c>
       <c r="L20" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M20" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5184,7 +5130,7 @@
       </c>
       <c r="S20" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T20" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5201,10 +5147,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-20</v>
       </c>
-      <c r="X20" s="60" t="s">
+      <c r="X20" s="59" t="s">
         <v>333</v>
       </c>
-      <c r="Y20" s="61" t="s">
+      <c r="Y20" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z20" s="43" t="s">
@@ -5215,23 +5161,23 @@
         <v>Symbolic cloud of detail review</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="45">
         <v>21</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D21" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E21" s="59" t="s">
+      <c r="E21" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="57" t="s">
         <v>460</v>
       </c>
       <c r="G21" s="46" t="s">
@@ -5251,7 +5197,7 @@
       </c>
       <c r="L21" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M21" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5277,7 +5223,7 @@
       </c>
       <c r="S21" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T21" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5294,10 +5240,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-21</v>
       </c>
-      <c r="X21" s="60" t="s">
+      <c r="X21" s="59" t="s">
         <v>334</v>
       </c>
-      <c r="Y21" s="61" t="s">
+      <c r="Y21" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z21" s="43" t="s">
@@ -5308,23 +5254,23 @@
         <v>Symbolic Cloud of Detail Review - Textual Label or Tag</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="45">
         <v>22</v>
       </c>
       <c r="B22" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D22" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="57" t="s">
         <v>462</v>
       </c>
       <c r="G22" s="46" t="s">
@@ -5344,7 +5290,7 @@
       </c>
       <c r="L22" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M22" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5370,7 +5316,7 @@
       </c>
       <c r="S22" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T22" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5387,10 +5333,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-22</v>
       </c>
-      <c r="X22" s="60" t="s">
+      <c r="X22" s="59" t="s">
         <v>341</v>
       </c>
-      <c r="Y22" s="61" t="s">
+      <c r="Y22" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z22" s="43" t="s">
@@ -5401,23 +5347,23 @@
         <v>Section view</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="45">
         <v>23</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C23" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D23" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E23" s="59" t="s">
+      <c r="E23" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F23" s="58" t="s">
+      <c r="F23" s="57" t="s">
         <v>543</v>
       </c>
       <c r="G23" s="46" t="s">
@@ -5437,7 +5383,7 @@
       </c>
       <c r="L23" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M23" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5463,7 +5409,7 @@
       </c>
       <c r="S23" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T23" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5480,10 +5426,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-23</v>
       </c>
-      <c r="X23" s="60" t="s">
+      <c r="X23" s="59" t="s">
         <v>336</v>
       </c>
-      <c r="Y23" s="61" t="s">
+      <c r="Y23" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z23" s="43" t="s">
@@ -5494,23 +5440,23 @@
         <v>Cutting Symbol - Head</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="45">
         <v>24</v>
       </c>
       <c r="B24" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C24" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D24" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E24" s="59" t="s">
+      <c r="E24" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="58" t="s">
+      <c r="F24" s="57" t="s">
         <v>464</v>
       </c>
       <c r="G24" s="46" t="s">
@@ -5530,7 +5476,7 @@
       </c>
       <c r="L24" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M24" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5556,7 +5502,7 @@
       </c>
       <c r="S24" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T24" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5573,10 +5519,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-24</v>
       </c>
-      <c r="X24" s="60" t="s">
+      <c r="X24" s="59" t="s">
         <v>337</v>
       </c>
-      <c r="Y24" s="61" t="s">
+      <c r="Y24" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z24" s="43" t="s">
@@ -5587,23 +5533,23 @@
         <v>Cutting Symbol - Thin Lines of Head</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="45">
         <v>25</v>
       </c>
       <c r="B25" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C25" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D25" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E25" s="59" t="s">
+      <c r="E25" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F25" s="58" t="s">
+      <c r="F25" s="57" t="s">
         <v>461</v>
       </c>
       <c r="G25" s="46" t="s">
@@ -5623,7 +5569,7 @@
       </c>
       <c r="L25" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M25" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5649,7 +5595,7 @@
       </c>
       <c r="S25" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T25" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5666,10 +5612,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-25</v>
       </c>
-      <c r="X25" s="60" t="s">
+      <c r="X25" s="59" t="s">
         <v>335</v>
       </c>
-      <c r="Y25" s="61" t="s">
+      <c r="Y25" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z25" s="43" t="s">
@@ -5680,23 +5626,23 @@
         <v>Cutting Symbol - Midlines of the Head</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="45">
         <v>26</v>
       </c>
       <c r="B26" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D26" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E26" s="59" t="s">
+      <c r="E26" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F26" s="58" t="s">
+      <c r="F26" s="57" t="s">
         <v>463</v>
       </c>
       <c r="G26" s="46" t="s">
@@ -5716,7 +5662,7 @@
       </c>
       <c r="L26" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M26" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5742,7 +5688,7 @@
       </c>
       <c r="S26" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T26" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5759,10 +5705,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-26</v>
       </c>
-      <c r="X26" s="60" t="s">
+      <c r="X26" s="59" t="s">
         <v>338</v>
       </c>
-      <c r="Y26" s="61" t="s">
+      <c r="Y26" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z26" s="43" t="s">
@@ -5773,23 +5719,23 @@
         <v>Cutting Symbol - Thick Head Lines</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="45">
         <v>27</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C27" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D27" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E27" s="59" t="s">
+      <c r="E27" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F27" s="58" t="s">
+      <c r="F27" s="57" t="s">
         <v>465</v>
       </c>
       <c r="G27" s="46" t="s">
@@ -5809,7 +5755,7 @@
       </c>
       <c r="L27" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M27" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5835,7 +5781,7 @@
       </c>
       <c r="S27" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T27" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5852,10 +5798,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-27</v>
       </c>
-      <c r="X27" s="60" t="s">
+      <c r="X27" s="59" t="s">
         <v>339</v>
       </c>
-      <c r="Y27" s="61" t="s">
+      <c r="Y27" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z27" s="43" t="s">
@@ -5866,23 +5812,23 @@
         <v>Cutting Symbol - Cutting Line</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="45">
         <v>28</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D28" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E28" s="59" t="s">
+      <c r="E28" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F28" s="58" t="s">
+      <c r="F28" s="57" t="s">
         <v>466</v>
       </c>
       <c r="G28" s="46" t="s">
@@ -5902,7 +5848,7 @@
       </c>
       <c r="L28" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M28" s="54" t="str">
         <f t="shared" si="6"/>
@@ -5928,7 +5874,7 @@
       </c>
       <c r="S28" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T28" s="43" t="str">
         <f t="shared" si="24"/>
@@ -5945,10 +5891,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-28</v>
       </c>
-      <c r="X28" s="60" t="s">
+      <c r="X28" s="59" t="s">
         <v>340</v>
       </c>
-      <c r="Y28" s="61" t="s">
+      <c r="Y28" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z28" s="43" t="s">
@@ -5959,23 +5905,23 @@
         <v>Interrupted cutting line</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="45">
         <v>29</v>
       </c>
       <c r="B29" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C29" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D29" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E29" s="59" t="s">
+      <c r="E29" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="F29" s="58" t="s">
+      <c r="F29" s="57" t="s">
         <v>556</v>
       </c>
       <c r="G29" s="46" t="s">
@@ -5995,7 +5941,7 @@
       </c>
       <c r="L29" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M29" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6021,7 +5967,7 @@
       </c>
       <c r="S29" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T29" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6038,10 +5984,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-29</v>
       </c>
-      <c r="X29" s="60" t="s">
+      <c r="X29" s="59" t="s">
         <v>342</v>
       </c>
-      <c r="Y29" s="61" t="s">
+      <c r="Y29" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z29" s="43" t="s">
@@ -6052,23 +5998,23 @@
         <v>Inserted image decal</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="45">
         <v>30</v>
       </c>
       <c r="B30" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D30" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="F30" s="58" t="s">
+      <c r="F30" s="57" t="s">
         <v>573</v>
       </c>
       <c r="G30" s="46" t="s">
@@ -6088,7 +6034,7 @@
       </c>
       <c r="L30" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M30" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6114,7 +6060,7 @@
       </c>
       <c r="S30" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T30" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6131,10 +6077,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-30</v>
       </c>
-      <c r="X30" s="60" t="s">
+      <c r="X30" s="59" t="s">
         <v>343</v>
       </c>
-      <c r="Y30" s="61" t="s">
+      <c r="Y30" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z30" s="43" t="s">
@@ -6145,23 +6091,23 @@
         <v>2D Detailing Component</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="45">
         <v>31</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C31" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C31" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D31" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E31" s="59" t="s">
+      <c r="E31" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="F31" s="58" t="s">
+      <c r="F31" s="57" t="s">
         <v>574</v>
       </c>
       <c r="G31" s="46" t="s">
@@ -6181,7 +6127,7 @@
       </c>
       <c r="L31" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M31" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6207,7 +6153,7 @@
       </c>
       <c r="S31" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T31" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6224,10 +6170,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-31</v>
       </c>
-      <c r="X31" s="60" t="s">
+      <c r="X31" s="59" t="s">
         <v>344</v>
       </c>
-      <c r="Y31" s="61" t="s">
+      <c r="Y31" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z31" s="43" t="s">
@@ -6238,23 +6184,23 @@
         <v>2D Detailing Component - Hidden Lines</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="45">
         <v>32</v>
       </c>
       <c r="B32" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C32" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D32" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="F32" s="58" t="s">
+      <c r="F32" s="57" t="s">
         <v>575</v>
       </c>
       <c r="G32" s="46" t="s">
@@ -6274,7 +6220,7 @@
       </c>
       <c r="L32" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M32" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6300,7 +6246,7 @@
       </c>
       <c r="S32" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T32" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6317,10 +6263,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-32</v>
       </c>
-      <c r="X32" s="60" t="s">
+      <c r="X32" s="59" t="s">
         <v>345</v>
       </c>
-      <c r="Y32" s="61" t="s">
+      <c r="Y32" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z32" s="43" t="s">
@@ -6331,23 +6277,23 @@
         <v>Repeated detail line</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="45">
         <v>33</v>
       </c>
       <c r="B33" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C33" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D33" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E33" s="59" t="s">
+      <c r="E33" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="F33" s="58" t="s">
+      <c r="F33" s="57" t="s">
         <v>187</v>
       </c>
       <c r="G33" s="46" t="s">
@@ -6367,7 +6313,7 @@
       </c>
       <c r="L33" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M33" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6393,7 +6339,7 @@
       </c>
       <c r="S33" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T33" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6410,10 +6356,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-33</v>
       </c>
-      <c r="X33" s="60" t="s">
+      <c r="X33" s="59" t="s">
         <v>346</v>
       </c>
-      <c r="Y33" s="61" t="s">
+      <c r="Y33" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z33" s="43" t="s">
@@ -6424,23 +6370,23 @@
         <v>View symbols</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="45">
         <v>34</v>
       </c>
       <c r="B34" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C34" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C34" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D34" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E34" s="59" t="s">
+      <c r="E34" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="58" t="s">
+      <c r="F34" s="57" t="s">
         <v>467</v>
       </c>
       <c r="G34" s="46" t="s">
@@ -6460,7 +6406,7 @@
       </c>
       <c r="L34" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M34" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6486,7 +6432,7 @@
       </c>
       <c r="S34" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T34" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6503,10 +6449,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-34</v>
       </c>
-      <c r="X34" s="60" t="s">
+      <c r="X34" s="59" t="s">
         <v>347</v>
       </c>
-      <c r="Y34" s="61" t="s">
+      <c r="Y34" s="60" t="s">
         <v>442</v>
       </c>
       <c r="Z34" s="43" t="s">
@@ -6517,23 +6463,23 @@
         <v>View Symbols - Brands</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="45">
         <v>35</v>
       </c>
       <c r="B35" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C35" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D35" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E35" s="59" t="s">
+      <c r="E35" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="F35" s="58" t="s">
+      <c r="F35" s="57" t="s">
         <v>468</v>
       </c>
       <c r="G35" s="46" t="s">
@@ -6553,7 +6499,7 @@
       </c>
       <c r="L35" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M35" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6579,7 +6525,7 @@
       </c>
       <c r="S35" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T35" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6596,10 +6542,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-35</v>
       </c>
-      <c r="X35" s="60" t="s">
+      <c r="X35" s="59" t="s">
         <v>348</v>
       </c>
-      <c r="Y35" s="61" t="s">
+      <c r="Y35" s="60" t="s">
         <v>446</v>
       </c>
       <c r="Z35" s="43" t="s">
@@ -6610,23 +6556,23 @@
         <v>Coordinate Point Symbol</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="45">
         <v>36</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C36" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C36" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D36" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E36" s="59" t="s">
+      <c r="E36" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="F36" s="58" t="s">
+      <c r="F36" s="57" t="s">
         <v>469</v>
       </c>
       <c r="G36" s="46" t="s">
@@ -6646,7 +6592,7 @@
       </c>
       <c r="L36" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M36" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6672,7 +6618,7 @@
       </c>
       <c r="S36" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T36" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6689,10 +6635,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-36</v>
       </c>
-      <c r="X36" s="60" t="s">
+      <c r="X36" s="59" t="s">
         <v>349</v>
       </c>
-      <c r="Y36" s="61" t="s">
+      <c r="Y36" s="60" t="s">
         <v>446</v>
       </c>
       <c r="Z36" s="43" t="s">
@@ -6703,23 +6649,23 @@
         <v>Coordinate Point Symbols</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="45">
         <v>37</v>
       </c>
       <c r="B37" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C37" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C37" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D37" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E37" s="59" t="s">
+      <c r="E37" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="F37" s="58" t="s">
+      <c r="F37" s="57" t="s">
         <v>471</v>
       </c>
       <c r="G37" s="46" t="s">
@@ -6739,7 +6685,7 @@
       </c>
       <c r="L37" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M37" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6765,7 +6711,7 @@
       </c>
       <c r="S37" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T37" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6782,10 +6728,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-37</v>
       </c>
-      <c r="X37" s="60" t="s">
+      <c r="X37" s="59" t="s">
         <v>350</v>
       </c>
-      <c r="Y37" s="61" t="s">
+      <c r="Y37" s="60" t="s">
         <v>446</v>
       </c>
       <c r="Z37" s="43" t="s">
@@ -6796,23 +6742,23 @@
         <v>Quotation mark</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="45">
         <v>38</v>
       </c>
       <c r="B38" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C38" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D38" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E38" s="59" t="s">
+      <c r="E38" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="F38" s="58" t="s">
+      <c r="F38" s="57" t="s">
         <v>470</v>
       </c>
       <c r="G38" s="46" t="s">
@@ -6832,7 +6778,7 @@
       </c>
       <c r="L38" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M38" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6858,7 +6804,7 @@
       </c>
       <c r="S38" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T38" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6875,10 +6821,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-38</v>
       </c>
-      <c r="X38" s="60" t="s">
+      <c r="X38" s="59" t="s">
         <v>351</v>
       </c>
-      <c r="Y38" s="61" t="s">
+      <c r="Y38" s="60" t="s">
         <v>446</v>
       </c>
       <c r="Z38" s="43" t="s">
@@ -6889,23 +6835,23 @@
         <v>Tick Mark Symbols</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="45">
         <v>39</v>
       </c>
       <c r="B39" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C39" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C39" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D39" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E39" s="59" t="s">
+      <c r="E39" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="F39" s="58" t="s">
+      <c r="F39" s="57" t="s">
         <v>473</v>
       </c>
       <c r="G39" s="46" t="s">
@@ -6925,7 +6871,7 @@
       </c>
       <c r="L39" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M39" s="54" t="str">
         <f t="shared" si="6"/>
@@ -6951,7 +6897,7 @@
       </c>
       <c r="S39" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T39" s="43" t="str">
         <f t="shared" si="24"/>
@@ -6968,10 +6914,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-39</v>
       </c>
-      <c r="X39" s="60" t="s">
+      <c r="X39" s="59" t="s">
         <v>352</v>
       </c>
-      <c r="Y39" s="61" t="s">
+      <c r="Y39" s="60" t="s">
         <v>446</v>
       </c>
       <c r="Z39" s="43" t="s">
@@ -6982,23 +6928,23 @@
         <v>Slope</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="45">
         <v>40</v>
       </c>
       <c r="B40" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C40" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C40" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D40" s="56" t="s">
         <v>558</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="F40" s="58" t="s">
+      <c r="F40" s="57" t="s">
         <v>472</v>
       </c>
       <c r="G40" s="46" t="s">
@@ -7018,7 +6964,7 @@
       </c>
       <c r="L40" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M40" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7044,7 +6990,7 @@
       </c>
       <c r="S40" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T40" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7061,10 +7007,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-40</v>
       </c>
-      <c r="X40" s="60" t="s">
+      <c r="X40" s="59" t="s">
         <v>353</v>
       </c>
-      <c r="Y40" s="61" t="s">
+      <c r="Y40" s="60" t="s">
         <v>446</v>
       </c>
       <c r="Z40" s="43" t="s">
@@ -7075,23 +7021,23 @@
         <v>Slope symbols</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="45">
         <v>41</v>
       </c>
       <c r="B41" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C41" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C41" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D41" s="56" t="s">
         <v>559</v>
       </c>
-      <c r="E41" s="59" t="s">
+      <c r="E41" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="F41" s="58" t="s">
+      <c r="F41" s="57" t="s">
         <v>589</v>
       </c>
       <c r="G41" s="46" t="s">
@@ -7111,7 +7057,7 @@
       </c>
       <c r="L41" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M41" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7137,7 +7083,7 @@
       </c>
       <c r="S41" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T41" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7154,10 +7100,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-41</v>
       </c>
-      <c r="X41" s="60" t="s">
+      <c r="X41" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="Y41" s="61" t="s">
+      <c r="Y41" s="60" t="s">
         <v>443</v>
       </c>
       <c r="Z41" s="43" t="s">
@@ -7168,23 +7114,23 @@
         <v>Dimension Quoted</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="45">
         <v>42</v>
       </c>
       <c r="B42" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C42" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C42" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D42" s="56" t="s">
         <v>559</v>
       </c>
-      <c r="E42" s="59" t="s">
+      <c r="E42" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="F42" s="58" t="s">
+      <c r="F42" s="57" t="s">
         <v>550</v>
       </c>
       <c r="G42" s="46" t="s">
@@ -7204,7 +7150,7 @@
       </c>
       <c r="L42" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M42" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7230,7 +7176,7 @@
       </c>
       <c r="S42" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T42" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7247,10 +7193,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-42</v>
       </c>
-      <c r="X42" s="60" t="s">
+      <c r="X42" s="59" t="s">
         <v>355</v>
       </c>
-      <c r="Y42" s="61" t="s">
+      <c r="Y42" s="60" t="s">
         <v>443</v>
       </c>
       <c r="Z42" s="43" t="s">
@@ -7261,23 +7207,23 @@
         <v>Quota Control Line</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="45">
         <v>43</v>
       </c>
       <c r="B43" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C43" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C43" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D43" s="56" t="s">
         <v>559</v>
       </c>
-      <c r="E43" s="59" t="s">
+      <c r="E43" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="F43" s="58" t="s">
+      <c r="F43" s="57" t="s">
         <v>474</v>
       </c>
       <c r="G43" s="46" t="s">
@@ -7297,7 +7243,7 @@
       </c>
       <c r="L43" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M43" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7323,7 +7269,7 @@
       </c>
       <c r="S43" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T43" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7340,10 +7286,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-43</v>
       </c>
-      <c r="X43" s="60" t="s">
+      <c r="X43" s="59" t="s">
         <v>356</v>
       </c>
-      <c r="Y43" s="61" t="s">
+      <c r="Y43" s="60" t="s">
         <v>443</v>
       </c>
       <c r="Z43" s="43" t="s">
@@ -7354,23 +7300,23 @@
         <v>Weak Reference Dimensions</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="45">
         <v>44</v>
       </c>
       <c r="B44" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C44" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C44" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D44" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="58" t="s">
         <v>190</v>
       </c>
-      <c r="F44" s="58" t="s">
+      <c r="F44" s="57" t="s">
         <v>476</v>
       </c>
       <c r="G44" s="46" t="s">
@@ -7390,7 +7336,7 @@
       </c>
       <c r="L44" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M44" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7416,7 +7362,7 @@
       </c>
       <c r="S44" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T44" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7433,10 +7379,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-44</v>
       </c>
-      <c r="X44" s="60" t="s">
+      <c r="X44" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="Y44" s="61" t="s">
+      <c r="Y44" s="60" t="s">
         <v>443</v>
       </c>
       <c r="Z44" s="43" t="s">
@@ -7447,23 +7393,23 @@
         <v>Dimension End Element Style - Unique Identifier Style ID</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="45">
         <v>45</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C45" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C45" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D45" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E45" s="59" t="s">
+      <c r="E45" s="58" t="s">
         <v>190</v>
       </c>
-      <c r="F45" s="58" t="s">
+      <c r="F45" s="57" t="s">
         <v>475</v>
       </c>
       <c r="G45" s="46" t="s">
@@ -7483,7 +7429,7 @@
       </c>
       <c r="L45" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M45" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7509,7 +7455,7 @@
       </c>
       <c r="S45" s="43" t="str">
         <f t="shared" si="23"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T45" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7526,10 +7472,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-45</v>
       </c>
-      <c r="X45" s="60" t="s">
+      <c r="X45" s="59" t="s">
         <v>358</v>
       </c>
-      <c r="Y45" s="61" t="s">
+      <c r="Y45" s="60" t="s">
         <v>443</v>
       </c>
       <c r="Z45" s="43" t="s">
@@ -7540,23 +7486,23 @@
         <v>Dimension End Element Style - Unique Identifier Style ID</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="45">
         <v>46</v>
       </c>
       <c r="B46" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C46" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C46" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D46" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E46" s="57" t="s">
+      <c r="E46" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F46" s="58" t="s">
+      <c r="F46" s="57" t="s">
         <v>477</v>
       </c>
       <c r="G46" s="46" t="s">
@@ -7576,7 +7522,7 @@
       </c>
       <c r="L46" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M46" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7602,7 +7548,7 @@
       </c>
       <c r="S46" s="43" t="str">
         <f t="shared" ref="S46:S77" si="28">SUBSTITUTE(C46, "_", " ")</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T46" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7619,10 +7565,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-46</v>
       </c>
-      <c r="X46" s="60" t="s">
+      <c r="X46" s="59" t="s">
         <v>359</v>
       </c>
-      <c r="Y46" s="61" t="s">
+      <c r="Y46" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z46" s="43" t="s">
@@ -7633,23 +7579,23 @@
         <v>Centerlines pattern</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="45">
         <v>47</v>
       </c>
       <c r="B47" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C47" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C47" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D47" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E47" s="57" t="s">
+      <c r="E47" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F47" s="58" t="s">
+      <c r="F47" s="57" t="s">
         <v>485</v>
       </c>
       <c r="G47" s="46" t="s">
@@ -7669,7 +7615,7 @@
       </c>
       <c r="L47" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M47" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7695,7 +7641,7 @@
       </c>
       <c r="S47" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T47" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7712,10 +7658,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-47</v>
       </c>
-      <c r="X47" s="60" t="s">
+      <c r="X47" s="59" t="s">
         <v>360</v>
       </c>
-      <c r="Y47" s="61" t="s">
+      <c r="Y47" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z47" s="43" t="s">
@@ -7726,23 +7672,23 @@
         <v>Invisible lines</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="45">
         <v>48</v>
       </c>
       <c r="B48" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C48" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C48" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D48" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E48" s="57" t="s">
+      <c r="E48" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F48" s="58" t="s">
+      <c r="F48" s="57" t="s">
         <v>479</v>
       </c>
       <c r="G48" s="46" t="s">
@@ -7762,7 +7708,7 @@
       </c>
       <c r="L48" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M48" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7788,7 +7734,7 @@
       </c>
       <c r="S48" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T48" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7805,10 +7751,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-48</v>
       </c>
-      <c r="X48" s="60" t="s">
+      <c r="X48" s="59" t="s">
         <v>361</v>
       </c>
-      <c r="Y48" s="61" t="s">
+      <c r="Y48" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z48" s="43" t="s">
@@ -7819,23 +7765,23 @@
         <v>Projected edge lines</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="45">
         <v>49</v>
       </c>
       <c r="B49" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C49" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C49" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D49" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E49" s="57" t="s">
+      <c r="E49" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F49" s="58" t="s">
+      <c r="F49" s="57" t="s">
         <v>480</v>
       </c>
       <c r="G49" s="46" t="s">
@@ -7855,7 +7801,7 @@
       </c>
       <c r="L49" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M49" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7881,7 +7827,7 @@
       </c>
       <c r="S49" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T49" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7898,10 +7844,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-49</v>
       </c>
-      <c r="X49" s="60" t="s">
+      <c r="X49" s="59" t="s">
         <v>362</v>
       </c>
-      <c r="Y49" s="61" t="s">
+      <c r="Y49" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z49" s="43" t="s">
@@ -7912,23 +7858,23 @@
         <v>Insulation lines</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="45">
         <v>50</v>
       </c>
       <c r="B50" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C50" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C50" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D50" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E50" s="57" t="s">
+      <c r="E50" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F50" s="58" t="s">
+      <c r="F50" s="57" t="s">
         <v>481</v>
       </c>
       <c r="G50" s="46" t="s">
@@ -7948,7 +7894,7 @@
       </c>
       <c r="L50" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M50" s="54" t="str">
         <f t="shared" si="6"/>
@@ -7974,7 +7920,7 @@
       </c>
       <c r="S50" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T50" s="43" t="str">
         <f t="shared" si="24"/>
@@ -7991,10 +7937,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-50</v>
       </c>
-      <c r="X50" s="60" t="s">
+      <c r="X50" s="59" t="s">
         <v>363</v>
       </c>
-      <c r="Y50" s="61" t="s">
+      <c r="Y50" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z50" s="43" t="s">
@@ -8005,23 +7951,23 @@
         <v>Centerlines</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="45">
         <v>51</v>
       </c>
       <c r="B51" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C51" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D51" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C51" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D51" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E51" s="57" t="s">
+      <c r="E51" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F51" s="58" t="s">
+      <c r="F51" s="57" t="s">
         <v>482</v>
       </c>
       <c r="G51" s="46" t="s">
@@ -8041,7 +7987,7 @@
       </c>
       <c r="L51" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M51" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8067,7 +8013,7 @@
       </c>
       <c r="S51" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T51" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8084,10 +8030,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-51</v>
       </c>
-      <c r="X51" s="60" t="s">
+      <c r="X51" s="59" t="s">
         <v>364</v>
       </c>
-      <c r="Y51" s="61" t="s">
+      <c r="Y51" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z51" s="43" t="s">
@@ -8098,23 +8044,23 @@
         <v>CL Centerlines</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="45">
         <v>52</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C52" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D52" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C52" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D52" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E52" s="57" t="s">
+      <c r="E52" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F52" s="58" t="s">
+      <c r="F52" s="57" t="s">
         <v>483</v>
       </c>
       <c r="G52" s="46" t="s">
@@ -8134,7 +8080,7 @@
       </c>
       <c r="L52" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M52" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8160,7 +8106,7 @@
       </c>
       <c r="S52" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T52" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8177,10 +8123,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-52</v>
       </c>
-      <c r="X52" s="60" t="s">
+      <c r="X52" s="59" t="s">
         <v>365</v>
       </c>
-      <c r="Y52" s="61" t="s">
+      <c r="Y52" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z52" s="43" t="s">
@@ -8191,23 +8137,23 @@
         <v>Demolition lines</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="45">
         <v>53</v>
       </c>
       <c r="B53" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C53" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C53" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D53" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E53" s="57" t="s">
+      <c r="E53" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F53" s="58" t="s">
+      <c r="F53" s="57" t="s">
         <v>484</v>
       </c>
       <c r="G53" s="46" t="s">
@@ -8227,7 +8173,7 @@
       </c>
       <c r="L53" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M53" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8253,7 +8199,7 @@
       </c>
       <c r="S53" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T53" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8270,10 +8216,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-53</v>
       </c>
-      <c r="X53" s="60" t="s">
+      <c r="X53" s="59" t="s">
         <v>366</v>
       </c>
-      <c r="Y53" s="61" t="s">
+      <c r="Y53" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z53" s="43" t="s">
@@ -8284,23 +8230,23 @@
         <v>Top edge projection lines</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="45">
         <v>54</v>
       </c>
       <c r="B54" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C54" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C54" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D54" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E54" s="57" t="s">
+      <c r="E54" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F54" s="58" t="s">
+      <c r="F54" s="57" t="s">
         <v>487</v>
       </c>
       <c r="G54" s="46" t="s">
@@ -8320,7 +8266,7 @@
       </c>
       <c r="L54" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M54" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8346,7 +8292,7 @@
       </c>
       <c r="S54" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T54" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8363,10 +8309,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-54</v>
       </c>
-      <c r="X54" s="60" t="s">
+      <c r="X54" s="59" t="s">
         <v>367</v>
       </c>
-      <c r="Y54" s="61" t="s">
+      <c r="Y54" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z54" s="43" t="s">
@@ -8377,23 +8323,23 @@
         <v>Hidden Lines</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="45">
         <v>55</v>
       </c>
       <c r="B55" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C55" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D55" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C55" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D55" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E55" s="57" t="s">
+      <c r="E55" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F55" s="58" t="s">
+      <c r="F55" s="57" t="s">
         <v>486</v>
       </c>
       <c r="G55" s="46" t="s">
@@ -8413,7 +8359,7 @@
       </c>
       <c r="L55" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M55" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8439,7 +8385,7 @@
       </c>
       <c r="S55" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T55" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8456,10 +8402,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-55</v>
       </c>
-      <c r="X55" s="60" t="s">
+      <c r="X55" s="59" t="s">
         <v>368</v>
       </c>
-      <c r="Y55" s="61" t="s">
+      <c r="Y55" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z55" s="43" t="s">
@@ -8470,23 +8416,23 @@
         <v>Hidden Floor Lines</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="45">
         <v>56</v>
       </c>
       <c r="B56" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C56" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D56" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C56" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D56" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E56" s="57" t="s">
+      <c r="E56" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F56" s="58" t="s">
+      <c r="F56" s="57" t="s">
         <v>478</v>
       </c>
       <c r="G56" s="46" t="s">
@@ -8506,7 +8452,7 @@
       </c>
       <c r="L56" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M56" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8532,7 +8478,7 @@
       </c>
       <c r="S56" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T56" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8549,10 +8495,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-56</v>
       </c>
-      <c r="X56" s="60" t="s">
+      <c r="X56" s="59" t="s">
         <v>369</v>
       </c>
-      <c r="Y56" s="61" t="s">
+      <c r="Y56" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z56" s="43" t="s">
@@ -8563,23 +8509,23 @@
         <v>Hidden Lines</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="45">
         <v>57</v>
       </c>
       <c r="B57" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C57" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C57" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D57" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E57" s="57" t="s">
+      <c r="E57" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F57" s="58" t="s">
+      <c r="F57" s="57" t="s">
         <v>488</v>
       </c>
       <c r="G57" s="46" t="s">
@@ -8599,7 +8545,7 @@
       </c>
       <c r="L57" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M57" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8625,7 +8571,7 @@
       </c>
       <c r="S57" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T57" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8642,10 +8588,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-57</v>
       </c>
-      <c r="X57" s="60" t="s">
+      <c r="X57" s="59" t="s">
         <v>370</v>
       </c>
-      <c r="Y57" s="61" t="s">
+      <c r="Y57" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z57" s="43" t="s">
@@ -8656,23 +8602,23 @@
         <v>Hidden rows of structural columns</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="45">
         <v>58</v>
       </c>
       <c r="B58" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C58" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D58" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C58" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D58" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E58" s="57" t="s">
+      <c r="E58" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F58" s="58" t="s">
+      <c r="F58" s="57" t="s">
         <v>489</v>
       </c>
       <c r="G58" s="46" t="s">
@@ -8692,7 +8638,7 @@
       </c>
       <c r="L58" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M58" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8718,7 +8664,7 @@
       </c>
       <c r="S58" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T58" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8735,10 +8681,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-58</v>
       </c>
-      <c r="X58" s="60" t="s">
+      <c r="X58" s="59" t="s">
         <v>371</v>
       </c>
-      <c r="Y58" s="61" t="s">
+      <c r="Y58" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z58" s="43" t="s">
@@ -8749,23 +8695,23 @@
         <v>Hidden lines of structural foundations</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="45">
         <v>59</v>
       </c>
       <c r="B59" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C59" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D59" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C59" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D59" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E59" s="57" t="s">
+      <c r="E59" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F59" s="58" t="s">
+      <c r="F59" s="57" t="s">
         <v>490</v>
       </c>
       <c r="G59" s="46" t="s">
@@ -8785,7 +8731,7 @@
       </c>
       <c r="L59" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M59" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8811,7 +8757,7 @@
       </c>
       <c r="S59" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T59" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8828,10 +8774,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-59</v>
       </c>
-      <c r="X59" s="60" t="s">
+      <c r="X59" s="59" t="s">
         <v>372</v>
       </c>
-      <c r="Y59" s="61" t="s">
+      <c r="Y59" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z59" s="43" t="s">
@@ -8842,23 +8788,23 @@
         <v>Hidden lines of structural beams</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="45">
         <v>60</v>
       </c>
       <c r="B60" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C60" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C60" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D60" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E60" s="57" t="s">
+      <c r="E60" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F60" s="58" t="s">
+      <c r="F60" s="57" t="s">
         <v>491</v>
       </c>
       <c r="G60" s="46" t="s">
@@ -8878,7 +8824,7 @@
       </c>
       <c r="L60" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M60" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8904,7 +8850,7 @@
       </c>
       <c r="S60" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T60" s="43" t="str">
         <f t="shared" si="24"/>
@@ -8921,10 +8867,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-60</v>
       </c>
-      <c r="X60" s="60" t="s">
+      <c r="X60" s="59" t="s">
         <v>373</v>
       </c>
-      <c r="Y60" s="61" t="s">
+      <c r="Y60" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z60" s="43" t="s">
@@ -8935,23 +8881,23 @@
         <v>Hidden Lines of Walls</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="45">
         <v>61</v>
       </c>
       <c r="B61" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C61" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D61" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C61" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D61" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="56" t="s">
         <v>551</v>
       </c>
-      <c r="F61" s="58" t="s">
+      <c r="F61" s="57" t="s">
         <v>552</v>
       </c>
       <c r="G61" s="46" t="s">
@@ -8971,7 +8917,7 @@
       </c>
       <c r="L61" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M61" s="54" t="str">
         <f t="shared" si="6"/>
@@ -8997,7 +8943,7 @@
       </c>
       <c r="S61" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T61" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9014,10 +8960,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-61</v>
       </c>
-      <c r="X61" s="60" t="s">
+      <c r="X61" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="Y61" s="61" t="s">
+      <c r="Y61" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z61" s="43" t="s">
@@ -9028,23 +8974,23 @@
         <v>Instance Row Style</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="45">
         <v>62</v>
       </c>
       <c r="B62" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C62" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D62" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C62" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D62" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E62" s="59" t="s">
+      <c r="E62" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="F62" s="58" t="s">
+      <c r="F62" s="57" t="s">
         <v>496</v>
       </c>
       <c r="G62" s="46" t="s">
@@ -9064,7 +9010,7 @@
       </c>
       <c r="L62" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M62" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9090,7 +9036,7 @@
       </c>
       <c r="S62" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T62" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9107,10 +9053,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-62</v>
       </c>
-      <c r="X62" s="60" t="s">
+      <c r="X62" s="59" t="s">
         <v>375</v>
       </c>
-      <c r="Y62" s="61" t="s">
+      <c r="Y62" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z62" s="43" t="s">
@@ -9121,23 +9067,23 @@
         <v>Ticks style centerline ticks</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="45">
         <v>63</v>
       </c>
       <c r="B63" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C63" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D63" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C63" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D63" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E63" s="59" t="s">
+      <c r="E63" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="F63" s="58" t="s">
+      <c r="F63" s="57" t="s">
         <v>495</v>
       </c>
       <c r="G63" s="46" t="s">
@@ -9157,7 +9103,7 @@
       </c>
       <c r="L63" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M63" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9183,7 +9129,7 @@
       </c>
       <c r="S63" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T63" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9200,10 +9146,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-63</v>
       </c>
-      <c r="X63" s="60" t="s">
+      <c r="X63" s="59" t="s">
         <v>376</v>
       </c>
-      <c r="Y63" s="61" t="s">
+      <c r="Y63" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z63" s="43" t="s">
@@ -9214,23 +9160,23 @@
         <v>Quota Tick Mark - Unique Style ID Identifier</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="45">
         <v>64</v>
       </c>
       <c r="B64" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C64" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D64" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C64" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D64" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E64" s="59" t="s">
+      <c r="E64" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="F64" s="58" t="s">
+      <c r="F64" s="57" t="s">
         <v>494</v>
       </c>
       <c r="G64" s="46" t="s">
@@ -9250,7 +9196,7 @@
       </c>
       <c r="L64" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M64" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9276,7 +9222,7 @@
       </c>
       <c r="S64" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T64" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9293,10 +9239,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-64</v>
       </c>
-      <c r="X64" s="60" t="s">
+      <c r="X64" s="59" t="s">
         <v>377</v>
       </c>
-      <c r="Y64" s="61" t="s">
+      <c r="Y64" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z64" s="43" t="s">
@@ -9307,23 +9253,23 @@
         <v>Tick Brand Interior - Unique Style ID Identifier</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="45">
         <v>65</v>
       </c>
       <c r="B65" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C65" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D65" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C65" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D65" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E65" s="59" t="s">
+      <c r="E65" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="F65" s="58" t="s">
+      <c r="F65" s="57" t="s">
         <v>493</v>
       </c>
       <c r="G65" s="46" t="s">
@@ -9343,7 +9289,7 @@
       </c>
       <c r="L65" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M65" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9369,7 +9315,7 @@
       </c>
       <c r="S65" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T65" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9386,10 +9332,10 @@
         <f t="shared" si="3"/>
         <v>Key-DOCU-65</v>
       </c>
-      <c r="X65" s="60" t="s">
+      <c r="X65" s="59" t="s">
         <v>378</v>
       </c>
-      <c r="Y65" s="61" t="s">
+      <c r="Y65" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z65" s="43" t="s">
@@ -9400,23 +9346,23 @@
         <v>Calling Line Tick Mark - Unique Style ID Identifier</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="45">
         <v>66</v>
       </c>
       <c r="B66" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C66" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C66" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D66" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E66" s="59" t="s">
+      <c r="E66" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="F66" s="58" t="s">
+      <c r="F66" s="57" t="s">
         <v>492</v>
       </c>
       <c r="G66" s="46" t="s">
@@ -9436,7 +9382,7 @@
       </c>
       <c r="L66" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M66" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9462,7 +9408,7 @@
       </c>
       <c r="S66" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T66" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9479,10 +9425,10 @@
         <f t="shared" ref="W66:W129" si="30">CONCATENATE("Key-DOCU-",A66)</f>
         <v>Key-DOCU-66</v>
       </c>
-      <c r="X66" s="60" t="s">
+      <c r="X66" s="59" t="s">
         <v>379</v>
       </c>
-      <c r="Y66" s="61" t="s">
+      <c r="Y66" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z66" s="43" t="s">
@@ -9493,23 +9439,23 @@
         <v>Symbolic arrows head</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="45">
         <v>67</v>
       </c>
       <c r="B67" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C67" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D67" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C67" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D67" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E67" s="57" t="s">
+      <c r="E67" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="F67" s="58" t="s">
+      <c r="F67" s="57" t="s">
         <v>497</v>
       </c>
       <c r="G67" s="46" t="s">
@@ -9529,7 +9475,7 @@
       </c>
       <c r="L67" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M67" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9555,7 +9501,7 @@
       </c>
       <c r="S67" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T67" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9572,10 +9518,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-67</v>
       </c>
-      <c r="X67" s="60" t="s">
+      <c r="X67" s="59" t="s">
         <v>380</v>
       </c>
-      <c r="Y67" s="61" t="s">
+      <c r="Y67" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z67" s="43" t="s">
@@ -9586,23 +9532,23 @@
         <v>Text and Leader - Text Source</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="45">
         <v>68</v>
       </c>
       <c r="B68" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C68" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D68" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C68" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D68" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E68" s="59" t="s">
+      <c r="E68" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="F68" s="58" t="s">
+      <c r="F68" s="57" t="s">
         <v>498</v>
       </c>
       <c r="G68" s="46" t="s">
@@ -9622,7 +9568,7 @@
       </c>
       <c r="L68" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M68" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9648,7 +9594,7 @@
       </c>
       <c r="S68" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T68" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9665,10 +9611,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-68</v>
       </c>
-      <c r="X68" s="60" t="s">
+      <c r="X68" s="59" t="s">
         <v>381</v>
       </c>
-      <c r="Y68" s="61" t="s">
+      <c r="Y68" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z68" s="43" t="s">
@@ -9679,23 +9625,23 @@
         <v>Text and Leader Line - Unique ID Identifier</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="45">
         <v>69</v>
       </c>
       <c r="B69" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C69" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D69" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C69" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D69" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="E69" s="59" t="s">
+      <c r="E69" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="F69" s="58" t="s">
+      <c r="F69" s="57" t="s">
         <v>499</v>
       </c>
       <c r="G69" s="46" t="s">
@@ -9715,7 +9661,7 @@
       </c>
       <c r="L69" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M69" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9741,7 +9687,7 @@
       </c>
       <c r="S69" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T69" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9758,10 +9704,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-69</v>
       </c>
-      <c r="X69" s="60" t="s">
+      <c r="X69" s="59" t="s">
         <v>382</v>
       </c>
-      <c r="Y69" s="61" t="s">
+      <c r="Y69" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z69" s="43" t="s">
@@ -9772,23 +9718,23 @@
         <v>Styling imported objects</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="45">
         <v>70</v>
       </c>
       <c r="B70" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C70" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D70" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C70" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D70" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E70" s="57" t="s">
+      <c r="E70" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="F70" s="58" t="s">
+      <c r="F70" s="57" t="s">
         <v>501</v>
       </c>
       <c r="G70" s="46" t="s">
@@ -9808,7 +9754,7 @@
       </c>
       <c r="L70" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M70" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9834,7 +9780,7 @@
       </c>
       <c r="S70" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T70" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9851,10 +9797,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-70</v>
       </c>
-      <c r="X70" s="60" t="s">
+      <c r="X70" s="59" t="s">
         <v>383</v>
       </c>
-      <c r="Y70" s="61" t="s">
+      <c r="Y70" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z70" s="43" t="s">
@@ -9865,23 +9811,23 @@
         <v>Duct Legend</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="45">
         <v>71</v>
       </c>
       <c r="B71" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C71" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D71" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C71" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D71" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E71" s="57" t="s">
+      <c r="E71" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="F71" s="58" t="s">
+      <c r="F71" s="57" t="s">
         <v>500</v>
       </c>
       <c r="G71" s="46" t="s">
@@ -9901,7 +9847,7 @@
       </c>
       <c r="L71" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M71" s="54" t="str">
         <f t="shared" si="6"/>
@@ -9927,7 +9873,7 @@
       </c>
       <c r="S71" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T71" s="43" t="str">
         <f t="shared" si="24"/>
@@ -9944,10 +9890,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-71</v>
       </c>
-      <c r="X71" s="60" t="s">
+      <c r="X71" s="59" t="s">
         <v>384</v>
       </c>
-      <c r="Y71" s="61" t="s">
+      <c r="Y71" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z71" s="43" t="s">
@@ -9958,23 +9904,23 @@
         <v>Duct Color Filling</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="45">
         <v>72</v>
       </c>
       <c r="B72" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C72" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D72" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C72" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D72" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E72" s="57" t="s">
+      <c r="E72" s="56" t="s">
         <v>195</v>
       </c>
-      <c r="F72" s="58" t="s">
+      <c r="F72" s="57" t="s">
         <v>502</v>
       </c>
       <c r="G72" s="46" t="s">
@@ -9994,7 +9940,7 @@
       </c>
       <c r="L72" s="54" t="str">
         <f t="shared" si="5"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M72" s="54" t="str">
         <f t="shared" si="6"/>
@@ -10020,7 +9966,7 @@
       </c>
       <c r="S72" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T72" s="43" t="str">
         <f t="shared" si="24"/>
@@ -10037,10 +9983,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-72</v>
       </c>
-      <c r="X72" s="60" t="s">
+      <c r="X72" s="59" t="s">
         <v>385</v>
       </c>
-      <c r="Y72" s="61" t="s">
+      <c r="Y72" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z72" s="43" t="s">
@@ -10051,23 +9997,23 @@
         <v>Pipes - Color Legends</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="45">
         <v>73</v>
       </c>
       <c r="B73" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C73" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D73" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C73" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D73" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E73" s="57" t="s">
+      <c r="E73" s="56" t="s">
         <v>195</v>
       </c>
-      <c r="F73" s="58" t="s">
+      <c r="F73" s="57" t="s">
         <v>503</v>
       </c>
       <c r="G73" s="46" t="s">
@@ -10087,7 +10033,7 @@
       </c>
       <c r="L73" s="54" t="str">
         <f t="shared" ref="L73:L142" si="31">CONCATENATE("", C73)</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M73" s="54" t="str">
         <f t="shared" ref="M73:M142" si="32">CONCATENATE("", D73)</f>
@@ -10113,7 +10059,7 @@
       </c>
       <c r="S73" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T73" s="43" t="str">
         <f t="shared" si="24"/>
@@ -10130,10 +10076,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-73</v>
       </c>
-      <c r="X73" s="60" t="s">
+      <c r="X73" s="59" t="s">
         <v>386</v>
       </c>
-      <c r="Y73" s="61" t="s">
+      <c r="Y73" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z73" s="43" t="s">
@@ -10144,23 +10090,23 @@
         <v>Pipes - Colors</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="45">
         <v>74</v>
       </c>
       <c r="B74" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C74" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D74" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C74" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D74" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E74" s="57" t="s">
+      <c r="E74" s="56" t="s">
         <v>196</v>
       </c>
-      <c r="F74" s="58" t="s">
+      <c r="F74" s="57" t="s">
         <v>504</v>
       </c>
       <c r="G74" s="46" t="s">
@@ -10180,7 +10126,7 @@
       </c>
       <c r="L74" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M74" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10206,7 +10152,7 @@
       </c>
       <c r="S74" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T74" s="43" t="str">
         <f t="shared" si="24"/>
@@ -10223,10 +10169,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-74</v>
       </c>
-      <c r="X74" s="60" t="s">
+      <c r="X74" s="59" t="s">
         <v>387</v>
       </c>
-      <c r="Y74" s="61" t="s">
+      <c r="Y74" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z74" s="43" t="s">
@@ -10237,23 +10183,23 @@
         <v>Environment - color filling</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="45">
         <v>75</v>
       </c>
       <c r="B75" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C75" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D75" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C75" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D75" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E75" s="57" t="s">
+      <c r="E75" s="56" t="s">
         <v>196</v>
       </c>
-      <c r="F75" s="58" t="s">
+      <c r="F75" s="57" t="s">
         <v>505</v>
       </c>
       <c r="G75" s="46" t="s">
@@ -10273,7 +10219,7 @@
       </c>
       <c r="L75" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M75" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10299,7 +10245,7 @@
       </c>
       <c r="S75" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T75" s="43" t="str">
         <f t="shared" si="24"/>
@@ -10316,10 +10262,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-75</v>
       </c>
-      <c r="X75" s="60" t="s">
+      <c r="X75" s="59" t="s">
         <v>388</v>
       </c>
-      <c r="Y75" s="61" t="s">
+      <c r="Y75" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z75" s="43" t="s">
@@ -10330,23 +10276,23 @@
         <v>Building occupation areas - color filling</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="45">
         <v>76</v>
       </c>
       <c r="B76" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C76" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D76" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C76" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D76" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E76" s="59" t="s">
+      <c r="E76" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="F76" s="58" t="s">
+      <c r="F76" s="57" t="s">
         <v>506</v>
       </c>
       <c r="G76" s="46" t="s">
@@ -10366,7 +10312,7 @@
       </c>
       <c r="L76" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M76" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10392,7 +10338,7 @@
       </c>
       <c r="S76" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T76" s="43" t="str">
         <f t="shared" si="24"/>
@@ -10409,10 +10355,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-76</v>
       </c>
-      <c r="X76" s="60" t="s">
+      <c r="X76" s="59" t="s">
         <v>389</v>
       </c>
-      <c r="Y76" s="61" t="s">
+      <c r="Y76" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z76" s="43" t="s">
@@ -10423,23 +10369,23 @@
         <v>MEP - HVAC Spaces - Color Fill</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="45">
         <v>77</v>
       </c>
       <c r="B77" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C77" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D77" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C77" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D77" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E77" s="59" t="s">
+      <c r="E77" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="F77" s="58" t="s">
+      <c r="F77" s="57" t="s">
         <v>507</v>
       </c>
       <c r="G77" s="46" t="s">
@@ -10459,7 +10405,7 @@
       </c>
       <c r="L77" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M77" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10485,7 +10431,7 @@
       </c>
       <c r="S77" s="43" t="str">
         <f t="shared" si="28"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T77" s="43" t="str">
         <f t="shared" si="24"/>
@@ -10502,10 +10448,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-77</v>
       </c>
-      <c r="X77" s="60" t="s">
+      <c r="X77" s="59" t="s">
         <v>390</v>
       </c>
-      <c r="Y77" s="61" t="s">
+      <c r="Y77" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z77" s="43" t="s">
@@ -10516,23 +10462,23 @@
         <v>HVAC zones - color fill</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="45">
         <v>78</v>
       </c>
       <c r="B78" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C78" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D78" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C78" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D78" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E78" s="59" t="s">
+      <c r="E78" s="58" t="s">
         <v>198</v>
       </c>
-      <c r="F78" s="58" t="s">
+      <c r="F78" s="57" t="s">
         <v>508</v>
       </c>
       <c r="G78" s="46" t="s">
@@ -10552,7 +10498,7 @@
       </c>
       <c r="L78" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M78" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10578,7 +10524,7 @@
       </c>
       <c r="S78" s="43" t="str">
         <f t="shared" ref="S78:S109" si="37">SUBSTITUTE(C78, "_", " ")</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T78" s="43" t="str">
         <f t="shared" ref="T78:T145" si="38">SUBSTITUTE(D78, "_", " ")</f>
@@ -10595,10 +10541,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-78</v>
       </c>
-      <c r="X78" s="60" t="s">
+      <c r="X78" s="59" t="s">
         <v>391</v>
       </c>
-      <c r="Y78" s="61" t="s">
+      <c r="Y78" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z78" s="43" t="s">
@@ -10609,23 +10555,23 @@
         <v>Subtitles - Color Scheme</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="45">
         <v>79</v>
       </c>
       <c r="B79" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C79" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D79" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C79" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D79" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="E79" s="59" t="s">
+      <c r="E79" s="58" t="s">
         <v>198</v>
       </c>
-      <c r="F79" s="58" t="s">
+      <c r="F79" s="57" t="s">
         <v>509</v>
       </c>
       <c r="G79" s="46" t="s">
@@ -10645,7 +10591,7 @@
       </c>
       <c r="L79" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M79" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10671,7 +10617,7 @@
       </c>
       <c r="S79" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T79" s="43" t="str">
         <f t="shared" si="38"/>
@@ -10688,10 +10634,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-79</v>
       </c>
-      <c r="X79" s="60" t="s">
+      <c r="X79" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="Y79" s="61" t="s">
+      <c r="Y79" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z79" s="43" t="s">
@@ -10702,23 +10648,23 @@
         <v>Component Legend</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="45">
         <v>80</v>
       </c>
       <c r="B80" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C80" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D80" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C80" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D80" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E80" s="57" t="s">
+      <c r="E80" s="56" t="s">
         <v>547</v>
       </c>
-      <c r="F80" s="58" t="s">
+      <c r="F80" s="57" t="s">
         <v>137</v>
       </c>
       <c r="G80" s="46" t="s">
@@ -10738,7 +10684,7 @@
       </c>
       <c r="L80" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M80" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10764,7 +10710,7 @@
       </c>
       <c r="S80" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T80" s="43" t="str">
         <f t="shared" si="38"/>
@@ -10781,10 +10727,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-80</v>
       </c>
-      <c r="X80" s="60" t="s">
+      <c r="X80" s="59" t="s">
         <v>396</v>
       </c>
-      <c r="Y80" s="61" t="s">
+      <c r="Y80" s="60" t="s">
         <v>444</v>
       </c>
       <c r="Z80" s="43" t="s">
@@ -10795,23 +10741,23 @@
         <v>Lines</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="45">
         <v>81</v>
       </c>
       <c r="B81" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C81" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D81" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C81" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D81" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E81" s="57" t="s">
+      <c r="E81" s="56" t="s">
         <v>547</v>
       </c>
-      <c r="F81" s="58" t="s">
+      <c r="F81" s="57" t="s">
         <v>544</v>
       </c>
       <c r="G81" s="46" t="s">
@@ -10831,7 +10777,7 @@
       </c>
       <c r="L81" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M81" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10857,7 +10803,7 @@
       </c>
       <c r="S81" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T81" s="43" t="str">
         <f t="shared" si="38"/>
@@ -10874,10 +10820,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-81</v>
       </c>
-      <c r="X81" s="60" t="s">
+      <c r="X81" s="59" t="s">
         <v>393</v>
       </c>
-      <c r="Y81" s="61" t="s">
+      <c r="Y81" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z81" s="43" t="s">
@@ -10888,23 +10834,23 @@
         <v>Lines - Call Cloud Lines</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="45">
         <v>82</v>
       </c>
       <c r="B82" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C82" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D82" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C82" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D82" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E82" s="57" t="s">
+      <c r="E82" s="56" t="s">
         <v>547</v>
       </c>
-      <c r="F82" s="58" t="s">
+      <c r="F82" s="57" t="s">
         <v>545</v>
       </c>
       <c r="G82" s="46" t="s">
@@ -10924,7 +10870,7 @@
       </c>
       <c r="L82" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M82" s="54" t="str">
         <f t="shared" si="32"/>
@@ -10950,7 +10896,7 @@
       </c>
       <c r="S82" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T82" s="43" t="str">
         <f t="shared" si="38"/>
@@ -10967,10 +10913,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-82</v>
       </c>
-      <c r="X82" s="60" t="s">
+      <c r="X82" s="59" t="s">
         <v>394</v>
       </c>
-      <c r="Y82" s="61" t="s">
+      <c r="Y82" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z82" s="43" t="s">
@@ -10981,23 +10927,23 @@
         <v>Direction line of the edges</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="45">
         <v>83</v>
       </c>
       <c r="B83" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C83" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D83" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C83" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D83" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E83" s="57" t="s">
+      <c r="E83" s="56" t="s">
         <v>547</v>
       </c>
-      <c r="F83" s="58" t="s">
+      <c r="F83" s="57" t="s">
         <v>546</v>
       </c>
       <c r="G83" s="46" t="s">
@@ -11017,7 +10963,7 @@
       </c>
       <c r="L83" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M83" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11043,7 +10989,7 @@
       </c>
       <c r="S83" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T83" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11060,10 +11006,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-83</v>
       </c>
-      <c r="X83" s="60" t="s">
+      <c r="X83" s="59" t="s">
         <v>395</v>
       </c>
-      <c r="Y83" s="61" t="s">
+      <c r="Y83" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z83" s="43" t="s">
@@ -11074,23 +11020,23 @@
         <v>Generic lines</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="45">
         <v>84</v>
       </c>
       <c r="B84" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C84" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D84" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C84" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D84" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E84" s="59" t="s">
+      <c r="E84" s="58" t="s">
         <v>588</v>
       </c>
-      <c r="F84" s="58" t="s">
+      <c r="F84" s="57" t="s">
         <v>510</v>
       </c>
       <c r="G84" s="46" t="s">
@@ -11110,7 +11056,7 @@
       </c>
       <c r="L84" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M84" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11136,7 +11082,7 @@
       </c>
       <c r="S84" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T84" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11153,10 +11099,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-84</v>
       </c>
-      <c r="X84" s="60" t="s">
+      <c r="X84" s="59" t="s">
         <v>451</v>
       </c>
-      <c r="Y84" s="61" t="s">
+      <c r="Y84" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z84" s="43" t="s">
@@ -11167,23 +11113,23 @@
         <v>Displacement value</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="45">
         <v>85</v>
       </c>
       <c r="B85" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C85" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D85" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C85" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D85" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E85" s="59" t="s">
+      <c r="E85" s="58" t="s">
         <v>588</v>
       </c>
-      <c r="F85" s="58" t="s">
+      <c r="F85" s="57" t="s">
         <v>511</v>
       </c>
       <c r="G85" s="46" t="s">
@@ -11203,7 +11149,7 @@
       </c>
       <c r="L85" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M85" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11229,7 +11175,7 @@
       </c>
       <c r="S85" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T85" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11246,10 +11192,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-85</v>
       </c>
-      <c r="X85" s="60" t="s">
+      <c r="X85" s="59" t="s">
         <v>452</v>
       </c>
-      <c r="Y85" s="61" t="s">
+      <c r="Y85" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z85" s="43" t="s">
@@ -11260,23 +11206,23 @@
         <v>Displacement path</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="45">
         <v>86</v>
       </c>
       <c r="B86" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C86" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D86" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C86" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D86" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E86" s="59" t="s">
+      <c r="E86" s="58" t="s">
         <v>588</v>
       </c>
-      <c r="F86" s="58" t="s">
+      <c r="F86" s="57" t="s">
         <v>512</v>
       </c>
       <c r="G86" s="46" t="s">
@@ -11296,7 +11242,7 @@
       </c>
       <c r="L86" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M86" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11322,7 +11268,7 @@
       </c>
       <c r="S86" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T86" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11339,10 +11285,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-86</v>
       </c>
-      <c r="X86" s="60" t="s">
+      <c r="X86" s="59" t="s">
         <v>398</v>
       </c>
-      <c r="Y86" s="61" t="s">
+      <c r="Y86" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z86" s="43" t="s">
@@ -11353,23 +11299,23 @@
         <v>Graphic warning - Open</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="45">
         <v>87</v>
       </c>
       <c r="B87" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C87" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D87" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C87" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D87" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E87" s="59" t="s">
+      <c r="E87" s="58" t="s">
         <v>588</v>
       </c>
-      <c r="F87" s="58" t="s">
+      <c r="F87" s="57" t="s">
         <v>513</v>
       </c>
       <c r="G87" s="46" t="s">
@@ -11389,7 +11335,7 @@
       </c>
       <c r="L87" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M87" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11415,7 +11361,7 @@
       </c>
       <c r="S87" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T87" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11432,10 +11378,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-87</v>
       </c>
-      <c r="X87" s="60" t="s">
+      <c r="X87" s="59" t="s">
         <v>399</v>
       </c>
-      <c r="Y87" s="61" t="s">
+      <c r="Y87" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z87" s="43" t="s">
@@ -11446,23 +11392,23 @@
         <v>Raster or bitmap image inserted into the model</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="45">
         <v>88</v>
       </c>
       <c r="B88" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C88" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D88" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C88" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D88" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E88" s="59" t="s">
+      <c r="E88" s="58" t="s">
         <v>588</v>
       </c>
-      <c r="F88" s="58" t="s">
+      <c r="F88" s="57" t="s">
         <v>514</v>
       </c>
       <c r="G88" s="46" t="s">
@@ -11482,7 +11428,7 @@
       </c>
       <c r="L88" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M88" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11508,7 +11454,7 @@
       </c>
       <c r="S88" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T88" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11525,10 +11471,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-88</v>
       </c>
-      <c r="X88" s="60" t="s">
+      <c r="X88" s="59" t="s">
         <v>400</v>
       </c>
-      <c r="Y88" s="61" t="s">
+      <c r="Y88" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z88" s="43" t="s">
@@ -11539,23 +11485,23 @@
         <v>Symbol of ascent or descent in tubes - Yin and Yang</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="45">
         <v>89</v>
       </c>
       <c r="B89" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C89" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D89" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C89" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D89" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E89" s="59" t="s">
+      <c r="E89" s="58" t="s">
         <v>588</v>
       </c>
-      <c r="F89" s="58" t="s">
+      <c r="F89" s="57" t="s">
         <v>515</v>
       </c>
       <c r="G89" s="46" t="s">
@@ -11575,7 +11521,7 @@
       </c>
       <c r="L89" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M89" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11601,7 +11547,7 @@
       </c>
       <c r="S89" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T89" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11618,10 +11564,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-89</v>
       </c>
-      <c r="X89" s="60" t="s">
+      <c r="X89" s="59" t="s">
         <v>401</v>
       </c>
-      <c r="Y89" s="61" t="s">
+      <c r="Y89" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z89" s="43" t="s">
@@ -11632,23 +11578,23 @@
         <v>Structural axis guides</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="45">
         <v>90</v>
       </c>
       <c r="B90" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C90" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D90" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C90" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D90" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E90" s="59" t="s">
+      <c r="E90" s="58" t="s">
         <v>587</v>
       </c>
-      <c r="F90" s="58" t="s">
+      <c r="F90" s="57" t="s">
         <v>153</v>
       </c>
       <c r="G90" s="46" t="s">
@@ -11668,7 +11614,7 @@
       </c>
       <c r="L90" s="54" t="str">
         <f t="shared" ref="L90:L91" si="41">CONCATENATE("", C90)</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M90" s="54" t="str">
         <f t="shared" ref="M90:M91" si="42">CONCATENATE("", D90)</f>
@@ -11694,7 +11640,7 @@
       </c>
       <c r="S90" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T90" s="43" t="str">
         <f t="shared" ref="T90:T91" si="45">SUBSTITUTE(D90, "_", " ")</f>
@@ -11711,10 +11657,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-90</v>
       </c>
-      <c r="X90" s="60" t="s">
+      <c r="X90" s="59" t="s">
         <v>404</v>
       </c>
-      <c r="Y90" s="61" t="s">
+      <c r="Y90" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z90" s="43" t="s">
@@ -11725,23 +11671,23 @@
         <v>Sheets or planks</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="45">
         <v>91</v>
       </c>
       <c r="B91" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C91" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D91" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C91" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D91" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E91" s="59" t="s">
+      <c r="E91" s="58" t="s">
         <v>587</v>
       </c>
-      <c r="F91" s="58" t="s">
+      <c r="F91" s="57" t="s">
         <v>145</v>
       </c>
       <c r="G91" s="46" t="s">
@@ -11761,7 +11707,7 @@
       </c>
       <c r="L91" s="54" t="str">
         <f t="shared" si="41"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M91" s="54" t="str">
         <f t="shared" si="42"/>
@@ -11787,7 +11733,7 @@
       </c>
       <c r="S91" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T91" s="43" t="str">
         <f t="shared" si="45"/>
@@ -11804,10 +11750,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-91</v>
       </c>
-      <c r="X91" s="60" t="s">
+      <c r="X91" s="59" t="s">
         <v>404</v>
       </c>
-      <c r="Y91" s="61" t="s">
+      <c r="Y91" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z91" s="43" t="s">
@@ -11818,23 +11764,23 @@
         <v>Sheets or planks</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="45">
         <v>92</v>
       </c>
       <c r="B92" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C92" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D92" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C92" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D92" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E92" s="59" t="s">
+      <c r="E92" s="58" t="s">
         <v>587</v>
       </c>
-      <c r="F92" s="58" t="s">
+      <c r="F92" s="57" t="s">
         <v>576</v>
       </c>
       <c r="G92" s="46" t="s">
@@ -11854,7 +11800,7 @@
       </c>
       <c r="L92" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M92" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11880,7 +11826,7 @@
       </c>
       <c r="S92" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T92" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11897,10 +11843,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-92</v>
       </c>
-      <c r="X92" s="60" t="s">
+      <c r="X92" s="59" t="s">
         <v>404</v>
       </c>
-      <c r="Y92" s="61" t="s">
+      <c r="Y92" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z92" s="43" t="s">
@@ -11911,23 +11857,23 @@
         <v>Sheets or planks</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="45">
         <v>93</v>
       </c>
       <c r="B93" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C93" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D93" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C93" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D93" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E93" s="59" t="s">
+      <c r="E93" s="58" t="s">
         <v>586</v>
       </c>
-      <c r="F93" s="58" t="s">
+      <c r="F93" s="57" t="s">
         <v>146</v>
       </c>
       <c r="G93" s="46" t="s">
@@ -11947,7 +11893,7 @@
       </c>
       <c r="L93" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M93" s="54" t="str">
         <f t="shared" si="32"/>
@@ -11973,7 +11919,7 @@
       </c>
       <c r="S93" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T93" s="43" t="str">
         <f t="shared" si="38"/>
@@ -11990,10 +11936,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-93</v>
       </c>
-      <c r="X93" s="60" t="s">
+      <c r="X93" s="59" t="s">
         <v>448</v>
       </c>
-      <c r="Y93" s="61" t="s">
+      <c r="Y93" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z93" s="43" t="s">
@@ -12004,23 +11950,23 @@
         <v>Stamps and boards</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="45">
         <v>94</v>
       </c>
       <c r="B94" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C94" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D94" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C94" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D94" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E94" s="59" t="s">
+      <c r="E94" s="58" t="s">
         <v>586</v>
       </c>
-      <c r="F94" s="58" t="s">
+      <c r="F94" s="57" t="s">
         <v>516</v>
       </c>
       <c r="G94" s="46" t="s">
@@ -12040,7 +11986,7 @@
       </c>
       <c r="L94" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M94" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12066,7 +12012,7 @@
       </c>
       <c r="S94" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T94" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12083,10 +12029,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-94</v>
       </c>
-      <c r="X94" s="60" t="s">
+      <c r="X94" s="59" t="s">
         <v>449</v>
       </c>
-      <c r="Y94" s="61" t="s">
+      <c r="Y94" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z94" s="43" t="s">
@@ -12097,23 +12043,23 @@
         <v>Fine lines of stamps and boards</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="45">
         <v>95</v>
       </c>
       <c r="B95" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C95" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D95" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C95" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D95" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E95" s="59" t="s">
+      <c r="E95" s="58" t="s">
         <v>586</v>
       </c>
-      <c r="F95" s="58" t="s">
+      <c r="F95" s="57" t="s">
         <v>517</v>
       </c>
       <c r="G95" s="46" t="s">
@@ -12133,7 +12079,7 @@
       </c>
       <c r="L95" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M95" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12159,7 +12105,7 @@
       </c>
       <c r="S95" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T95" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12176,10 +12122,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-95</v>
       </c>
-      <c r="X95" s="60" t="s">
+      <c r="X95" s="59" t="s">
         <v>447</v>
       </c>
-      <c r="Y95" s="61" t="s">
+      <c r="Y95" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z95" s="43" t="s">
@@ -12190,23 +12136,23 @@
         <v>Medium lines of stamps and boards</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="45">
         <v>96</v>
       </c>
       <c r="B96" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C96" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D96" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C96" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D96" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E96" s="59" t="s">
+      <c r="E96" s="58" t="s">
         <v>586</v>
       </c>
-      <c r="F96" s="58" t="s">
+      <c r="F96" s="57" t="s">
         <v>518</v>
       </c>
       <c r="G96" s="46" t="s">
@@ -12226,7 +12172,7 @@
       </c>
       <c r="L96" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M96" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12252,7 +12198,7 @@
       </c>
       <c r="S96" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T96" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12269,10 +12215,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-96</v>
       </c>
-      <c r="X96" s="60" t="s">
+      <c r="X96" s="59" t="s">
         <v>450</v>
       </c>
-      <c r="Y96" s="61" t="s">
+      <c r="Y96" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z96" s="43" t="s">
@@ -12283,23 +12229,23 @@
         <v>Thick lines of stamps and boards</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="45">
         <v>97</v>
       </c>
       <c r="B97" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C97" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D97" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C97" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D97" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E97" s="59" t="s">
+      <c r="E97" s="58" t="s">
         <v>586</v>
       </c>
-      <c r="F97" s="58" t="s">
+      <c r="F97" s="57" t="s">
         <v>453</v>
       </c>
       <c r="G97" s="46" t="s">
@@ -12319,7 +12265,7 @@
       </c>
       <c r="L97" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M97" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12345,7 +12291,7 @@
       </c>
       <c r="S97" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T97" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12362,10 +12308,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-97</v>
       </c>
-      <c r="X97" s="60" t="s">
+      <c r="X97" s="59" t="s">
         <v>402</v>
       </c>
-      <c r="Y97" s="61" t="s">
+      <c r="Y97" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z97" s="43" t="s">
@@ -12376,23 +12322,23 @@
         <v>Design reviews</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="45">
         <v>98</v>
       </c>
       <c r="B98" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C98" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D98" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C98" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D98" s="56" t="s">
         <v>563</v>
       </c>
-      <c r="E98" s="59" t="s">
+      <c r="E98" s="58" t="s">
         <v>586</v>
       </c>
-      <c r="F98" s="58" t="s">
+      <c r="F98" s="57" t="s">
         <v>549</v>
       </c>
       <c r="G98" s="46" t="s">
@@ -12412,7 +12358,7 @@
       </c>
       <c r="L98" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M98" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12438,7 +12384,7 @@
       </c>
       <c r="S98" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T98" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12455,10 +12401,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-98</v>
       </c>
-      <c r="X98" s="60" t="s">
+      <c r="X98" s="59" t="s">
         <v>403</v>
       </c>
-      <c r="Y98" s="61" t="s">
+      <c r="Y98" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z98" s="43" t="s">
@@ -12469,23 +12415,23 @@
         <v>Design Revisions - Numbering</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="45">
         <v>99</v>
       </c>
       <c r="B99" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C99" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D99" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C99" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D99" s="56" t="s">
         <v>564</v>
       </c>
-      <c r="E99" s="59" t="s">
+      <c r="E99" s="58" t="s">
         <v>585</v>
       </c>
-      <c r="F99" s="58" t="s">
+      <c r="F99" s="57" t="s">
         <v>519</v>
       </c>
       <c r="G99" s="46" t="s">
@@ -12505,7 +12451,7 @@
       </c>
       <c r="L99" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M99" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12531,7 +12477,7 @@
       </c>
       <c r="S99" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T99" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12548,10 +12494,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-99</v>
       </c>
-      <c r="X99" s="60" t="s">
+      <c r="X99" s="59" t="s">
         <v>405</v>
       </c>
-      <c r="Y99" s="61" t="s">
+      <c r="Y99" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z99" s="43" t="s">
@@ -12562,23 +12508,23 @@
         <v>Region with lineal pattern fill</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="45">
         <v>100</v>
       </c>
       <c r="B100" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C100" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D100" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C100" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D100" s="56" t="s">
         <v>564</v>
       </c>
-      <c r="E100" s="59" t="s">
+      <c r="E100" s="58" t="s">
         <v>585</v>
       </c>
-      <c r="F100" s="58" t="s">
+      <c r="F100" s="57" t="s">
         <v>520</v>
       </c>
       <c r="G100" s="46" t="s">
@@ -12598,7 +12544,7 @@
       </c>
       <c r="L100" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M100" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12624,7 +12570,7 @@
       </c>
       <c r="S100" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T100" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12641,10 +12587,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-100</v>
       </c>
-      <c r="X100" s="60" t="s">
+      <c r="X100" s="59" t="s">
         <v>406</v>
       </c>
-      <c r="Y100" s="61" t="s">
+      <c r="Y100" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z100" s="43" t="s">
@@ -12655,23 +12601,23 @@
         <v>Hatch patterns</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="45">
         <v>101</v>
       </c>
       <c r="B101" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C101" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D101" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C101" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D101" s="56" t="s">
         <v>564</v>
       </c>
-      <c r="E101" s="59" t="s">
+      <c r="E101" s="58" t="s">
         <v>584</v>
       </c>
-      <c r="F101" s="58" t="s">
+      <c r="F101" s="57" t="s">
         <v>521</v>
       </c>
       <c r="G101" s="46" t="s">
@@ -12691,7 +12637,7 @@
       </c>
       <c r="L101" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M101" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12717,7 +12663,7 @@
       </c>
       <c r="S101" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T101" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12734,10 +12680,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-101</v>
       </c>
-      <c r="X101" s="60" t="s">
+      <c r="X101" s="59" t="s">
         <v>407</v>
       </c>
-      <c r="Y101" s="61" t="s">
+      <c r="Y101" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z101" s="43" t="s">
@@ -12748,23 +12694,23 @@
         <v>Region with color fill</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="45">
         <v>102</v>
       </c>
       <c r="B102" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C102" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D102" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C102" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D102" s="56" t="s">
         <v>564</v>
       </c>
-      <c r="E102" s="59" t="s">
+      <c r="E102" s="58" t="s">
         <v>584</v>
       </c>
-      <c r="F102" s="58" t="s">
+      <c r="F102" s="57" t="s">
         <v>569</v>
       </c>
       <c r="G102" s="46" t="s">
@@ -12784,7 +12730,7 @@
       </c>
       <c r="L102" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M102" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12810,7 +12756,7 @@
       </c>
       <c r="S102" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T102" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12827,10 +12773,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-102</v>
       </c>
-      <c r="X102" s="60" t="s">
+      <c r="X102" s="59" t="s">
         <v>408</v>
       </c>
-      <c r="Y102" s="61" t="s">
+      <c r="Y102" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z102" s="43" t="s">
@@ -12841,23 +12787,23 @@
         <v>Graphic masking region</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="45">
         <v>103</v>
       </c>
       <c r="B103" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C103" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D103" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C103" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D103" s="56" t="s">
         <v>565</v>
       </c>
-      <c r="E103" s="59" t="s">
+      <c r="E103" s="58" t="s">
         <v>583</v>
       </c>
-      <c r="F103" s="58" t="s">
+      <c r="F103" s="57" t="s">
         <v>522</v>
       </c>
       <c r="G103" s="46" t="s">
@@ -12877,7 +12823,7 @@
       </c>
       <c r="L103" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M103" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12903,7 +12849,7 @@
       </c>
       <c r="S103" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T103" s="43" t="str">
         <f t="shared" si="38"/>
@@ -12920,10 +12866,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-103</v>
       </c>
-      <c r="X103" s="60" t="s">
+      <c r="X103" s="59" t="s">
         <v>409</v>
       </c>
-      <c r="Y103" s="61" t="s">
+      <c r="Y103" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z103" s="43" t="s">
@@ -12934,23 +12880,23 @@
         <v>Coincidences</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="45">
         <v>104</v>
       </c>
       <c r="B104" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C104" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D104" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C104" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D104" s="56" t="s">
         <v>565</v>
       </c>
-      <c r="E104" s="59" t="s">
+      <c r="E104" s="58" t="s">
         <v>583</v>
       </c>
-      <c r="F104" s="58" t="s">
+      <c r="F104" s="57" t="s">
         <v>523</v>
       </c>
       <c r="G104" s="46" t="s">
@@ -12970,7 +12916,7 @@
       </c>
       <c r="L104" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M104" s="54" t="str">
         <f t="shared" si="32"/>
@@ -12996,7 +12942,7 @@
       </c>
       <c r="S104" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T104" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13013,10 +12959,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-104</v>
       </c>
-      <c r="X104" s="60" t="s">
+      <c r="X104" s="59" t="s">
         <v>410</v>
       </c>
-      <c r="Y104" s="61" t="s">
+      <c r="Y104" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z104" s="43" t="s">
@@ -13027,23 +12973,23 @@
         <v>Textual coincidences</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="45">
         <v>105</v>
       </c>
       <c r="B105" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C105" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D105" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C105" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D105" s="56" t="s">
         <v>565</v>
       </c>
-      <c r="E105" s="59" t="s">
+      <c r="E105" s="58" t="s">
         <v>583</v>
       </c>
-      <c r="F105" s="58" t="s">
+      <c r="F105" s="57" t="s">
         <v>524</v>
       </c>
       <c r="G105" s="46" t="s">
@@ -13063,7 +13009,7 @@
       </c>
       <c r="L105" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M105" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13089,7 +13035,7 @@
       </c>
       <c r="S105" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T105" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13106,10 +13052,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-105</v>
       </c>
-      <c r="X105" s="60" t="s">
+      <c r="X105" s="59" t="s">
         <v>411</v>
       </c>
-      <c r="Y105" s="61" t="s">
+      <c r="Y105" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z105" s="43" t="s">
@@ -13120,23 +13066,23 @@
         <v>Coincidences of details</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="45">
         <v>106</v>
       </c>
       <c r="B106" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C106" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D106" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C106" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D106" s="56" t="s">
         <v>565</v>
       </c>
-      <c r="E106" s="59" t="s">
+      <c r="E106" s="58" t="s">
         <v>583</v>
       </c>
-      <c r="F106" s="58" t="s">
+      <c r="F106" s="57" t="s">
         <v>525</v>
       </c>
       <c r="G106" s="46" t="s">
@@ -13156,7 +13102,7 @@
       </c>
       <c r="L106" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M106" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13182,7 +13128,7 @@
       </c>
       <c r="S106" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T106" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13199,10 +13145,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-106</v>
       </c>
-      <c r="X106" s="60" t="s">
+      <c r="X106" s="59" t="s">
         <v>412</v>
       </c>
-      <c r="Y106" s="61" t="s">
+      <c r="Y106" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z106" s="43" t="s">
@@ -13213,23 +13159,23 @@
         <v>Coincidences - Coincidence Lines</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="45">
         <v>107</v>
       </c>
       <c r="B107" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C107" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D107" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C107" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D107" s="56" t="s">
         <v>565</v>
       </c>
-      <c r="E107" s="59" t="s">
+      <c r="E107" s="58" t="s">
         <v>583</v>
       </c>
-      <c r="F107" s="58" t="s">
+      <c r="F107" s="57" t="s">
         <v>526</v>
       </c>
       <c r="G107" s="46" t="s">
@@ -13249,7 +13195,7 @@
       </c>
       <c r="L107" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M107" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13275,7 +13221,7 @@
       </c>
       <c r="S107" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T107" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13292,10 +13238,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-107</v>
       </c>
-      <c r="X107" s="60" t="s">
+      <c r="X107" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="Y107" s="61" t="s">
+      <c r="Y107" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z107" s="43" t="s">
@@ -13306,23 +13252,23 @@
         <v>Model coincidences</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="45">
         <v>108</v>
       </c>
       <c r="B108" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C108" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D108" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C108" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D108" s="56" t="s">
         <v>565</v>
       </c>
-      <c r="E108" s="59" t="s">
+      <c r="E108" s="58" t="s">
         <v>583</v>
       </c>
-      <c r="F108" s="58" t="s">
+      <c r="F108" s="57" t="s">
         <v>527</v>
       </c>
       <c r="G108" s="46" t="s">
@@ -13342,7 +13288,7 @@
       </c>
       <c r="L108" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M108" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13368,7 +13314,7 @@
       </c>
       <c r="S108" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T108" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13385,10 +13331,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-108</v>
       </c>
-      <c r="X108" s="60" t="s">
+      <c r="X108" s="59" t="s">
         <v>414</v>
       </c>
-      <c r="Y108" s="61" t="s">
+      <c r="Y108" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z108" s="43" t="s">
@@ -13399,23 +13345,23 @@
         <v>Profile matches</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="45">
         <v>109</v>
       </c>
       <c r="B109" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C109" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D109" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C109" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D109" s="56" t="s">
         <v>565</v>
       </c>
-      <c r="E109" s="59" t="s">
+      <c r="E109" s="58" t="s">
         <v>583</v>
       </c>
-      <c r="F109" s="58" t="s">
+      <c r="F109" s="57" t="s">
         <v>528</v>
       </c>
       <c r="G109" s="46" t="s">
@@ -13435,7 +13381,7 @@
       </c>
       <c r="L109" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M109" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13461,7 +13407,7 @@
       </c>
       <c r="S109" s="43" t="str">
         <f t="shared" si="37"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T109" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13478,10 +13424,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-109</v>
       </c>
-      <c r="X109" s="60" t="s">
+      <c r="X109" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="Y109" s="61" t="s">
+      <c r="Y109" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z109" s="43" t="s">
@@ -13492,23 +13438,23 @@
         <v>Coincidences of situation components</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="45">
         <v>110</v>
       </c>
       <c r="B110" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C110" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D110" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C110" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D110" s="56" t="s">
         <v>566</v>
       </c>
-      <c r="E110" s="59" t="s">
+      <c r="E110" s="58" t="s">
         <v>530</v>
       </c>
-      <c r="F110" s="58" t="s">
+      <c r="F110" s="57" t="s">
         <v>166</v>
       </c>
       <c r="G110" s="46" t="s">
@@ -13528,7 +13474,7 @@
       </c>
       <c r="L110" s="54" t="str">
         <f t="shared" ref="L110" si="50">CONCATENATE("", C110)</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M110" s="54" t="str">
         <f t="shared" ref="M110" si="51">CONCATENATE("", D110)</f>
@@ -13554,7 +13500,7 @@
       </c>
       <c r="S110" s="43" t="str">
         <f t="shared" ref="S110:S145" si="54">SUBSTITUTE(C110, "_", " ")</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T110" s="43" t="str">
         <f t="shared" ref="T110" si="55">SUBSTITUTE(D110, "_", " ")</f>
@@ -13571,10 +13517,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-110</v>
       </c>
-      <c r="X110" s="60" t="s">
+      <c r="X110" s="59" t="s">
         <v>418</v>
       </c>
-      <c r="Y110" s="61" t="s">
+      <c r="Y110" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z110" s="43" t="s">
@@ -13585,23 +13531,23 @@
         <v>Textual table</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="45">
         <v>111</v>
       </c>
       <c r="B111" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C111" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D111" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C111" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D111" s="56" t="s">
         <v>566</v>
       </c>
-      <c r="E111" s="59" t="s">
+      <c r="E111" s="58" t="s">
         <v>530</v>
       </c>
-      <c r="F111" s="58" t="s">
+      <c r="F111" s="57" t="s">
         <v>529</v>
       </c>
       <c r="G111" s="46" t="s">
@@ -13621,7 +13567,7 @@
       </c>
       <c r="L111" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M111" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13647,7 +13593,7 @@
       </c>
       <c r="S111" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T111" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13664,10 +13610,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-111</v>
       </c>
-      <c r="X111" s="60" t="s">
+      <c r="X111" s="59" t="s">
         <v>416</v>
       </c>
-      <c r="Y111" s="61" t="s">
+      <c r="Y111" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z111" s="43" t="s">
@@ -13678,23 +13624,23 @@
         <v>Graphical Table Layouts</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="45">
         <v>112</v>
       </c>
       <c r="B112" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C112" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D112" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C112" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D112" s="56" t="s">
         <v>566</v>
       </c>
-      <c r="E112" s="59" t="s">
+      <c r="E112" s="58" t="s">
         <v>530</v>
       </c>
-      <c r="F112" s="58" t="s">
+      <c r="F112" s="57" t="s">
         <v>199</v>
       </c>
       <c r="G112" s="46" t="s">
@@ -13714,7 +13660,7 @@
       </c>
       <c r="L112" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M112" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13740,7 +13686,7 @@
       </c>
       <c r="S112" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T112" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13757,10 +13703,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-112</v>
       </c>
-      <c r="X112" s="60" t="s">
+      <c r="X112" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="Y112" s="61" t="s">
+      <c r="Y112" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z112" s="43" t="s">
@@ -13771,23 +13717,23 @@
         <v>Graphical table</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="45">
         <v>113</v>
       </c>
       <c r="B113" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C113" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D113" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C113" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D113" s="56" t="s">
         <v>566</v>
       </c>
-      <c r="E113" s="59" t="s">
+      <c r="E113" s="58" t="s">
         <v>530</v>
       </c>
-      <c r="F113" s="58" t="s">
+      <c r="F113" s="57" t="s">
         <v>531</v>
       </c>
       <c r="G113" s="46" t="s">
@@ -13807,7 +13753,7 @@
       </c>
       <c r="L113" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M113" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13833,7 +13779,7 @@
       </c>
       <c r="S113" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T113" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13850,10 +13796,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-113</v>
       </c>
-      <c r="X113" s="60" t="s">
+      <c r="X113" s="59" t="s">
         <v>419</v>
       </c>
-      <c r="Y113" s="61" t="s">
+      <c r="Y113" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z113" s="43" t="s">
@@ -13864,23 +13810,23 @@
         <v>Set of parameters of a table</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="45">
         <v>114</v>
       </c>
       <c r="B114" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C114" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D114" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C114" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D114" s="56" t="s">
         <v>566</v>
       </c>
-      <c r="E114" s="59" t="s">
+      <c r="E114" s="58" t="s">
         <v>530</v>
       </c>
-      <c r="F114" s="58" t="s">
+      <c r="F114" s="57" t="s">
         <v>532</v>
       </c>
       <c r="G114" s="46" t="s">
@@ -13900,7 +13846,7 @@
       </c>
       <c r="L114" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M114" s="54" t="str">
         <f t="shared" si="32"/>
@@ -13926,7 +13872,7 @@
       </c>
       <c r="S114" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T114" s="43" t="str">
         <f t="shared" si="38"/>
@@ -13943,10 +13889,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-114</v>
       </c>
-      <c r="X114" s="60" t="s">
+      <c r="X114" s="59" t="s">
         <v>420</v>
       </c>
-      <c r="Y114" s="61" t="s">
+      <c r="Y114" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z114" s="43" t="s">
@@ -13957,23 +13903,23 @@
         <v>Circuit Tables Template</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="45">
         <v>115</v>
       </c>
       <c r="B115" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C115" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D115" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C115" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D115" s="56" t="s">
         <v>567</v>
       </c>
       <c r="E115" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="F115" s="58" t="s">
+      <c r="F115" s="57" t="s">
         <v>571</v>
       </c>
       <c r="G115" s="46" t="s">
@@ -13993,7 +13939,7 @@
       </c>
       <c r="L115" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M115" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14019,7 +13965,7 @@
       </c>
       <c r="S115" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T115" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14036,10 +13982,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-115</v>
       </c>
-      <c r="X115" s="60" t="s">
+      <c r="X115" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="Y115" s="61" t="s">
+      <c r="Y115" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z115" s="43" t="s">
@@ -14050,23 +13996,23 @@
         <v>Annotation - textual cut space</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="45">
         <v>116</v>
       </c>
       <c r="B116" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C116" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D116" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C116" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D116" s="56" t="s">
         <v>567</v>
       </c>
       <c r="E116" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="F116" s="58" t="s">
+      <c r="F116" s="57" t="s">
         <v>572</v>
       </c>
       <c r="G116" s="46" t="s">
@@ -14086,7 +14032,7 @@
       </c>
       <c r="L116" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M116" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14112,7 +14058,7 @@
       </c>
       <c r="S116" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T116" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14129,10 +14075,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-116</v>
       </c>
-      <c r="X116" s="60" t="s">
+      <c r="X116" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="Y116" s="61" t="s">
+      <c r="Y116" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z116" s="43" t="s">
@@ -14143,23 +14089,23 @@
         <v>Annotation - special textual cutout space</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="45">
         <v>117</v>
       </c>
       <c r="B117" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C117" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D117" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C117" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D117" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E117" s="59" t="s">
+      <c r="E117" s="58" t="s">
         <v>548</v>
       </c>
-      <c r="F117" s="58" t="s">
+      <c r="F117" s="57" t="s">
         <v>582</v>
       </c>
       <c r="G117" s="46" t="s">
@@ -14179,7 +14125,7 @@
       </c>
       <c r="L117" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M117" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14205,7 +14151,7 @@
       </c>
       <c r="S117" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T117" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14222,10 +14168,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-117</v>
       </c>
-      <c r="X117" s="60" t="s">
+      <c r="X117" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="Y117" s="61" t="s">
+      <c r="Y117" s="60" t="s">
         <v>441</v>
       </c>
       <c r="Z117" s="43" t="s">
@@ -14236,23 +14182,23 @@
         <v>3D Model Texts</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="45">
         <v>118</v>
       </c>
       <c r="B118" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C118" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D118" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C118" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D118" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E118" s="59" t="s">
+      <c r="E118" s="58" t="s">
         <v>548</v>
       </c>
-      <c r="F118" s="58" t="s">
+      <c r="F118" s="57" t="s">
         <v>536</v>
       </c>
       <c r="G118" s="46" t="s">
@@ -14272,7 +14218,7 @@
       </c>
       <c r="L118" s="54" t="str">
         <f t="shared" ref="L118" si="60">CONCATENATE("", C118)</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M118" s="54" t="str">
         <f t="shared" ref="M118" si="61">CONCATENATE("", D118)</f>
@@ -14298,7 +14244,7 @@
       </c>
       <c r="S118" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T118" s="43" t="str">
         <f t="shared" ref="T118" si="64">SUBSTITUTE(D118, "_", " ")</f>
@@ -14315,10 +14261,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-118</v>
       </c>
-      <c r="X118" s="60" t="s">
+      <c r="X118" s="59" t="s">
         <v>424</v>
       </c>
-      <c r="Y118" s="61" t="s">
+      <c r="Y118" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z118" s="43" t="s">
@@ -14329,23 +14275,23 @@
         <v>Textual notes</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="45">
         <v>119</v>
       </c>
       <c r="B119" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C119" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D119" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C119" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D119" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E119" s="59" t="s">
+      <c r="E119" s="58" t="s">
         <v>548</v>
       </c>
-      <c r="F119" s="58" t="s">
+      <c r="F119" s="57" t="s">
         <v>533</v>
       </c>
       <c r="G119" s="46" t="s">
@@ -14365,7 +14311,7 @@
       </c>
       <c r="L119" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M119" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14391,7 +14337,7 @@
       </c>
       <c r="S119" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T119" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14408,10 +14354,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-119</v>
       </c>
-      <c r="X119" s="60" t="s">
+      <c r="X119" s="59" t="s">
         <v>421</v>
       </c>
-      <c r="Y119" s="61" t="s">
+      <c r="Y119" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z119" s="43" t="s">
@@ -14422,23 +14368,23 @@
         <v>Generic annotations</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="45">
         <v>120</v>
       </c>
       <c r="B120" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C120" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D120" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C120" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D120" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E120" s="59" t="s">
+      <c r="E120" s="58" t="s">
         <v>548</v>
       </c>
-      <c r="F120" s="58" t="s">
+      <c r="F120" s="57" t="s">
         <v>534</v>
       </c>
       <c r="G120" s="46" t="s">
@@ -14458,7 +14404,7 @@
       </c>
       <c r="L120" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M120" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14484,7 +14430,7 @@
       </c>
       <c r="S120" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T120" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14501,10 +14447,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-120</v>
       </c>
-      <c r="X120" s="60" t="s">
+      <c r="X120" s="59" t="s">
         <v>422</v>
       </c>
-      <c r="Y120" s="61" t="s">
+      <c r="Y120" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z120" s="43" t="s">
@@ -14515,23 +14461,23 @@
         <v>Multiple textual references</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="45">
         <v>121</v>
       </c>
       <c r="B121" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C121" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D121" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C121" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D121" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E121" s="59" t="s">
+      <c r="E121" s="58" t="s">
         <v>548</v>
       </c>
-      <c r="F121" s="58" t="s">
+      <c r="F121" s="57" t="s">
         <v>535</v>
       </c>
       <c r="G121" s="46" t="s">
@@ -14551,7 +14497,7 @@
       </c>
       <c r="L121" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M121" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14577,7 +14523,7 @@
       </c>
       <c r="S121" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T121" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14594,10 +14540,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-121</v>
       </c>
-      <c r="X121" s="60" t="s">
+      <c r="X121" s="59" t="s">
         <v>423</v>
       </c>
-      <c r="Y121" s="61" t="s">
+      <c r="Y121" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z121" s="43" t="s">
@@ -14608,23 +14554,23 @@
         <v>Structural annotations</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="45">
         <v>122</v>
       </c>
       <c r="B122" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C122" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D122" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C122" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D122" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E122" s="59" t="s">
+      <c r="E122" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F122" s="58" t="s">
+      <c r="F122" s="57" t="s">
         <v>542</v>
       </c>
       <c r="G122" s="46" t="s">
@@ -14644,7 +14590,7 @@
       </c>
       <c r="L122" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M122" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14670,7 +14616,7 @@
       </c>
       <c r="S122" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T122" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14687,10 +14633,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-122</v>
       </c>
-      <c r="X122" s="60" t="s">
+      <c r="X122" s="59" t="s">
         <v>425</v>
       </c>
-      <c r="Y122" s="61" t="s">
+      <c r="Y122" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z122" s="43" t="s">
@@ -14701,23 +14647,23 @@
         <v>2D Detailing Component - Textual Label or Tag</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="45">
         <v>123</v>
       </c>
       <c r="B123" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C123" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D123" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C123" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D123" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E123" s="59" t="s">
+      <c r="E123" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F123" s="58" t="s">
+      <c r="F123" s="57" t="s">
         <v>541</v>
       </c>
       <c r="G123" s="46" t="s">
@@ -14737,7 +14683,7 @@
       </c>
       <c r="L123" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M123" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14763,7 +14709,7 @@
       </c>
       <c r="S123" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T123" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14780,10 +14726,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-123</v>
       </c>
-      <c r="X123" s="60" t="s">
+      <c r="X123" s="59" t="s">
         <v>426</v>
       </c>
-      <c r="Y123" s="61" t="s">
+      <c r="Y123" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z123" s="43" t="s">
@@ -14794,23 +14740,23 @@
         <v>Key Notes - Textual Tag or Tag</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="45">
         <v>124</v>
       </c>
       <c r="B124" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C124" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D124" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C124" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D124" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E124" s="59" t="s">
+      <c r="E124" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F124" s="58" t="s">
+      <c r="F124" s="57" t="s">
         <v>540</v>
       </c>
       <c r="G124" s="46" t="s">
@@ -14830,7 +14776,7 @@
       </c>
       <c r="L124" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M124" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14856,7 +14802,7 @@
       </c>
       <c r="S124" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T124" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14873,10 +14819,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-124</v>
       </c>
-      <c r="X124" s="60" t="s">
+      <c r="X124" s="59" t="s">
         <v>427</v>
       </c>
-      <c r="Y124" s="61" t="s">
+      <c r="Y124" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z124" s="43" t="s">
@@ -14887,23 +14833,23 @@
         <v>Template Groups - Textual Label or Tag</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="45">
         <v>125</v>
       </c>
       <c r="B125" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C125" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D125" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C125" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D125" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E125" s="59" t="s">
+      <c r="E125" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F125" s="58" t="s">
+      <c r="F125" s="57" t="s">
         <v>539</v>
       </c>
       <c r="G125" s="46" t="s">
@@ -14923,7 +14869,7 @@
       </c>
       <c r="L125" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M125" s="54" t="str">
         <f t="shared" si="32"/>
@@ -14949,7 +14895,7 @@
       </c>
       <c r="S125" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T125" s="43" t="str">
         <f t="shared" si="38"/>
@@ -14966,10 +14912,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-125</v>
       </c>
-      <c r="X125" s="60" t="s">
+      <c r="X125" s="59" t="s">
         <v>428</v>
       </c>
-      <c r="Y125" s="61" t="s">
+      <c r="Y125" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z125" s="43" t="s">
@@ -14980,23 +14926,23 @@
         <v>Textual Label or Milticategoria Tag</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="45">
         <v>126</v>
       </c>
       <c r="B126" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C126" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D126" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C126" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D126" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E126" s="59" t="s">
+      <c r="E126" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F126" s="58" t="s">
+      <c r="F126" s="57" t="s">
         <v>538</v>
       </c>
       <c r="G126" s="46" t="s">
@@ -15016,7 +14962,7 @@
       </c>
       <c r="L126" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M126" s="54" t="str">
         <f t="shared" si="32"/>
@@ -15042,7 +14988,7 @@
       </c>
       <c r="S126" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T126" s="43" t="str">
         <f t="shared" si="38"/>
@@ -15059,10 +15005,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-126</v>
       </c>
-      <c r="X126" s="60" t="s">
+      <c r="X126" s="59" t="s">
         <v>429</v>
       </c>
-      <c r="Y126" s="61" t="s">
+      <c r="Y126" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z126" s="43" t="s">
@@ -15073,23 +15019,23 @@
         <v>Multiple Leader Lines - Textual Tag or Tag</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="45">
         <v>127</v>
       </c>
       <c r="B127" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C127" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D127" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C127" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D127" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E127" s="59" t="s">
+      <c r="E127" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F127" s="58" t="s">
+      <c r="F127" s="57" t="s">
         <v>176</v>
       </c>
       <c r="G127" s="46" t="s">
@@ -15109,7 +15055,7 @@
       </c>
       <c r="L127" s="54" t="str">
         <f t="shared" ref="L127:L129" si="65">CONCATENATE("", C127)</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M127" s="54" t="str">
         <f t="shared" ref="M127:M129" si="66">CONCATENATE("", D127)</f>
@@ -15135,7 +15081,7 @@
       </c>
       <c r="S127" s="43" t="str">
         <f t="shared" ref="S127:S129" si="69">SUBSTITUTE(C127, "_", " ")</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T127" s="43" t="str">
         <f t="shared" ref="T127:T129" si="70">SUBSTITUTE(D127, "_", " ")</f>
@@ -15152,10 +15098,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-127</v>
       </c>
-      <c r="X127" s="60" t="s">
+      <c r="X127" s="59" t="s">
         <v>430</v>
       </c>
-      <c r="Y127" s="61" t="s">
+      <c r="Y127" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z127" s="43" t="s">
@@ -15166,23 +15112,23 @@
         <v>Textual Label or Tag</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="45">
         <v>128</v>
       </c>
       <c r="B128" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C128" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D128" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C128" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D128" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E128" s="59" t="s">
+      <c r="E128" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F128" s="58" t="s">
+      <c r="F128" s="57" t="s">
         <v>607</v>
       </c>
       <c r="G128" s="46" t="s">
@@ -15202,7 +15148,7 @@
       </c>
       <c r="L128" s="54" t="str">
         <f t="shared" si="65"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M128" s="54" t="str">
         <f t="shared" si="66"/>
@@ -15228,7 +15174,7 @@
       </c>
       <c r="S128" s="43" t="str">
         <f t="shared" si="69"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T128" s="43" t="str">
         <f t="shared" si="70"/>
@@ -15245,10 +15191,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-128</v>
       </c>
-      <c r="X128" s="60" t="s">
+      <c r="X128" s="59" t="s">
         <v>612</v>
       </c>
-      <c r="Y128" s="61" t="s">
+      <c r="Y128" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z128" s="43" t="s">
@@ -15259,23 +15205,23 @@
         <v>Textual Label or Wall Tag</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="45">
         <v>129</v>
       </c>
       <c r="B129" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C129" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D129" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C129" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D129" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E129" s="59" t="s">
+      <c r="E129" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F129" s="58" t="s">
+      <c r="F129" s="57" t="s">
         <v>608</v>
       </c>
       <c r="G129" s="46" t="s">
@@ -15295,7 +15241,7 @@
       </c>
       <c r="L129" s="54" t="str">
         <f t="shared" si="65"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M129" s="54" t="str">
         <f t="shared" si="66"/>
@@ -15321,7 +15267,7 @@
       </c>
       <c r="S129" s="43" t="str">
         <f t="shared" si="69"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T129" s="43" t="str">
         <f t="shared" si="70"/>
@@ -15338,10 +15284,10 @@
         <f t="shared" si="30"/>
         <v>Key-DOCU-129</v>
       </c>
-      <c r="X129" s="60" t="s">
+      <c r="X129" s="59" t="s">
         <v>610</v>
       </c>
-      <c r="Y129" s="61" t="s">
+      <c r="Y129" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z129" s="43" t="s">
@@ -15352,23 +15298,23 @@
         <v>Textual Label or Door Tag</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="45">
         <v>130</v>
       </c>
       <c r="B130" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C130" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D130" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C130" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D130" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="E130" s="59" t="s">
+      <c r="E130" s="58" t="s">
         <v>537</v>
       </c>
-      <c r="F130" s="58" t="s">
+      <c r="F130" s="57" t="s">
         <v>609</v>
       </c>
       <c r="G130" s="46" t="s">
@@ -15388,7 +15334,7 @@
       </c>
       <c r="L130" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M130" s="54" t="str">
         <f t="shared" si="32"/>
@@ -15414,7 +15360,7 @@
       </c>
       <c r="S130" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T130" s="43" t="str">
         <f t="shared" si="38"/>
@@ -15431,10 +15377,10 @@
         <f t="shared" ref="W130:W145" si="73">CONCATENATE("Key-DOCU-",A130)</f>
         <v>Key-DOCU-130</v>
       </c>
-      <c r="X130" s="60" t="s">
+      <c r="X130" s="59" t="s">
         <v>611</v>
       </c>
-      <c r="Y130" s="61" t="s">
+      <c r="Y130" s="60" t="s">
         <v>323</v>
       </c>
       <c r="Z130" s="43" t="s">
@@ -15445,23 +15391,23 @@
         <v>Textual Label or Windows Tag</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="45">
         <v>131</v>
       </c>
       <c r="B131" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C131" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D131" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C131" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D131" s="56" t="s">
         <v>578</v>
       </c>
-      <c r="E131" s="59" t="s">
+      <c r="E131" s="58" t="s">
         <v>579</v>
       </c>
-      <c r="F131" s="58" t="s">
+      <c r="F131" s="57" t="s">
         <v>260</v>
       </c>
       <c r="G131" s="46" t="s">
@@ -15481,7 +15427,7 @@
       </c>
       <c r="L131" s="54" t="str">
         <f t="shared" ref="L131" si="74">CONCATENATE("", C131)</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M131" s="54" t="str">
         <f t="shared" ref="M131" si="75">CONCATENATE("", D131)</f>
@@ -15507,7 +15453,7 @@
       </c>
       <c r="S131" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T131" s="43" t="str">
         <f t="shared" ref="T131" si="78">SUBSTITUTE(D131, "_", " ")</f>
@@ -15538,23 +15484,23 @@
         <v>Licensing is not required. The document is Public Domain</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="45">
         <v>132</v>
       </c>
       <c r="B132" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C132" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D132" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C132" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D132" s="56" t="s">
         <v>578</v>
       </c>
-      <c r="E132" s="59" t="s">
+      <c r="E132" s="58" t="s">
         <v>579</v>
       </c>
-      <c r="F132" s="58" t="s">
+      <c r="F132" s="57" t="s">
         <v>580</v>
       </c>
       <c r="G132" s="46" t="s">
@@ -15574,7 +15520,7 @@
       </c>
       <c r="L132" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M132" s="54" t="str">
         <f t="shared" si="32"/>
@@ -15600,7 +15546,7 @@
       </c>
       <c r="S132" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T132" s="43" t="str">
         <f t="shared" si="38"/>
@@ -15631,23 +15577,23 @@
         <v>Creative Commons License</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="45">
         <v>133</v>
       </c>
       <c r="B133" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C133" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D133" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C133" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D133" s="56" t="s">
         <v>578</v>
       </c>
-      <c r="E133" s="59" t="s">
+      <c r="E133" s="58" t="s">
         <v>579</v>
       </c>
-      <c r="F133" s="58" t="s">
+      <c r="F133" s="57" t="s">
         <v>259</v>
       </c>
       <c r="G133" s="46" t="s">
@@ -15667,7 +15613,7 @@
       </c>
       <c r="L133" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M133" s="54" t="str">
         <f t="shared" si="32"/>
@@ -15693,7 +15639,7 @@
       </c>
       <c r="S133" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T133" s="43" t="str">
         <f t="shared" si="38"/>
@@ -15724,23 +15670,23 @@
         <v>Copyright License</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="45">
         <v>134</v>
       </c>
       <c r="B134" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C134" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D134" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C134" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D134" s="56" t="s">
         <v>578</v>
       </c>
-      <c r="E134" s="59" t="s">
+      <c r="E134" s="58" t="s">
         <v>579</v>
       </c>
-      <c r="F134" s="58" t="s">
+      <c r="F134" s="57" t="s">
         <v>245</v>
       </c>
       <c r="G134" s="46" t="s">
@@ -15760,7 +15706,7 @@
       </c>
       <c r="L134" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M134" s="54" t="str">
         <f t="shared" si="32"/>
@@ -15786,7 +15732,7 @@
       </c>
       <c r="S134" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T134" s="43" t="str">
         <f t="shared" si="38"/>
@@ -15817,23 +15763,23 @@
         <v>Industrial Law License</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="45">
         <v>135</v>
       </c>
       <c r="B135" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C135" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D135" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C135" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D135" s="56" t="s">
         <v>578</v>
       </c>
-      <c r="E135" s="59" t="s">
+      <c r="E135" s="58" t="s">
         <v>278</v>
       </c>
-      <c r="F135" s="58" t="s">
+      <c r="F135" s="57" t="s">
         <v>268</v>
       </c>
       <c r="G135" s="46" t="s">
@@ -15853,7 +15799,7 @@
       </c>
       <c r="L135" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M135" s="54" t="str">
         <f t="shared" si="32"/>
@@ -15879,7 +15825,7 @@
       </c>
       <c r="S135" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T135" s="43" t="str">
         <f t="shared" si="38"/>
@@ -15910,23 +15856,23 @@
         <v>Law published in Brazil</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="45">
         <v>136</v>
       </c>
       <c r="B136" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C136" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D136" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C136" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D136" s="56" t="s">
         <v>578</v>
       </c>
-      <c r="E136" s="59" t="s">
+      <c r="E136" s="58" t="s">
         <v>278</v>
       </c>
-      <c r="F136" s="58" t="s">
+      <c r="F136" s="57" t="s">
         <v>269</v>
       </c>
       <c r="G136" s="46" t="s">
@@ -15946,7 +15892,7 @@
       </c>
       <c r="L136" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M136" s="54" t="str">
         <f t="shared" si="32"/>
@@ -15972,7 +15918,7 @@
       </c>
       <c r="S136" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T136" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16003,23 +15949,23 @@
         <v>Decree published in Brazil</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="45">
         <v>137</v>
       </c>
       <c r="B137" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C137" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D137" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C137" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D137" s="56" t="s">
         <v>578</v>
       </c>
-      <c r="E137" s="59" t="s">
+      <c r="E137" s="58" t="s">
         <v>278</v>
       </c>
-      <c r="F137" s="58" t="s">
+      <c r="F137" s="57" t="s">
         <v>281</v>
       </c>
       <c r="G137" s="46" t="s">
@@ -16039,7 +15985,7 @@
       </c>
       <c r="L137" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M137" s="54" t="str">
         <f t="shared" si="32"/>
@@ -16065,7 +16011,7 @@
       </c>
       <c r="S137" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T137" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16096,23 +16042,23 @@
         <v>Bill in Brazil</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="45">
         <v>138</v>
       </c>
       <c r="B138" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C138" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D138" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C138" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D138" s="56" t="s">
         <v>568</v>
       </c>
-      <c r="E138" s="59" t="s">
+      <c r="E138" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="F138" s="58" t="s">
+      <c r="F138" s="57" t="s">
         <v>288</v>
       </c>
       <c r="G138" s="46" t="s">
@@ -16132,7 +16078,7 @@
       </c>
       <c r="L138" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M138" s="54" t="str">
         <f t="shared" si="32"/>
@@ -16158,7 +16104,7 @@
       </c>
       <c r="S138" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T138" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16189,23 +16135,23 @@
         <v>Internal Guide to Technical Procedures</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="45">
         <v>139</v>
       </c>
       <c r="B139" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C139" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D139" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C139" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D139" s="56" t="s">
         <v>568</v>
       </c>
-      <c r="E139" s="59" t="s">
+      <c r="E139" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="F139" s="58" t="s">
+      <c r="F139" s="57" t="s">
         <v>287</v>
       </c>
       <c r="G139" s="46" t="s">
@@ -16225,7 +16171,7 @@
       </c>
       <c r="L139" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M139" s="54" t="str">
         <f t="shared" si="32"/>
@@ -16251,7 +16197,7 @@
       </c>
       <c r="S139" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T139" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16282,23 +16228,23 @@
         <v>Internal Manual of Technical Procedures</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="45">
         <v>140</v>
       </c>
       <c r="B140" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C140" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D140" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C140" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D140" s="56" t="s">
         <v>568</v>
       </c>
-      <c r="E140" s="59" t="s">
+      <c r="E140" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="F140" s="58" t="s">
+      <c r="F140" s="57" t="s">
         <v>290</v>
       </c>
       <c r="G140" s="46" t="s">
@@ -16318,7 +16264,7 @@
       </c>
       <c r="L140" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M140" s="54" t="str">
         <f t="shared" si="32"/>
@@ -16344,7 +16290,7 @@
       </c>
       <c r="S140" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T140" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16375,23 +16321,23 @@
         <v>Technical book</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="45">
         <v>141</v>
       </c>
       <c r="B141" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C141" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D141" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C141" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D141" s="56" t="s">
         <v>568</v>
       </c>
-      <c r="E141" s="59" t="s">
+      <c r="E141" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="F141" s="58" t="s">
+      <c r="F141" s="57" t="s">
         <v>294</v>
       </c>
       <c r="G141" s="46" t="s">
@@ -16411,7 +16357,7 @@
       </c>
       <c r="L141" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M141" s="54" t="str">
         <f t="shared" si="32"/>
@@ -16437,7 +16383,7 @@
       </c>
       <c r="S141" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T141" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16468,23 +16414,23 @@
         <v>Training</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="45">
         <v>142</v>
       </c>
       <c r="B142" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C142" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D142" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C142" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D142" s="56" t="s">
         <v>568</v>
       </c>
-      <c r="E142" s="59" t="s">
+      <c r="E142" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="F142" s="58" t="s">
+      <c r="F142" s="57" t="s">
         <v>289</v>
       </c>
       <c r="G142" s="46" t="s">
@@ -16504,7 +16450,7 @@
       </c>
       <c r="L142" s="54" t="str">
         <f t="shared" si="31"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M142" s="54" t="str">
         <f t="shared" si="32"/>
@@ -16530,7 +16476,7 @@
       </c>
       <c r="S142" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T142" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16561,23 +16507,23 @@
         <v>Normative</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="45">
         <v>143</v>
       </c>
       <c r="B143" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C143" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D143" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C143" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D143" s="56" t="s">
         <v>568</v>
       </c>
-      <c r="E143" s="59" t="s">
+      <c r="E143" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="F143" s="58" t="s">
+      <c r="F143" s="57" t="s">
         <v>295</v>
       </c>
       <c r="G143" s="46" t="s">
@@ -16597,7 +16543,7 @@
       </c>
       <c r="L143" s="54" t="str">
         <f t="shared" ref="L143:L145" si="81">CONCATENATE("", C143)</f>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M143" s="54" t="str">
         <f t="shared" ref="M143:M145" si="82">CONCATENATE("", D143)</f>
@@ -16623,7 +16569,7 @@
       </c>
       <c r="S143" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T143" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16654,23 +16600,23 @@
         <v>PowerPoint presentations or similar</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="45">
         <v>144</v>
       </c>
       <c r="B144" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C144" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D144" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C144" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D144" s="56" t="s">
         <v>568</v>
       </c>
-      <c r="E144" s="59" t="s">
+      <c r="E144" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="F144" s="58" t="s">
+      <c r="F144" s="57" t="s">
         <v>298</v>
       </c>
       <c r="G144" s="46" t="s">
@@ -16690,7 +16636,7 @@
       </c>
       <c r="L144" s="54" t="str">
         <f t="shared" si="81"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M144" s="54" t="str">
         <f t="shared" si="82"/>
@@ -16716,7 +16662,7 @@
       </c>
       <c r="S144" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T144" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16747,23 +16693,23 @@
         <v>Internal binders</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="45">
         <v>145</v>
       </c>
       <c r="B145" s="52" t="s">
-        <v>657</v>
-      </c>
-      <c r="C145" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D145" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C145" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D145" s="56" t="s">
         <v>568</v>
       </c>
-      <c r="E145" s="59" t="s">
+      <c r="E145" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="F145" s="58" t="s">
+      <c r="F145" s="57" t="s">
         <v>299</v>
       </c>
       <c r="G145" s="46" t="s">
@@ -16783,7 +16729,7 @@
       </c>
       <c r="L145" s="54" t="str">
         <f t="shared" si="81"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="M145" s="54" t="str">
         <f t="shared" si="82"/>
@@ -16809,7 +16755,7 @@
       </c>
       <c r="S145" s="43" t="str">
         <f t="shared" si="54"/>
-        <v>Documental</v>
+        <v>Documentais</v>
       </c>
       <c r="T145" s="43" t="str">
         <f t="shared" si="38"/>
@@ -16844,39 +16790,34 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:Z146">
     <sortCondition ref="A1:A146"/>
   </sortState>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F7:F1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="9" priority="26" operator="equal">
+  <conditionalFormatting sqref="A2:B145">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 A7:A145 AA7:AA145">
-    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
+  <conditionalFormatting sqref="F1 F7:F1048576">
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="11" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:O1">
+    <cfRule type="cellIs" dxfId="2" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B145">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA145">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16887,14 +16828,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.7109375" style="12"/>
-    <col min="11" max="16384" width="5.7109375" style="24"/>
+    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.69140625" style="12"/>
+    <col min="11" max="16384" width="5.69140625" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -16959,7 +16900,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -17032,15 +16973,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.15234375" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -17054,7 +16995,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -17076,34 +17017,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{429087C4-377B-4931-BC50-C00BD9684F83}">
   <dimension ref="A1:W37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="7" max="7" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.84375" customWidth="1"/>
+    <col min="5" max="5" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.84375" customWidth="1"/>
+    <col min="7" max="7" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.84375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.42578125" customWidth="1"/>
-    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.28515625" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.69140625" customWidth="1"/>
+    <col min="16" max="16" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.3828125" customWidth="1"/>
+    <col min="19" max="19" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.3046875" customWidth="1"/>
+    <col min="21" max="21" width="11.15234375" customWidth="1"/>
+    <col min="22" max="22" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -17174,7 +17115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -17245,7 +17186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -17316,7 +17257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -17387,7 +17328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -17458,7 +17399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -17529,7 +17470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -17600,7 +17541,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -17671,7 +17612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -17742,7 +17683,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -17813,7 +17754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -17884,7 +17825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -17955,7 +17896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -18026,7 +17967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -18097,7 +18038,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -18168,7 +18109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -18239,7 +18180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -18310,7 +18251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -18381,7 +18322,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -18452,7 +18393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -18523,7 +18464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -18594,7 +18535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -18665,7 +18606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -18736,7 +18677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -18807,7 +18748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -18878,7 +18819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -18949,7 +18890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -19020,7 +18961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -19091,7 +19032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -19162,7 +19103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -19233,7 +19174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -19304,7 +19245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -19375,7 +19316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -19446,7 +19387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -19517,7 +19458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -19588,7 +19529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -19659,7 +19600,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -19733,7 +19674,7 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="B18:B37 B1:B13">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
